--- a/results/metrics.xlsx
+++ b/results/metrics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahmadabdullah/Desktop/GHaLIB/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBFA307F-602D-8441-8959-88063D069CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9C827D-1205-644B-9787-587A8763D497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="21">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -67,13 +67,22 @@
     <t>F-1 (D)</t>
   </si>
   <si>
-    <t>Accuracy (T)</t>
+    <t>RoBERTa + ROS</t>
   </si>
   <si>
-    <t>F-1 (T)</t>
+    <t>Test Score</t>
   </si>
   <si>
-    <t>RoBERTa + ROS</t>
+    <t>Currently best on LB</t>
+  </si>
+  <si>
+    <t>Best is 0.85</t>
+  </si>
+  <si>
+    <t>DistilBERT</t>
+  </si>
+  <si>
+    <t>GloVe</t>
   </si>
 </sst>
 </file>
@@ -91,11 +100,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -418,12 +429,10 @@
       <c r="H1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J1" s="7" t="s">
+      <c r="I1" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="J1" s="7"/>
       <c r="K1" s="3"/>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
@@ -463,13 +472,17 @@
         <v>7</v>
       </c>
       <c r="G2" s="4">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="H2" s="4">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
+      <c r="I2" s="4">
+        <v>0.79</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
@@ -509,12 +522,11 @@
         <v>7</v>
       </c>
       <c r="G3" s="4">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="H3" s="4">
-        <v>0.5</v>
+        <v>0.56000000000000005</v>
       </c>
-      <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
@@ -560,8 +572,12 @@
       <c r="H4" s="4">
         <v>0.93</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
+      <c r="I4" s="4">
+        <v>0.95</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
@@ -606,8 +622,12 @@
       <c r="H5" s="4">
         <v>0.53</v>
       </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
+      <c r="I5" s="4">
+        <v>0.77</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
@@ -635,7 +655,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>12</v>
@@ -681,7 +701,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>12</v>
@@ -723,11 +743,27 @@
       <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
+      <c r="B8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0.67</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.54</v>
+      </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
@@ -753,11 +789,27 @@
       <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
+      <c r="B9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0.78</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.78</v>
+      </c>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
@@ -783,11 +835,27 @@
       <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="B10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0.73</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.73</v>
+      </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
@@ -813,11 +881,27 @@
       <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
+      <c r="B11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="4">
+        <v>0.62</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.44</v>
+      </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>

--- a/results/metrics.xlsx
+++ b/results/metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahmadabdullah/Desktop/GHaLIB/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9C827D-1205-644B-9787-587A8763D497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60989895-397F-E248-A90B-F0E20F7E2D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="20">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -74,9 +74,6 @@
   </si>
   <si>
     <t>Currently best on LB</t>
-  </si>
-  <si>
-    <t>Best is 0.85</t>
   </si>
   <si>
     <t>DistilBERT</t>
@@ -472,16 +469,16 @@
         <v>7</v>
       </c>
       <c r="G2" s="4">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="H2" s="4">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="I2" s="4">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
@@ -623,7 +620,7 @@
         <v>0.53</v>
       </c>
       <c r="I5" s="4">
-        <v>0.77</v>
+        <v>0.53</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>17</v>
@@ -747,7 +744,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>12</v>
@@ -793,7 +790,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>12</v>
@@ -839,7 +836,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>12</v>
@@ -885,7 +882,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>12</v>

--- a/results/metrics.xlsx
+++ b/results/metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahmadabdullah/Desktop/GHaLIB/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60989895-397F-E248-A90B-F0E20F7E2D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B7F4A3-FF33-784C-8F95-F12A83F010D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="24">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -80,6 +80,18 @@
   </si>
   <si>
     <t>GloVe</t>
+  </si>
+  <si>
+    <t>UrduBERT</t>
+  </si>
+  <si>
+    <t>RoBERTa Urdu</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>MultiLing BERT</t>
   </si>
 </sst>
 </file>
@@ -156,7 +168,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -168,11 +180,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -399,6 +419,8 @@
     <col min="2" max="2" width="12.6640625" customWidth="1"/>
     <col min="3" max="3" width="13.6640625" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="9" max="9" width="16.6640625" customWidth="1"/>
+    <col min="10" max="10" width="22.6640625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.2">
@@ -414,22 +436,24 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>14</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="7"/>
+      <c r="J1" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="K1" s="3"/>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
@@ -450,34 +474,34 @@
       <c r="AB1" s="4"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A2" s="4">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="7">
         <v>0.85</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="7">
         <v>0.85</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="7">
         <v>0.85</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="7" t="s">
         <v>17</v>
       </c>
       <c r="K2" s="4"/>
@@ -500,31 +524,32 @@
       <c r="AB2" s="4"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A3" s="4">
+      <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="7">
         <v>0.68</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="7">
         <v>0.56000000000000005</v>
       </c>
-      <c r="J3" s="4"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="7"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
@@ -545,34 +570,34 @@
       <c r="AB3" s="4"/>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A4" s="4">
+      <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>4</v>
+      <c r="C4" s="7" t="s">
+        <v>21</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="7">
         <v>0.93</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="7">
         <v>0.93</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="7">
         <v>0.95</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="7" t="s">
         <v>17</v>
       </c>
       <c r="K4" s="4"/>
@@ -595,34 +620,34 @@
       <c r="AB4" s="4"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A5" s="4">
+      <c r="A5" s="7">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>4</v>
+      <c r="C5" s="7" t="s">
+        <v>21</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="7">
         <v>0.73</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="7">
         <v>0.53</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="7">
         <v>0.53</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="7" t="s">
         <v>17</v>
       </c>
       <c r="K5" s="4"/>
@@ -645,32 +670,32 @@
       <c r="AB5" s="4"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A6" s="4">
+      <c r="A6" s="7">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="7">
         <v>0.61</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="7">
         <v>0.52</v>
       </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
@@ -691,32 +716,32 @@
       <c r="AB6" s="4"/>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A7" s="4">
+      <c r="A7" s="7">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="7">
         <v>0.56000000000000005</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="7">
         <v>0.24</v>
       </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
@@ -737,32 +762,32 @@
       <c r="AB7" s="4"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A8" s="4">
+      <c r="A8" s="7">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="7">
         <v>0.67</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="7">
         <v>0.54</v>
       </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
@@ -783,32 +808,32 @@
       <c r="AB8" s="4"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A9" s="4">
+      <c r="A9" s="7">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="7">
         <v>0.78</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="7">
         <v>0.78</v>
       </c>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
@@ -829,32 +854,32 @@
       <c r="AB9" s="4"/>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A10" s="4">
+      <c r="A10" s="7">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="7">
         <v>0.73</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="7">
         <v>0.73</v>
       </c>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
@@ -875,32 +900,32 @@
       <c r="AB10" s="4"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A11" s="4">
+      <c r="A11" s="7">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="7">
         <v>0.62</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="7">
         <v>0.44</v>
       </c>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
@@ -921,18 +946,32 @@
       <c r="AB11" s="4"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A12" s="4">
+      <c r="A12" s="7">
         <v>11</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
+      <c r="B12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G12" s="7">
+        <v>0.93</v>
+      </c>
+      <c r="H12" s="7">
+        <v>0.93</v>
+      </c>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
@@ -953,18 +992,32 @@
       <c r="AB12" s="4"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A13" s="4">
+      <c r="A13" s="7">
         <v>12</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
+      <c r="B13" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="7">
+        <v>0.71</v>
+      </c>
+      <c r="H13" s="7">
+        <v>0.51</v>
+      </c>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
@@ -985,18 +1038,32 @@
       <c r="AB13" s="4"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A14" s="4">
+      <c r="A14" s="7">
         <v>13</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
+      <c r="B14" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G14" s="7">
+        <v>0.85</v>
+      </c>
+      <c r="H14" s="7">
+        <v>0.85</v>
+      </c>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
@@ -1017,18 +1084,32 @@
       <c r="AB14" s="4"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A15" s="4">
+      <c r="A15" s="7">
         <v>14</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
+      <c r="B15" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G15" s="7">
+        <v>0.68</v>
+      </c>
+      <c r="H15" s="7">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
@@ -1049,18 +1130,32 @@
       <c r="AB15" s="4"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A16" s="4">
+      <c r="A16" s="7">
         <v>15</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
+      <c r="B16" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G16" s="7">
+        <v>0.93</v>
+      </c>
+      <c r="H16" s="7">
+        <v>0.93</v>
+      </c>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
@@ -1081,18 +1176,32 @@
       <c r="AB16" s="4"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A17" s="4">
+      <c r="A17" s="7">
         <v>16</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
+      <c r="B17" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G17" s="7">
+        <v>0.73</v>
+      </c>
+      <c r="H17" s="7">
+        <v>0.53</v>
+      </c>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
@@ -1113,18 +1222,32 @@
       <c r="AB17" s="4"/>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A18" s="4">
+      <c r="A18" s="7">
         <v>17</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
+      <c r="B18" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G18" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="H18" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
@@ -1145,18 +1268,32 @@
       <c r="AB18" s="4"/>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A19" s="4">
+      <c r="A19" s="7">
         <v>18</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
+      <c r="B19" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G19" s="7">
+        <v>0.68</v>
+      </c>
+      <c r="H19" s="7">
+        <v>0.49</v>
+      </c>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
@@ -1177,18 +1314,32 @@
       <c r="AB19" s="4"/>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A20" s="4">
+      <c r="A20" s="7">
         <v>19</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
+      <c r="B20" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G20" s="7">
+        <v>0.93</v>
+      </c>
+      <c r="H20" s="7">
+        <v>0.93</v>
+      </c>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
@@ -1209,18 +1360,32 @@
       <c r="AB20" s="4"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A21" s="4">
+      <c r="A21" s="7">
         <v>20</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
+      <c r="B21" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G21" s="7">
+        <v>0.73</v>
+      </c>
+      <c r="H21" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
@@ -1250,7 +1415,7 @@
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
+      <c r="J22" s="7"/>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
@@ -1280,7 +1445,7 @@
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
+      <c r="J23" s="7"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
@@ -1310,7 +1475,7 @@
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
+      <c r="J24" s="7"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
@@ -1340,7 +1505,7 @@
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
+      <c r="J25" s="7"/>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
@@ -1370,7 +1535,7 @@
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
+      <c r="J26" s="7"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
@@ -1400,7 +1565,7 @@
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
+      <c r="J27" s="7"/>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
@@ -1430,7 +1595,7 @@
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
+      <c r="J28" s="7"/>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
@@ -1460,7 +1625,7 @@
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
+      <c r="J29" s="7"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
@@ -1490,7 +1655,7 @@
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
+      <c r="J30" s="7"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
@@ -1520,7 +1685,7 @@
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
+      <c r="J31" s="7"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
@@ -1550,7 +1715,7 @@
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
+      <c r="J32" s="7"/>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
@@ -1580,7 +1745,7 @@
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
+      <c r="J33" s="7"/>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
@@ -1610,7 +1775,7 @@
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
+      <c r="J34" s="7"/>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
@@ -1640,7 +1805,7 @@
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
+      <c r="J35" s="7"/>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
       <c r="M35" s="4"/>
@@ -1670,7 +1835,7 @@
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
+      <c r="J36" s="7"/>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
       <c r="M36" s="4"/>
@@ -1700,7 +1865,7 @@
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
+      <c r="J37" s="7"/>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
       <c r="M37" s="4"/>
@@ -1730,7 +1895,7 @@
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
+      <c r="J38" s="7"/>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
@@ -1760,7 +1925,7 @@
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
+      <c r="J39" s="7"/>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
       <c r="M39" s="4"/>
@@ -1790,7 +1955,7 @@
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
+      <c r="J40" s="7"/>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
@@ -1820,7 +1985,7 @@
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
+      <c r="J41" s="7"/>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
       <c r="M41" s="4"/>
@@ -1850,7 +2015,7 @@
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
+      <c r="J42" s="7"/>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
       <c r="M42" s="4"/>
@@ -1880,7 +2045,7 @@
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
+      <c r="J43" s="7"/>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
@@ -1910,7 +2075,7 @@
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
+      <c r="J44" s="7"/>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
       <c r="M44" s="4"/>
@@ -1940,7 +2105,7 @@
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
+      <c r="J45" s="7"/>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
@@ -1970,7 +2135,7 @@
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
+      <c r="J46" s="7"/>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
       <c r="M46" s="4"/>
@@ -2000,7 +2165,7 @@
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
+      <c r="J47" s="7"/>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
       <c r="M47" s="4"/>
@@ -2030,7 +2195,7 @@
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
+      <c r="J48" s="7"/>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
@@ -2060,7 +2225,7 @@
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
+      <c r="J49" s="7"/>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
@@ -2090,7 +2255,7 @@
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
+      <c r="J50" s="7"/>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
       <c r="M50" s="4"/>
@@ -2120,7 +2285,7 @@
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
+      <c r="J51" s="7"/>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
@@ -2150,7 +2315,7 @@
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
-      <c r="J52" s="4"/>
+      <c r="J52" s="7"/>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
@@ -2180,7 +2345,7 @@
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
+      <c r="J53" s="7"/>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
@@ -2210,7 +2375,7 @@
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
+      <c r="J54" s="7"/>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>
       <c r="M54" s="4"/>
@@ -2240,7 +2405,7 @@
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
-      <c r="J55" s="4"/>
+      <c r="J55" s="7"/>
       <c r="K55" s="4"/>
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
@@ -2270,7 +2435,7 @@
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
-      <c r="J56" s="4"/>
+      <c r="J56" s="7"/>
       <c r="K56" s="4"/>
       <c r="L56" s="4"/>
       <c r="M56" s="4"/>
@@ -2300,7 +2465,7 @@
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
-      <c r="J57" s="4"/>
+      <c r="J57" s="7"/>
       <c r="K57" s="4"/>
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
@@ -2330,7 +2495,7 @@
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
-      <c r="J58" s="4"/>
+      <c r="J58" s="7"/>
       <c r="K58" s="4"/>
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
@@ -2360,7 +2525,7 @@
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
-      <c r="J59" s="4"/>
+      <c r="J59" s="7"/>
       <c r="K59" s="4"/>
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
@@ -2390,7 +2555,7 @@
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
-      <c r="J60" s="4"/>
+      <c r="J60" s="7"/>
       <c r="K60" s="4"/>
       <c r="L60" s="4"/>
       <c r="M60" s="4"/>
@@ -2420,7 +2585,7 @@
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
-      <c r="J61" s="4"/>
+      <c r="J61" s="7"/>
       <c r="K61" s="4"/>
       <c r="L61" s="4"/>
       <c r="M61" s="4"/>
@@ -2450,7 +2615,7 @@
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
-      <c r="J62" s="4"/>
+      <c r="J62" s="7"/>
       <c r="K62" s="4"/>
       <c r="L62" s="4"/>
       <c r="M62" s="4"/>
@@ -2480,7 +2645,7 @@
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
-      <c r="J63" s="4"/>
+      <c r="J63" s="7"/>
       <c r="K63" s="4"/>
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
@@ -2510,7 +2675,7 @@
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
-      <c r="J64" s="4"/>
+      <c r="J64" s="7"/>
       <c r="K64" s="4"/>
       <c r="L64" s="4"/>
       <c r="M64" s="4"/>
@@ -2540,7 +2705,7 @@
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
-      <c r="J65" s="4"/>
+      <c r="J65" s="7"/>
       <c r="K65" s="4"/>
       <c r="L65" s="4"/>
       <c r="M65" s="4"/>
@@ -2570,7 +2735,7 @@
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
-      <c r="J66" s="4"/>
+      <c r="J66" s="7"/>
       <c r="K66" s="4"/>
       <c r="L66" s="4"/>
       <c r="M66" s="4"/>
@@ -2600,7 +2765,7 @@
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
-      <c r="J67" s="4"/>
+      <c r="J67" s="7"/>
       <c r="K67" s="4"/>
       <c r="L67" s="4"/>
       <c r="M67" s="4"/>
@@ -2630,7 +2795,7 @@
       <c r="G68" s="4"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
-      <c r="J68" s="4"/>
+      <c r="J68" s="7"/>
       <c r="K68" s="4"/>
       <c r="L68" s="4"/>
       <c r="M68" s="4"/>
@@ -2660,7 +2825,7 @@
       <c r="G69" s="4"/>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
-      <c r="J69" s="4"/>
+      <c r="J69" s="7"/>
       <c r="K69" s="4"/>
       <c r="L69" s="4"/>
       <c r="M69" s="4"/>
@@ -2690,7 +2855,7 @@
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
-      <c r="J70" s="4"/>
+      <c r="J70" s="7"/>
       <c r="K70" s="4"/>
       <c r="L70" s="4"/>
       <c r="M70" s="4"/>
@@ -2720,7 +2885,7 @@
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
-      <c r="J71" s="4"/>
+      <c r="J71" s="7"/>
       <c r="K71" s="4"/>
       <c r="L71" s="4"/>
       <c r="M71" s="4"/>
@@ -2750,7 +2915,7 @@
       <c r="G72" s="4"/>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
-      <c r="J72" s="4"/>
+      <c r="J72" s="7"/>
       <c r="K72" s="4"/>
       <c r="L72" s="4"/>
       <c r="M72" s="4"/>
@@ -2780,7 +2945,7 @@
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
-      <c r="J73" s="4"/>
+      <c r="J73" s="7"/>
       <c r="K73" s="4"/>
       <c r="L73" s="4"/>
       <c r="M73" s="4"/>
@@ -2810,7 +2975,7 @@
       <c r="G74" s="4"/>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
-      <c r="J74" s="4"/>
+      <c r="J74" s="7"/>
       <c r="K74" s="4"/>
       <c r="L74" s="4"/>
       <c r="M74" s="4"/>
@@ -2840,7 +3005,7 @@
       <c r="G75" s="4"/>
       <c r="H75" s="4"/>
       <c r="I75" s="4"/>
-      <c r="J75" s="4"/>
+      <c r="J75" s="7"/>
       <c r="K75" s="4"/>
       <c r="L75" s="4"/>
       <c r="M75" s="4"/>
@@ -2870,7 +3035,7 @@
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
-      <c r="J76" s="4"/>
+      <c r="J76" s="7"/>
       <c r="K76" s="4"/>
       <c r="L76" s="4"/>
       <c r="M76" s="4"/>
@@ -2900,7 +3065,7 @@
       <c r="G77" s="4"/>
       <c r="H77" s="4"/>
       <c r="I77" s="4"/>
-      <c r="J77" s="4"/>
+      <c r="J77" s="7"/>
       <c r="K77" s="4"/>
       <c r="L77" s="4"/>
       <c r="M77" s="4"/>
@@ -2930,7 +3095,7 @@
       <c r="G78" s="4"/>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
-      <c r="J78" s="4"/>
+      <c r="J78" s="7"/>
       <c r="K78" s="4"/>
       <c r="L78" s="4"/>
       <c r="M78" s="4"/>
@@ -2960,7 +3125,7 @@
       <c r="G79" s="4"/>
       <c r="H79" s="4"/>
       <c r="I79" s="4"/>
-      <c r="J79" s="4"/>
+      <c r="J79" s="7"/>
       <c r="K79" s="4"/>
       <c r="L79" s="4"/>
       <c r="M79" s="4"/>
@@ -2990,7 +3155,7 @@
       <c r="G80" s="4"/>
       <c r="H80" s="4"/>
       <c r="I80" s="4"/>
-      <c r="J80" s="4"/>
+      <c r="J80" s="7"/>
       <c r="K80" s="4"/>
       <c r="L80" s="4"/>
       <c r="M80" s="4"/>
@@ -3020,7 +3185,7 @@
       <c r="G81" s="4"/>
       <c r="H81" s="4"/>
       <c r="I81" s="4"/>
-      <c r="J81" s="4"/>
+      <c r="J81" s="7"/>
       <c r="K81" s="4"/>
       <c r="L81" s="4"/>
       <c r="M81" s="4"/>
@@ -3050,7 +3215,7 @@
       <c r="G82" s="4"/>
       <c r="H82" s="4"/>
       <c r="I82" s="4"/>
-      <c r="J82" s="4"/>
+      <c r="J82" s="7"/>
       <c r="K82" s="4"/>
       <c r="L82" s="4"/>
       <c r="M82" s="4"/>
@@ -3080,7 +3245,7 @@
       <c r="G83" s="4"/>
       <c r="H83" s="4"/>
       <c r="I83" s="4"/>
-      <c r="J83" s="4"/>
+      <c r="J83" s="7"/>
       <c r="K83" s="4"/>
       <c r="L83" s="4"/>
       <c r="M83" s="4"/>
@@ -3110,7 +3275,7 @@
       <c r="G84" s="4"/>
       <c r="H84" s="4"/>
       <c r="I84" s="4"/>
-      <c r="J84" s="4"/>
+      <c r="J84" s="7"/>
       <c r="K84" s="4"/>
       <c r="L84" s="4"/>
       <c r="M84" s="4"/>
@@ -3140,7 +3305,7 @@
       <c r="G85" s="4"/>
       <c r="H85" s="4"/>
       <c r="I85" s="4"/>
-      <c r="J85" s="4"/>
+      <c r="J85" s="7"/>
       <c r="K85" s="4"/>
       <c r="L85" s="4"/>
       <c r="M85" s="4"/>
@@ -3170,7 +3335,7 @@
       <c r="G86" s="4"/>
       <c r="H86" s="4"/>
       <c r="I86" s="4"/>
-      <c r="J86" s="4"/>
+      <c r="J86" s="7"/>
       <c r="K86" s="4"/>
       <c r="L86" s="4"/>
       <c r="M86" s="4"/>
@@ -3200,7 +3365,7 @@
       <c r="G87" s="4"/>
       <c r="H87" s="4"/>
       <c r="I87" s="4"/>
-      <c r="J87" s="4"/>
+      <c r="J87" s="7"/>
       <c r="K87" s="4"/>
       <c r="L87" s="4"/>
       <c r="M87" s="4"/>
@@ -3230,7 +3395,7 @@
       <c r="G88" s="4"/>
       <c r="H88" s="4"/>
       <c r="I88" s="4"/>
-      <c r="J88" s="4"/>
+      <c r="J88" s="7"/>
       <c r="K88" s="4"/>
       <c r="L88" s="4"/>
       <c r="M88" s="4"/>
@@ -3260,7 +3425,7 @@
       <c r="G89" s="4"/>
       <c r="H89" s="4"/>
       <c r="I89" s="4"/>
-      <c r="J89" s="4"/>
+      <c r="J89" s="7"/>
       <c r="K89" s="4"/>
       <c r="L89" s="4"/>
       <c r="M89" s="4"/>
@@ -3290,7 +3455,7 @@
       <c r="G90" s="4"/>
       <c r="H90" s="4"/>
       <c r="I90" s="4"/>
-      <c r="J90" s="4"/>
+      <c r="J90" s="7"/>
       <c r="K90" s="4"/>
       <c r="L90" s="4"/>
       <c r="M90" s="4"/>
@@ -3320,7 +3485,7 @@
       <c r="G91" s="4"/>
       <c r="H91" s="4"/>
       <c r="I91" s="4"/>
-      <c r="J91" s="4"/>
+      <c r="J91" s="7"/>
       <c r="K91" s="4"/>
       <c r="L91" s="4"/>
       <c r="M91" s="4"/>
@@ -3350,7 +3515,7 @@
       <c r="G92" s="4"/>
       <c r="H92" s="4"/>
       <c r="I92" s="4"/>
-      <c r="J92" s="4"/>
+      <c r="J92" s="7"/>
       <c r="K92" s="4"/>
       <c r="L92" s="4"/>
       <c r="M92" s="4"/>
@@ -3380,7 +3545,7 @@
       <c r="G93" s="4"/>
       <c r="H93" s="4"/>
       <c r="I93" s="4"/>
-      <c r="J93" s="4"/>
+      <c r="J93" s="7"/>
       <c r="K93" s="4"/>
       <c r="L93" s="4"/>
       <c r="M93" s="4"/>
@@ -3410,7 +3575,7 @@
       <c r="G94" s="4"/>
       <c r="H94" s="4"/>
       <c r="I94" s="4"/>
-      <c r="J94" s="4"/>
+      <c r="J94" s="7"/>
       <c r="K94" s="4"/>
       <c r="L94" s="4"/>
       <c r="M94" s="4"/>
@@ -3440,7 +3605,7 @@
       <c r="G95" s="4"/>
       <c r="H95" s="4"/>
       <c r="I95" s="4"/>
-      <c r="J95" s="4"/>
+      <c r="J95" s="7"/>
       <c r="K95" s="4"/>
       <c r="L95" s="4"/>
       <c r="M95" s="4"/>
@@ -3470,7 +3635,7 @@
       <c r="G96" s="4"/>
       <c r="H96" s="4"/>
       <c r="I96" s="4"/>
-      <c r="J96" s="4"/>
+      <c r="J96" s="7"/>
       <c r="K96" s="4"/>
       <c r="L96" s="4"/>
       <c r="M96" s="4"/>
@@ -3500,7 +3665,7 @@
       <c r="G97" s="4"/>
       <c r="H97" s="4"/>
       <c r="I97" s="4"/>
-      <c r="J97" s="4"/>
+      <c r="J97" s="7"/>
       <c r="K97" s="4"/>
       <c r="L97" s="4"/>
       <c r="M97" s="4"/>
@@ -3530,7 +3695,7 @@
       <c r="G98" s="4"/>
       <c r="H98" s="4"/>
       <c r="I98" s="4"/>
-      <c r="J98" s="4"/>
+      <c r="J98" s="7"/>
       <c r="K98" s="4"/>
       <c r="L98" s="4"/>
       <c r="M98" s="4"/>
@@ -3560,7 +3725,7 @@
       <c r="G99" s="4"/>
       <c r="H99" s="4"/>
       <c r="I99" s="4"/>
-      <c r="J99" s="4"/>
+      <c r="J99" s="7"/>
       <c r="K99" s="4"/>
       <c r="L99" s="4"/>
       <c r="M99" s="4"/>
@@ -3590,7 +3755,7 @@
       <c r="G100" s="4"/>
       <c r="H100" s="4"/>
       <c r="I100" s="4"/>
-      <c r="J100" s="4"/>
+      <c r="J100" s="7"/>
       <c r="K100" s="4"/>
       <c r="L100" s="4"/>
       <c r="M100" s="4"/>
@@ -3620,7 +3785,7 @@
       <c r="G101" s="4"/>
       <c r="H101" s="4"/>
       <c r="I101" s="4"/>
-      <c r="J101" s="4"/>
+      <c r="J101" s="7"/>
       <c r="K101" s="4"/>
       <c r="L101" s="4"/>
       <c r="M101" s="4"/>
@@ -3650,7 +3815,7 @@
       <c r="G102" s="4"/>
       <c r="H102" s="4"/>
       <c r="I102" s="4"/>
-      <c r="J102" s="4"/>
+      <c r="J102" s="7"/>
       <c r="K102" s="4"/>
       <c r="L102" s="4"/>
       <c r="M102" s="4"/>
@@ -3680,7 +3845,7 @@
       <c r="G103" s="4"/>
       <c r="H103" s="4"/>
       <c r="I103" s="4"/>
-      <c r="J103" s="4"/>
+      <c r="J103" s="7"/>
       <c r="K103" s="4"/>
       <c r="L103" s="4"/>
       <c r="M103" s="4"/>
@@ -3710,7 +3875,7 @@
       <c r="G104" s="4"/>
       <c r="H104" s="4"/>
       <c r="I104" s="4"/>
-      <c r="J104" s="4"/>
+      <c r="J104" s="7"/>
       <c r="K104" s="4"/>
       <c r="L104" s="4"/>
       <c r="M104" s="4"/>
@@ -3740,7 +3905,7 @@
       <c r="G105" s="4"/>
       <c r="H105" s="4"/>
       <c r="I105" s="4"/>
-      <c r="J105" s="4"/>
+      <c r="J105" s="7"/>
       <c r="K105" s="4"/>
       <c r="L105" s="4"/>
       <c r="M105" s="4"/>
@@ -3770,7 +3935,7 @@
       <c r="G106" s="4"/>
       <c r="H106" s="4"/>
       <c r="I106" s="4"/>
-      <c r="J106" s="4"/>
+      <c r="J106" s="7"/>
       <c r="K106" s="4"/>
       <c r="L106" s="4"/>
       <c r="M106" s="4"/>
@@ -3800,7 +3965,7 @@
       <c r="G107" s="4"/>
       <c r="H107" s="4"/>
       <c r="I107" s="4"/>
-      <c r="J107" s="4"/>
+      <c r="J107" s="7"/>
       <c r="K107" s="4"/>
       <c r="L107" s="4"/>
       <c r="M107" s="4"/>
@@ -3830,7 +3995,7 @@
       <c r="G108" s="4"/>
       <c r="H108" s="4"/>
       <c r="I108" s="4"/>
-      <c r="J108" s="4"/>
+      <c r="J108" s="7"/>
       <c r="K108" s="4"/>
       <c r="L108" s="4"/>
       <c r="M108" s="4"/>
@@ -3860,7 +4025,7 @@
       <c r="G109" s="4"/>
       <c r="H109" s="4"/>
       <c r="I109" s="4"/>
-      <c r="J109" s="4"/>
+      <c r="J109" s="7"/>
       <c r="K109" s="4"/>
       <c r="L109" s="4"/>
       <c r="M109" s="4"/>
@@ -3890,7 +4055,7 @@
       <c r="G110" s="4"/>
       <c r="H110" s="4"/>
       <c r="I110" s="4"/>
-      <c r="J110" s="4"/>
+      <c r="J110" s="7"/>
       <c r="K110" s="4"/>
       <c r="L110" s="4"/>
       <c r="M110" s="4"/>
@@ -3920,7 +4085,7 @@
       <c r="G111" s="4"/>
       <c r="H111" s="4"/>
       <c r="I111" s="4"/>
-      <c r="J111" s="4"/>
+      <c r="J111" s="7"/>
       <c r="K111" s="4"/>
       <c r="L111" s="4"/>
       <c r="M111" s="4"/>
@@ -3950,7 +4115,7 @@
       <c r="G112" s="4"/>
       <c r="H112" s="4"/>
       <c r="I112" s="4"/>
-      <c r="J112" s="4"/>
+      <c r="J112" s="7"/>
       <c r="K112" s="4"/>
       <c r="L112" s="4"/>
       <c r="M112" s="4"/>
@@ -3980,7 +4145,7 @@
       <c r="G113" s="4"/>
       <c r="H113" s="4"/>
       <c r="I113" s="4"/>
-      <c r="J113" s="4"/>
+      <c r="J113" s="7"/>
       <c r="K113" s="4"/>
       <c r="L113" s="4"/>
       <c r="M113" s="4"/>
@@ -4010,7 +4175,7 @@
       <c r="G114" s="4"/>
       <c r="H114" s="4"/>
       <c r="I114" s="4"/>
-      <c r="J114" s="4"/>
+      <c r="J114" s="7"/>
       <c r="K114" s="4"/>
       <c r="L114" s="4"/>
       <c r="M114" s="4"/>
@@ -4040,7 +4205,7 @@
       <c r="G115" s="4"/>
       <c r="H115" s="4"/>
       <c r="I115" s="4"/>
-      <c r="J115" s="4"/>
+      <c r="J115" s="7"/>
       <c r="K115" s="4"/>
       <c r="L115" s="4"/>
       <c r="M115" s="4"/>
@@ -4070,7 +4235,7 @@
       <c r="G116" s="4"/>
       <c r="H116" s="4"/>
       <c r="I116" s="4"/>
-      <c r="J116" s="4"/>
+      <c r="J116" s="7"/>
       <c r="K116" s="4"/>
       <c r="L116" s="4"/>
       <c r="M116" s="4"/>
@@ -4100,7 +4265,7 @@
       <c r="G117" s="4"/>
       <c r="H117" s="4"/>
       <c r="I117" s="4"/>
-      <c r="J117" s="4"/>
+      <c r="J117" s="7"/>
       <c r="K117" s="4"/>
       <c r="L117" s="4"/>
       <c r="M117" s="4"/>
@@ -4130,7 +4295,7 @@
       <c r="G118" s="4"/>
       <c r="H118" s="4"/>
       <c r="I118" s="4"/>
-      <c r="J118" s="4"/>
+      <c r="J118" s="7"/>
       <c r="K118" s="4"/>
       <c r="L118" s="4"/>
       <c r="M118" s="4"/>
@@ -4160,7 +4325,7 @@
       <c r="G119" s="4"/>
       <c r="H119" s="4"/>
       <c r="I119" s="4"/>
-      <c r="J119" s="4"/>
+      <c r="J119" s="7"/>
       <c r="K119" s="4"/>
       <c r="L119" s="4"/>
       <c r="M119" s="4"/>
@@ -4190,7 +4355,7 @@
       <c r="G120" s="4"/>
       <c r="H120" s="4"/>
       <c r="I120" s="4"/>
-      <c r="J120" s="4"/>
+      <c r="J120" s="7"/>
       <c r="K120" s="4"/>
       <c r="L120" s="4"/>
       <c r="M120" s="4"/>
@@ -4220,7 +4385,7 @@
       <c r="G121" s="4"/>
       <c r="H121" s="4"/>
       <c r="I121" s="4"/>
-      <c r="J121" s="4"/>
+      <c r="J121" s="7"/>
       <c r="K121" s="4"/>
       <c r="L121" s="4"/>
       <c r="M121" s="4"/>
@@ -4250,7 +4415,7 @@
       <c r="G122" s="4"/>
       <c r="H122" s="4"/>
       <c r="I122" s="4"/>
-      <c r="J122" s="4"/>
+      <c r="J122" s="7"/>
       <c r="K122" s="4"/>
       <c r="L122" s="4"/>
       <c r="M122" s="4"/>
@@ -4280,7 +4445,7 @@
       <c r="G123" s="4"/>
       <c r="H123" s="4"/>
       <c r="I123" s="4"/>
-      <c r="J123" s="4"/>
+      <c r="J123" s="7"/>
       <c r="K123" s="4"/>
       <c r="L123" s="4"/>
       <c r="M123" s="4"/>
@@ -4310,7 +4475,7 @@
       <c r="G124" s="4"/>
       <c r="H124" s="4"/>
       <c r="I124" s="4"/>
-      <c r="J124" s="4"/>
+      <c r="J124" s="7"/>
       <c r="K124" s="4"/>
       <c r="L124" s="4"/>
       <c r="M124" s="4"/>
@@ -4340,7 +4505,7 @@
       <c r="G125" s="4"/>
       <c r="H125" s="4"/>
       <c r="I125" s="4"/>
-      <c r="J125" s="4"/>
+      <c r="J125" s="7"/>
       <c r="K125" s="4"/>
       <c r="L125" s="4"/>
       <c r="M125" s="4"/>
@@ -4370,7 +4535,7 @@
       <c r="G126" s="4"/>
       <c r="H126" s="4"/>
       <c r="I126" s="4"/>
-      <c r="J126" s="4"/>
+      <c r="J126" s="7"/>
       <c r="K126" s="4"/>
       <c r="L126" s="4"/>
       <c r="M126" s="4"/>
@@ -4400,7 +4565,7 @@
       <c r="G127" s="4"/>
       <c r="H127" s="4"/>
       <c r="I127" s="4"/>
-      <c r="J127" s="4"/>
+      <c r="J127" s="7"/>
       <c r="K127" s="4"/>
       <c r="L127" s="4"/>
       <c r="M127" s="4"/>
@@ -4430,7 +4595,7 @@
       <c r="G128" s="4"/>
       <c r="H128" s="4"/>
       <c r="I128" s="4"/>
-      <c r="J128" s="4"/>
+      <c r="J128" s="7"/>
       <c r="K128" s="4"/>
       <c r="L128" s="4"/>
       <c r="M128" s="4"/>
@@ -4460,7 +4625,7 @@
       <c r="G129" s="4"/>
       <c r="H129" s="4"/>
       <c r="I129" s="4"/>
-      <c r="J129" s="4"/>
+      <c r="J129" s="7"/>
       <c r="K129" s="4"/>
       <c r="L129" s="4"/>
       <c r="M129" s="4"/>
@@ -4490,7 +4655,7 @@
       <c r="G130" s="4"/>
       <c r="H130" s="4"/>
       <c r="I130" s="4"/>
-      <c r="J130" s="4"/>
+      <c r="J130" s="7"/>
       <c r="K130" s="4"/>
       <c r="L130" s="4"/>
       <c r="M130" s="4"/>
@@ -4520,7 +4685,7 @@
       <c r="G131" s="4"/>
       <c r="H131" s="4"/>
       <c r="I131" s="4"/>
-      <c r="J131" s="4"/>
+      <c r="J131" s="7"/>
       <c r="K131" s="4"/>
       <c r="L131" s="4"/>
       <c r="M131" s="4"/>
@@ -4550,7 +4715,7 @@
       <c r="G132" s="4"/>
       <c r="H132" s="4"/>
       <c r="I132" s="4"/>
-      <c r="J132" s="4"/>
+      <c r="J132" s="7"/>
       <c r="K132" s="4"/>
       <c r="L132" s="4"/>
       <c r="M132" s="4"/>
@@ -4580,7 +4745,7 @@
       <c r="G133" s="4"/>
       <c r="H133" s="4"/>
       <c r="I133" s="4"/>
-      <c r="J133" s="4"/>
+      <c r="J133" s="7"/>
       <c r="K133" s="4"/>
       <c r="L133" s="4"/>
       <c r="M133" s="4"/>
@@ -4610,7 +4775,7 @@
       <c r="G134" s="4"/>
       <c r="H134" s="4"/>
       <c r="I134" s="4"/>
-      <c r="J134" s="4"/>
+      <c r="J134" s="7"/>
       <c r="K134" s="4"/>
       <c r="L134" s="4"/>
       <c r="M134" s="4"/>
@@ -4640,7 +4805,7 @@
       <c r="G135" s="4"/>
       <c r="H135" s="4"/>
       <c r="I135" s="4"/>
-      <c r="J135" s="4"/>
+      <c r="J135" s="7"/>
       <c r="K135" s="4"/>
       <c r="L135" s="4"/>
       <c r="M135" s="4"/>
@@ -4670,7 +4835,7 @@
       <c r="G136" s="4"/>
       <c r="H136" s="4"/>
       <c r="I136" s="4"/>
-      <c r="J136" s="4"/>
+      <c r="J136" s="7"/>
       <c r="K136" s="4"/>
       <c r="L136" s="4"/>
       <c r="M136" s="4"/>
@@ -4700,7 +4865,7 @@
       <c r="G137" s="4"/>
       <c r="H137" s="4"/>
       <c r="I137" s="4"/>
-      <c r="J137" s="4"/>
+      <c r="J137" s="7"/>
       <c r="K137" s="4"/>
       <c r="L137" s="4"/>
       <c r="M137" s="4"/>
@@ -4730,7 +4895,7 @@
       <c r="G138" s="4"/>
       <c r="H138" s="4"/>
       <c r="I138" s="4"/>
-      <c r="J138" s="4"/>
+      <c r="J138" s="7"/>
       <c r="K138" s="4"/>
       <c r="L138" s="4"/>
       <c r="M138" s="4"/>
@@ -4760,7 +4925,7 @@
       <c r="G139" s="4"/>
       <c r="H139" s="4"/>
       <c r="I139" s="4"/>
-      <c r="J139" s="4"/>
+      <c r="J139" s="7"/>
       <c r="K139" s="4"/>
       <c r="L139" s="4"/>
       <c r="M139" s="4"/>
@@ -4790,7 +4955,7 @@
       <c r="G140" s="4"/>
       <c r="H140" s="4"/>
       <c r="I140" s="4"/>
-      <c r="J140" s="4"/>
+      <c r="J140" s="7"/>
       <c r="K140" s="4"/>
       <c r="L140" s="4"/>
       <c r="M140" s="4"/>
@@ -4820,7 +4985,7 @@
       <c r="G141" s="4"/>
       <c r="H141" s="4"/>
       <c r="I141" s="4"/>
-      <c r="J141" s="4"/>
+      <c r="J141" s="7"/>
       <c r="K141" s="4"/>
       <c r="L141" s="4"/>
       <c r="M141" s="4"/>
@@ -4850,7 +5015,7 @@
       <c r="G142" s="4"/>
       <c r="H142" s="4"/>
       <c r="I142" s="4"/>
-      <c r="J142" s="4"/>
+      <c r="J142" s="7"/>
       <c r="K142" s="4"/>
       <c r="L142" s="4"/>
       <c r="M142" s="4"/>
@@ -4880,7 +5045,7 @@
       <c r="G143" s="4"/>
       <c r="H143" s="4"/>
       <c r="I143" s="4"/>
-      <c r="J143" s="4"/>
+      <c r="J143" s="7"/>
       <c r="K143" s="4"/>
       <c r="L143" s="4"/>
       <c r="M143" s="4"/>
@@ -4910,7 +5075,7 @@
       <c r="G144" s="4"/>
       <c r="H144" s="4"/>
       <c r="I144" s="4"/>
-      <c r="J144" s="4"/>
+      <c r="J144" s="7"/>
       <c r="K144" s="4"/>
       <c r="L144" s="4"/>
       <c r="M144" s="4"/>
@@ -4940,7 +5105,7 @@
       <c r="G145" s="4"/>
       <c r="H145" s="4"/>
       <c r="I145" s="4"/>
-      <c r="J145" s="4"/>
+      <c r="J145" s="7"/>
       <c r="K145" s="4"/>
       <c r="L145" s="4"/>
       <c r="M145" s="4"/>
@@ -4970,7 +5135,7 @@
       <c r="G146" s="4"/>
       <c r="H146" s="4"/>
       <c r="I146" s="4"/>
-      <c r="J146" s="4"/>
+      <c r="J146" s="7"/>
       <c r="K146" s="4"/>
       <c r="L146" s="4"/>
       <c r="M146" s="4"/>
@@ -5000,7 +5165,7 @@
       <c r="G147" s="4"/>
       <c r="H147" s="4"/>
       <c r="I147" s="4"/>
-      <c r="J147" s="4"/>
+      <c r="J147" s="7"/>
       <c r="K147" s="4"/>
       <c r="L147" s="4"/>
       <c r="M147" s="4"/>
@@ -5030,7 +5195,7 @@
       <c r="G148" s="4"/>
       <c r="H148" s="4"/>
       <c r="I148" s="4"/>
-      <c r="J148" s="4"/>
+      <c r="J148" s="7"/>
       <c r="K148" s="4"/>
       <c r="L148" s="4"/>
       <c r="M148" s="4"/>
@@ -5060,7 +5225,7 @@
       <c r="G149" s="4"/>
       <c r="H149" s="4"/>
       <c r="I149" s="4"/>
-      <c r="J149" s="4"/>
+      <c r="J149" s="7"/>
       <c r="K149" s="4"/>
       <c r="L149" s="4"/>
       <c r="M149" s="4"/>
@@ -5090,7 +5255,7 @@
       <c r="G150" s="4"/>
       <c r="H150" s="4"/>
       <c r="I150" s="4"/>
-      <c r="J150" s="4"/>
+      <c r="J150" s="7"/>
       <c r="K150" s="4"/>
       <c r="L150" s="4"/>
       <c r="M150" s="4"/>
@@ -5120,7 +5285,7 @@
       <c r="G151" s="4"/>
       <c r="H151" s="4"/>
       <c r="I151" s="4"/>
-      <c r="J151" s="4"/>
+      <c r="J151" s="7"/>
       <c r="K151" s="4"/>
       <c r="L151" s="4"/>
       <c r="M151" s="4"/>
@@ -5150,7 +5315,7 @@
       <c r="G152" s="4"/>
       <c r="H152" s="4"/>
       <c r="I152" s="4"/>
-      <c r="J152" s="4"/>
+      <c r="J152" s="7"/>
       <c r="K152" s="4"/>
       <c r="L152" s="4"/>
       <c r="M152" s="4"/>
@@ -5180,7 +5345,7 @@
       <c r="G153" s="4"/>
       <c r="H153" s="4"/>
       <c r="I153" s="4"/>
-      <c r="J153" s="4"/>
+      <c r="J153" s="7"/>
       <c r="K153" s="4"/>
       <c r="L153" s="4"/>
       <c r="M153" s="4"/>
@@ -5210,7 +5375,7 @@
       <c r="G154" s="4"/>
       <c r="H154" s="4"/>
       <c r="I154" s="4"/>
-      <c r="J154" s="4"/>
+      <c r="J154" s="7"/>
       <c r="K154" s="4"/>
       <c r="L154" s="4"/>
       <c r="M154" s="4"/>
@@ -5240,7 +5405,7 @@
       <c r="G155" s="4"/>
       <c r="H155" s="4"/>
       <c r="I155" s="4"/>
-      <c r="J155" s="4"/>
+      <c r="J155" s="7"/>
       <c r="K155" s="4"/>
       <c r="L155" s="4"/>
       <c r="M155" s="4"/>
@@ -5270,7 +5435,7 @@
       <c r="G156" s="4"/>
       <c r="H156" s="4"/>
       <c r="I156" s="4"/>
-      <c r="J156" s="4"/>
+      <c r="J156" s="7"/>
       <c r="K156" s="4"/>
       <c r="L156" s="4"/>
       <c r="M156" s="4"/>
@@ -5300,7 +5465,7 @@
       <c r="G157" s="4"/>
       <c r="H157" s="4"/>
       <c r="I157" s="4"/>
-      <c r="J157" s="4"/>
+      <c r="J157" s="7"/>
       <c r="K157" s="4"/>
       <c r="L157" s="4"/>
       <c r="M157" s="4"/>
@@ -5330,7 +5495,7 @@
       <c r="G158" s="4"/>
       <c r="H158" s="4"/>
       <c r="I158" s="4"/>
-      <c r="J158" s="4"/>
+      <c r="J158" s="7"/>
       <c r="K158" s="4"/>
       <c r="L158" s="4"/>
       <c r="M158" s="4"/>
@@ -5360,7 +5525,7 @@
       <c r="G159" s="4"/>
       <c r="H159" s="4"/>
       <c r="I159" s="4"/>
-      <c r="J159" s="4"/>
+      <c r="J159" s="7"/>
       <c r="K159" s="4"/>
       <c r="L159" s="4"/>
       <c r="M159" s="4"/>
@@ -5390,7 +5555,7 @@
       <c r="G160" s="4"/>
       <c r="H160" s="4"/>
       <c r="I160" s="4"/>
-      <c r="J160" s="4"/>
+      <c r="J160" s="7"/>
       <c r="K160" s="4"/>
       <c r="L160" s="4"/>
       <c r="M160" s="4"/>
@@ -5420,7 +5585,7 @@
       <c r="G161" s="4"/>
       <c r="H161" s="4"/>
       <c r="I161" s="4"/>
-      <c r="J161" s="4"/>
+      <c r="J161" s="7"/>
       <c r="K161" s="4"/>
       <c r="L161" s="4"/>
       <c r="M161" s="4"/>
@@ -5450,7 +5615,7 @@
       <c r="G162" s="4"/>
       <c r="H162" s="4"/>
       <c r="I162" s="4"/>
-      <c r="J162" s="4"/>
+      <c r="J162" s="7"/>
       <c r="K162" s="4"/>
       <c r="L162" s="4"/>
       <c r="M162" s="4"/>
@@ -5480,7 +5645,7 @@
       <c r="G163" s="4"/>
       <c r="H163" s="4"/>
       <c r="I163" s="4"/>
-      <c r="J163" s="4"/>
+      <c r="J163" s="7"/>
       <c r="K163" s="4"/>
       <c r="L163" s="4"/>
       <c r="M163" s="4"/>
@@ -5510,7 +5675,7 @@
       <c r="G164" s="4"/>
       <c r="H164" s="4"/>
       <c r="I164" s="4"/>
-      <c r="J164" s="4"/>
+      <c r="J164" s="7"/>
       <c r="K164" s="4"/>
       <c r="L164" s="4"/>
       <c r="M164" s="4"/>
@@ -5540,7 +5705,7 @@
       <c r="G165" s="4"/>
       <c r="H165" s="4"/>
       <c r="I165" s="4"/>
-      <c r="J165" s="4"/>
+      <c r="J165" s="7"/>
       <c r="K165" s="4"/>
       <c r="L165" s="4"/>
       <c r="M165" s="4"/>
@@ -5570,7 +5735,7 @@
       <c r="G166" s="4"/>
       <c r="H166" s="4"/>
       <c r="I166" s="4"/>
-      <c r="J166" s="4"/>
+      <c r="J166" s="7"/>
       <c r="K166" s="4"/>
       <c r="L166" s="4"/>
       <c r="M166" s="4"/>
@@ -5600,7 +5765,7 @@
       <c r="G167" s="4"/>
       <c r="H167" s="4"/>
       <c r="I167" s="4"/>
-      <c r="J167" s="4"/>
+      <c r="J167" s="7"/>
       <c r="K167" s="4"/>
       <c r="L167" s="4"/>
       <c r="M167" s="4"/>
@@ -5630,7 +5795,7 @@
       <c r="G168" s="4"/>
       <c r="H168" s="4"/>
       <c r="I168" s="4"/>
-      <c r="J168" s="4"/>
+      <c r="J168" s="7"/>
       <c r="K168" s="4"/>
       <c r="L168" s="4"/>
       <c r="M168" s="4"/>
@@ -5660,7 +5825,7 @@
       <c r="G169" s="4"/>
       <c r="H169" s="4"/>
       <c r="I169" s="4"/>
-      <c r="J169" s="4"/>
+      <c r="J169" s="7"/>
       <c r="K169" s="4"/>
       <c r="L169" s="4"/>
       <c r="M169" s="4"/>
@@ -5690,7 +5855,7 @@
       <c r="G170" s="4"/>
       <c r="H170" s="4"/>
       <c r="I170" s="4"/>
-      <c r="J170" s="4"/>
+      <c r="J170" s="7"/>
       <c r="K170" s="4"/>
       <c r="L170" s="4"/>
       <c r="M170" s="4"/>
@@ -5720,7 +5885,7 @@
       <c r="G171" s="4"/>
       <c r="H171" s="4"/>
       <c r="I171" s="4"/>
-      <c r="J171" s="4"/>
+      <c r="J171" s="7"/>
       <c r="K171" s="4"/>
       <c r="L171" s="4"/>
       <c r="M171" s="4"/>
@@ -5750,7 +5915,7 @@
       <c r="G172" s="4"/>
       <c r="H172" s="4"/>
       <c r="I172" s="4"/>
-      <c r="J172" s="4"/>
+      <c r="J172" s="7"/>
       <c r="K172" s="4"/>
       <c r="L172" s="4"/>
       <c r="M172" s="4"/>
@@ -5780,7 +5945,7 @@
       <c r="G173" s="4"/>
       <c r="H173" s="4"/>
       <c r="I173" s="4"/>
-      <c r="J173" s="4"/>
+      <c r="J173" s="7"/>
       <c r="K173" s="4"/>
       <c r="L173" s="4"/>
       <c r="M173" s="4"/>
@@ -5810,7 +5975,7 @@
       <c r="G174" s="4"/>
       <c r="H174" s="4"/>
       <c r="I174" s="4"/>
-      <c r="J174" s="4"/>
+      <c r="J174" s="7"/>
       <c r="K174" s="4"/>
       <c r="L174" s="4"/>
       <c r="M174" s="4"/>
@@ -5840,7 +6005,7 @@
       <c r="G175" s="4"/>
       <c r="H175" s="4"/>
       <c r="I175" s="4"/>
-      <c r="J175" s="4"/>
+      <c r="J175" s="7"/>
       <c r="K175" s="4"/>
       <c r="L175" s="4"/>
       <c r="M175" s="4"/>
@@ -5870,7 +6035,7 @@
       <c r="G176" s="4"/>
       <c r="H176" s="4"/>
       <c r="I176" s="4"/>
-      <c r="J176" s="4"/>
+      <c r="J176" s="7"/>
       <c r="K176" s="4"/>
       <c r="L176" s="4"/>
       <c r="M176" s="4"/>
@@ -5900,7 +6065,7 @@
       <c r="G177" s="4"/>
       <c r="H177" s="4"/>
       <c r="I177" s="4"/>
-      <c r="J177" s="4"/>
+      <c r="J177" s="7"/>
       <c r="K177" s="4"/>
       <c r="L177" s="4"/>
       <c r="M177" s="4"/>
@@ -5930,7 +6095,7 @@
       <c r="G178" s="4"/>
       <c r="H178" s="4"/>
       <c r="I178" s="4"/>
-      <c r="J178" s="4"/>
+      <c r="J178" s="7"/>
       <c r="K178" s="4"/>
       <c r="L178" s="4"/>
       <c r="M178" s="4"/>
@@ -5960,7 +6125,7 @@
       <c r="G179" s="4"/>
       <c r="H179" s="4"/>
       <c r="I179" s="4"/>
-      <c r="J179" s="4"/>
+      <c r="J179" s="7"/>
       <c r="K179" s="4"/>
       <c r="L179" s="4"/>
       <c r="M179" s="4"/>
@@ -5990,7 +6155,7 @@
       <c r="G180" s="4"/>
       <c r="H180" s="4"/>
       <c r="I180" s="4"/>
-      <c r="J180" s="4"/>
+      <c r="J180" s="7"/>
       <c r="K180" s="4"/>
       <c r="L180" s="4"/>
       <c r="M180" s="4"/>
@@ -6020,7 +6185,7 @@
       <c r="G181" s="4"/>
       <c r="H181" s="4"/>
       <c r="I181" s="4"/>
-      <c r="J181" s="4"/>
+      <c r="J181" s="7"/>
       <c r="K181" s="4"/>
       <c r="L181" s="4"/>
       <c r="M181" s="4"/>
@@ -6050,7 +6215,7 @@
       <c r="G182" s="4"/>
       <c r="H182" s="4"/>
       <c r="I182" s="4"/>
-      <c r="J182" s="4"/>
+      <c r="J182" s="7"/>
       <c r="K182" s="4"/>
       <c r="L182" s="4"/>
       <c r="M182" s="4"/>
@@ -6080,7 +6245,7 @@
       <c r="G183" s="4"/>
       <c r="H183" s="4"/>
       <c r="I183" s="4"/>
-      <c r="J183" s="4"/>
+      <c r="J183" s="7"/>
       <c r="K183" s="4"/>
       <c r="L183" s="4"/>
       <c r="M183" s="4"/>
@@ -6110,7 +6275,7 @@
       <c r="G184" s="4"/>
       <c r="H184" s="4"/>
       <c r="I184" s="4"/>
-      <c r="J184" s="4"/>
+      <c r="J184" s="7"/>
       <c r="K184" s="4"/>
       <c r="L184" s="4"/>
       <c r="M184" s="4"/>
@@ -6140,7 +6305,7 @@
       <c r="G185" s="4"/>
       <c r="H185" s="4"/>
       <c r="I185" s="4"/>
-      <c r="J185" s="4"/>
+      <c r="J185" s="7"/>
       <c r="K185" s="4"/>
       <c r="L185" s="4"/>
       <c r="M185" s="4"/>
@@ -6170,7 +6335,7 @@
       <c r="G186" s="4"/>
       <c r="H186" s="4"/>
       <c r="I186" s="4"/>
-      <c r="J186" s="4"/>
+      <c r="J186" s="7"/>
       <c r="K186" s="4"/>
       <c r="L186" s="4"/>
       <c r="M186" s="4"/>
@@ -6200,7 +6365,7 @@
       <c r="G187" s="4"/>
       <c r="H187" s="4"/>
       <c r="I187" s="4"/>
-      <c r="J187" s="4"/>
+      <c r="J187" s="7"/>
       <c r="K187" s="4"/>
       <c r="L187" s="4"/>
       <c r="M187" s="4"/>
@@ -6230,7 +6395,7 @@
       <c r="G188" s="4"/>
       <c r="H188" s="4"/>
       <c r="I188" s="4"/>
-      <c r="J188" s="4"/>
+      <c r="J188" s="7"/>
       <c r="K188" s="4"/>
       <c r="L188" s="4"/>
       <c r="M188" s="4"/>
@@ -6260,7 +6425,7 @@
       <c r="G189" s="4"/>
       <c r="H189" s="4"/>
       <c r="I189" s="4"/>
-      <c r="J189" s="4"/>
+      <c r="J189" s="7"/>
       <c r="K189" s="4"/>
       <c r="L189" s="4"/>
       <c r="M189" s="4"/>
@@ -6290,7 +6455,7 @@
       <c r="G190" s="4"/>
       <c r="H190" s="4"/>
       <c r="I190" s="4"/>
-      <c r="J190" s="4"/>
+      <c r="J190" s="7"/>
       <c r="K190" s="4"/>
       <c r="L190" s="4"/>
       <c r="M190" s="4"/>
@@ -6320,7 +6485,7 @@
       <c r="G191" s="4"/>
       <c r="H191" s="4"/>
       <c r="I191" s="4"/>
-      <c r="J191" s="4"/>
+      <c r="J191" s="7"/>
       <c r="K191" s="4"/>
       <c r="L191" s="4"/>
       <c r="M191" s="4"/>
@@ -6350,7 +6515,7 @@
       <c r="G192" s="4"/>
       <c r="H192" s="4"/>
       <c r="I192" s="4"/>
-      <c r="J192" s="4"/>
+      <c r="J192" s="7"/>
       <c r="K192" s="4"/>
       <c r="L192" s="4"/>
       <c r="M192" s="4"/>
@@ -6380,7 +6545,7 @@
       <c r="G193" s="4"/>
       <c r="H193" s="4"/>
       <c r="I193" s="4"/>
-      <c r="J193" s="4"/>
+      <c r="J193" s="7"/>
       <c r="K193" s="4"/>
       <c r="L193" s="4"/>
       <c r="M193" s="4"/>
@@ -6410,7 +6575,7 @@
       <c r="G194" s="4"/>
       <c r="H194" s="4"/>
       <c r="I194" s="4"/>
-      <c r="J194" s="4"/>
+      <c r="J194" s="7"/>
       <c r="K194" s="4"/>
       <c r="L194" s="4"/>
       <c r="M194" s="4"/>
@@ -6440,7 +6605,7 @@
       <c r="G195" s="4"/>
       <c r="H195" s="4"/>
       <c r="I195" s="4"/>
-      <c r="J195" s="4"/>
+      <c r="J195" s="7"/>
       <c r="K195" s="4"/>
       <c r="L195" s="4"/>
       <c r="M195" s="4"/>
@@ -6470,7 +6635,7 @@
       <c r="G196" s="4"/>
       <c r="H196" s="4"/>
       <c r="I196" s="4"/>
-      <c r="J196" s="4"/>
+      <c r="J196" s="7"/>
       <c r="K196" s="4"/>
       <c r="L196" s="4"/>
       <c r="M196" s="4"/>
@@ -6500,7 +6665,7 @@
       <c r="G197" s="4"/>
       <c r="H197" s="4"/>
       <c r="I197" s="4"/>
-      <c r="J197" s="4"/>
+      <c r="J197" s="7"/>
       <c r="K197" s="4"/>
       <c r="L197" s="4"/>
       <c r="M197" s="4"/>
@@ -6530,7 +6695,7 @@
       <c r="G198" s="4"/>
       <c r="H198" s="4"/>
       <c r="I198" s="4"/>
-      <c r="J198" s="4"/>
+      <c r="J198" s="7"/>
       <c r="K198" s="4"/>
       <c r="L198" s="4"/>
       <c r="M198" s="4"/>
@@ -6560,7 +6725,7 @@
       <c r="G199" s="4"/>
       <c r="H199" s="4"/>
       <c r="I199" s="4"/>
-      <c r="J199" s="4"/>
+      <c r="J199" s="7"/>
       <c r="K199" s="4"/>
       <c r="L199" s="4"/>
       <c r="M199" s="4"/>
@@ -6590,7 +6755,7 @@
       <c r="G200" s="4"/>
       <c r="H200" s="4"/>
       <c r="I200" s="4"/>
-      <c r="J200" s="4"/>
+      <c r="J200" s="7"/>
       <c r="K200" s="4"/>
       <c r="L200" s="4"/>
       <c r="M200" s="4"/>
@@ -6620,7 +6785,7 @@
       <c r="G201" s="4"/>
       <c r="H201" s="4"/>
       <c r="I201" s="4"/>
-      <c r="J201" s="4"/>
+      <c r="J201" s="7"/>
       <c r="K201" s="4"/>
       <c r="L201" s="4"/>
       <c r="M201" s="4"/>
@@ -6650,7 +6815,7 @@
       <c r="G202" s="4"/>
       <c r="H202" s="4"/>
       <c r="I202" s="4"/>
-      <c r="J202" s="4"/>
+      <c r="J202" s="7"/>
       <c r="K202" s="4"/>
       <c r="L202" s="4"/>
       <c r="M202" s="4"/>
@@ -6680,7 +6845,7 @@
       <c r="G203" s="4"/>
       <c r="H203" s="4"/>
       <c r="I203" s="4"/>
-      <c r="J203" s="4"/>
+      <c r="J203" s="7"/>
       <c r="K203" s="4"/>
       <c r="L203" s="4"/>
       <c r="M203" s="4"/>
@@ -6710,7 +6875,7 @@
       <c r="G204" s="4"/>
       <c r="H204" s="4"/>
       <c r="I204" s="4"/>
-      <c r="J204" s="4"/>
+      <c r="J204" s="7"/>
       <c r="K204" s="4"/>
       <c r="L204" s="4"/>
       <c r="M204" s="4"/>
@@ -6740,7 +6905,7 @@
       <c r="G205" s="4"/>
       <c r="H205" s="4"/>
       <c r="I205" s="4"/>
-      <c r="J205" s="4"/>
+      <c r="J205" s="7"/>
       <c r="K205" s="4"/>
       <c r="L205" s="4"/>
       <c r="M205" s="4"/>
@@ -6770,7 +6935,7 @@
       <c r="G206" s="4"/>
       <c r="H206" s="4"/>
       <c r="I206" s="4"/>
-      <c r="J206" s="4"/>
+      <c r="J206" s="7"/>
       <c r="K206" s="4"/>
       <c r="L206" s="4"/>
       <c r="M206" s="4"/>
@@ -6800,7 +6965,7 @@
       <c r="G207" s="4"/>
       <c r="H207" s="4"/>
       <c r="I207" s="4"/>
-      <c r="J207" s="4"/>
+      <c r="J207" s="7"/>
       <c r="K207" s="4"/>
       <c r="L207" s="4"/>
       <c r="M207" s="4"/>
@@ -6830,7 +6995,7 @@
       <c r="G208" s="4"/>
       <c r="H208" s="4"/>
       <c r="I208" s="4"/>
-      <c r="J208" s="4"/>
+      <c r="J208" s="7"/>
       <c r="K208" s="4"/>
       <c r="L208" s="4"/>
       <c r="M208" s="4"/>
@@ -6860,7 +7025,7 @@
       <c r="G209" s="4"/>
       <c r="H209" s="4"/>
       <c r="I209" s="4"/>
-      <c r="J209" s="4"/>
+      <c r="J209" s="7"/>
       <c r="K209" s="4"/>
       <c r="L209" s="4"/>
       <c r="M209" s="4"/>
@@ -6890,7 +7055,7 @@
       <c r="G210" s="4"/>
       <c r="H210" s="4"/>
       <c r="I210" s="4"/>
-      <c r="J210" s="4"/>
+      <c r="J210" s="7"/>
       <c r="K210" s="4"/>
       <c r="L210" s="4"/>
       <c r="M210" s="4"/>
@@ -6920,7 +7085,7 @@
       <c r="G211" s="4"/>
       <c r="H211" s="4"/>
       <c r="I211" s="4"/>
-      <c r="J211" s="4"/>
+      <c r="J211" s="7"/>
       <c r="K211" s="4"/>
       <c r="L211" s="4"/>
       <c r="M211" s="4"/>
@@ -6950,7 +7115,7 @@
       <c r="G212" s="4"/>
       <c r="H212" s="4"/>
       <c r="I212" s="4"/>
-      <c r="J212" s="4"/>
+      <c r="J212" s="7"/>
       <c r="K212" s="4"/>
       <c r="L212" s="4"/>
       <c r="M212" s="4"/>
@@ -6980,7 +7145,7 @@
       <c r="G213" s="4"/>
       <c r="H213" s="4"/>
       <c r="I213" s="4"/>
-      <c r="J213" s="4"/>
+      <c r="J213" s="7"/>
       <c r="K213" s="4"/>
       <c r="L213" s="4"/>
       <c r="M213" s="4"/>
@@ -7010,7 +7175,7 @@
       <c r="G214" s="4"/>
       <c r="H214" s="4"/>
       <c r="I214" s="4"/>
-      <c r="J214" s="4"/>
+      <c r="J214" s="7"/>
       <c r="K214" s="4"/>
       <c r="L214" s="4"/>
       <c r="M214" s="4"/>
@@ -7040,7 +7205,7 @@
       <c r="G215" s="4"/>
       <c r="H215" s="4"/>
       <c r="I215" s="4"/>
-      <c r="J215" s="4"/>
+      <c r="J215" s="7"/>
       <c r="K215" s="4"/>
       <c r="L215" s="4"/>
       <c r="M215" s="4"/>
@@ -7070,7 +7235,7 @@
       <c r="G216" s="4"/>
       <c r="H216" s="4"/>
       <c r="I216" s="4"/>
-      <c r="J216" s="4"/>
+      <c r="J216" s="7"/>
       <c r="K216" s="4"/>
       <c r="L216" s="4"/>
       <c r="M216" s="4"/>
@@ -7100,7 +7265,7 @@
       <c r="G217" s="4"/>
       <c r="H217" s="4"/>
       <c r="I217" s="4"/>
-      <c r="J217" s="4"/>
+      <c r="J217" s="7"/>
       <c r="K217" s="4"/>
       <c r="L217" s="4"/>
       <c r="M217" s="4"/>
@@ -7130,7 +7295,7 @@
       <c r="G218" s="4"/>
       <c r="H218" s="4"/>
       <c r="I218" s="4"/>
-      <c r="J218" s="4"/>
+      <c r="J218" s="7"/>
       <c r="K218" s="4"/>
       <c r="L218" s="4"/>
       <c r="M218" s="4"/>
@@ -7160,7 +7325,7 @@
       <c r="G219" s="4"/>
       <c r="H219" s="4"/>
       <c r="I219" s="4"/>
-      <c r="J219" s="4"/>
+      <c r="J219" s="7"/>
       <c r="K219" s="4"/>
       <c r="L219" s="4"/>
       <c r="M219" s="4"/>
@@ -7190,7 +7355,7 @@
       <c r="G220" s="4"/>
       <c r="H220" s="4"/>
       <c r="I220" s="4"/>
-      <c r="J220" s="4"/>
+      <c r="J220" s="7"/>
       <c r="K220" s="4"/>
       <c r="L220" s="4"/>
       <c r="M220" s="4"/>
@@ -7220,7 +7385,7 @@
       <c r="G221" s="4"/>
       <c r="H221" s="4"/>
       <c r="I221" s="4"/>
-      <c r="J221" s="4"/>
+      <c r="J221" s="7"/>
       <c r="K221" s="4"/>
       <c r="L221" s="4"/>
       <c r="M221" s="4"/>
@@ -7250,7 +7415,7 @@
       <c r="G222" s="4"/>
       <c r="H222" s="4"/>
       <c r="I222" s="4"/>
-      <c r="J222" s="4"/>
+      <c r="J222" s="7"/>
       <c r="K222" s="4"/>
       <c r="L222" s="4"/>
       <c r="M222" s="4"/>
@@ -7280,7 +7445,7 @@
       <c r="G223" s="4"/>
       <c r="H223" s="4"/>
       <c r="I223" s="4"/>
-      <c r="J223" s="4"/>
+      <c r="J223" s="7"/>
       <c r="K223" s="4"/>
       <c r="L223" s="4"/>
       <c r="M223" s="4"/>
@@ -7310,7 +7475,7 @@
       <c r="G224" s="4"/>
       <c r="H224" s="4"/>
       <c r="I224" s="4"/>
-      <c r="J224" s="4"/>
+      <c r="J224" s="7"/>
       <c r="K224" s="4"/>
       <c r="L224" s="4"/>
       <c r="M224" s="4"/>
@@ -7340,7 +7505,7 @@
       <c r="G225" s="4"/>
       <c r="H225" s="4"/>
       <c r="I225" s="4"/>
-      <c r="J225" s="4"/>
+      <c r="J225" s="7"/>
       <c r="K225" s="4"/>
       <c r="L225" s="4"/>
       <c r="M225" s="4"/>
@@ -7370,7 +7535,7 @@
       <c r="G226" s="4"/>
       <c r="H226" s="4"/>
       <c r="I226" s="4"/>
-      <c r="J226" s="4"/>
+      <c r="J226" s="7"/>
       <c r="K226" s="4"/>
       <c r="L226" s="4"/>
       <c r="M226" s="4"/>
@@ -7400,7 +7565,7 @@
       <c r="G227" s="4"/>
       <c r="H227" s="4"/>
       <c r="I227" s="4"/>
-      <c r="J227" s="4"/>
+      <c r="J227" s="7"/>
       <c r="K227" s="4"/>
       <c r="L227" s="4"/>
       <c r="M227" s="4"/>
@@ -7430,7 +7595,7 @@
       <c r="G228" s="4"/>
       <c r="H228" s="4"/>
       <c r="I228" s="4"/>
-      <c r="J228" s="4"/>
+      <c r="J228" s="7"/>
       <c r="K228" s="4"/>
       <c r="L228" s="4"/>
       <c r="M228" s="4"/>
@@ -7460,7 +7625,7 @@
       <c r="G229" s="4"/>
       <c r="H229" s="4"/>
       <c r="I229" s="4"/>
-      <c r="J229" s="4"/>
+      <c r="J229" s="7"/>
       <c r="K229" s="4"/>
       <c r="L229" s="4"/>
       <c r="M229" s="4"/>
@@ -7490,7 +7655,7 @@
       <c r="G230" s="4"/>
       <c r="H230" s="4"/>
       <c r="I230" s="4"/>
-      <c r="J230" s="4"/>
+      <c r="J230" s="7"/>
       <c r="K230" s="4"/>
       <c r="L230" s="4"/>
       <c r="M230" s="4"/>
@@ -7520,7 +7685,7 @@
       <c r="G231" s="4"/>
       <c r="H231" s="4"/>
       <c r="I231" s="4"/>
-      <c r="J231" s="4"/>
+      <c r="J231" s="7"/>
       <c r="K231" s="4"/>
       <c r="L231" s="4"/>
       <c r="M231" s="4"/>
@@ -7550,7 +7715,7 @@
       <c r="G232" s="4"/>
       <c r="H232" s="4"/>
       <c r="I232" s="4"/>
-      <c r="J232" s="4"/>
+      <c r="J232" s="7"/>
       <c r="K232" s="4"/>
       <c r="L232" s="4"/>
       <c r="M232" s="4"/>
@@ -7580,7 +7745,7 @@
       <c r="G233" s="4"/>
       <c r="H233" s="4"/>
       <c r="I233" s="4"/>
-      <c r="J233" s="4"/>
+      <c r="J233" s="7"/>
       <c r="K233" s="4"/>
       <c r="L233" s="4"/>
       <c r="M233" s="4"/>
@@ -7610,7 +7775,7 @@
       <c r="G234" s="4"/>
       <c r="H234" s="4"/>
       <c r="I234" s="4"/>
-      <c r="J234" s="4"/>
+      <c r="J234" s="7"/>
       <c r="K234" s="4"/>
       <c r="L234" s="4"/>
       <c r="M234" s="4"/>
@@ -7640,7 +7805,7 @@
       <c r="G235" s="4"/>
       <c r="H235" s="4"/>
       <c r="I235" s="4"/>
-      <c r="J235" s="4"/>
+      <c r="J235" s="7"/>
       <c r="K235" s="4"/>
       <c r="L235" s="4"/>
       <c r="M235" s="4"/>
@@ -7670,7 +7835,7 @@
       <c r="G236" s="4"/>
       <c r="H236" s="4"/>
       <c r="I236" s="4"/>
-      <c r="J236" s="4"/>
+      <c r="J236" s="7"/>
       <c r="K236" s="4"/>
       <c r="L236" s="4"/>
       <c r="M236" s="4"/>
@@ -7700,7 +7865,7 @@
       <c r="G237" s="4"/>
       <c r="H237" s="4"/>
       <c r="I237" s="4"/>
-      <c r="J237" s="4"/>
+      <c r="J237" s="7"/>
       <c r="K237" s="4"/>
       <c r="L237" s="4"/>
       <c r="M237" s="4"/>
@@ -7730,7 +7895,7 @@
       <c r="G238" s="4"/>
       <c r="H238" s="4"/>
       <c r="I238" s="4"/>
-      <c r="J238" s="4"/>
+      <c r="J238" s="7"/>
       <c r="K238" s="4"/>
       <c r="L238" s="4"/>
       <c r="M238" s="4"/>
@@ -7760,7 +7925,7 @@
       <c r="G239" s="4"/>
       <c r="H239" s="4"/>
       <c r="I239" s="4"/>
-      <c r="J239" s="4"/>
+      <c r="J239" s="7"/>
       <c r="K239" s="4"/>
       <c r="L239" s="4"/>
       <c r="M239" s="4"/>
@@ -7790,7 +7955,7 @@
       <c r="G240" s="4"/>
       <c r="H240" s="4"/>
       <c r="I240" s="4"/>
-      <c r="J240" s="4"/>
+      <c r="J240" s="7"/>
       <c r="K240" s="4"/>
       <c r="L240" s="4"/>
       <c r="M240" s="4"/>
@@ -7820,7 +7985,7 @@
       <c r="G241" s="4"/>
       <c r="H241" s="4"/>
       <c r="I241" s="4"/>
-      <c r="J241" s="4"/>
+      <c r="J241" s="7"/>
       <c r="K241" s="4"/>
       <c r="L241" s="4"/>
       <c r="M241" s="4"/>
@@ -7850,7 +8015,7 @@
       <c r="G242" s="4"/>
       <c r="H242" s="4"/>
       <c r="I242" s="4"/>
-      <c r="J242" s="4"/>
+      <c r="J242" s="7"/>
       <c r="K242" s="4"/>
       <c r="L242" s="4"/>
       <c r="M242" s="4"/>
@@ -7880,7 +8045,7 @@
       <c r="G243" s="4"/>
       <c r="H243" s="4"/>
       <c r="I243" s="4"/>
-      <c r="J243" s="4"/>
+      <c r="J243" s="7"/>
       <c r="K243" s="4"/>
       <c r="L243" s="4"/>
       <c r="M243" s="4"/>
@@ -7910,7 +8075,7 @@
       <c r="G244" s="4"/>
       <c r="H244" s="4"/>
       <c r="I244" s="4"/>
-      <c r="J244" s="4"/>
+      <c r="J244" s="7"/>
       <c r="K244" s="4"/>
       <c r="L244" s="4"/>
       <c r="M244" s="4"/>
@@ -7940,7 +8105,7 @@
       <c r="G245" s="4"/>
       <c r="H245" s="4"/>
       <c r="I245" s="4"/>
-      <c r="J245" s="4"/>
+      <c r="J245" s="7"/>
       <c r="K245" s="4"/>
       <c r="L245" s="4"/>
       <c r="M245" s="4"/>
@@ -7970,7 +8135,7 @@
       <c r="G246" s="4"/>
       <c r="H246" s="4"/>
       <c r="I246" s="4"/>
-      <c r="J246" s="4"/>
+      <c r="J246" s="7"/>
       <c r="K246" s="4"/>
       <c r="L246" s="4"/>
       <c r="M246" s="4"/>
@@ -8000,7 +8165,7 @@
       <c r="G247" s="4"/>
       <c r="H247" s="4"/>
       <c r="I247" s="4"/>
-      <c r="J247" s="4"/>
+      <c r="J247" s="7"/>
       <c r="K247" s="4"/>
       <c r="L247" s="4"/>
       <c r="M247" s="4"/>
@@ -8030,7 +8195,7 @@
       <c r="G248" s="4"/>
       <c r="H248" s="4"/>
       <c r="I248" s="4"/>
-      <c r="J248" s="4"/>
+      <c r="J248" s="7"/>
       <c r="K248" s="4"/>
       <c r="L248" s="4"/>
       <c r="M248" s="4"/>
@@ -8060,7 +8225,7 @@
       <c r="G249" s="4"/>
       <c r="H249" s="4"/>
       <c r="I249" s="4"/>
-      <c r="J249" s="4"/>
+      <c r="J249" s="7"/>
       <c r="K249" s="4"/>
       <c r="L249" s="4"/>
       <c r="M249" s="4"/>
@@ -8090,7 +8255,7 @@
       <c r="G250" s="4"/>
       <c r="H250" s="4"/>
       <c r="I250" s="4"/>
-      <c r="J250" s="4"/>
+      <c r="J250" s="7"/>
       <c r="K250" s="4"/>
       <c r="L250" s="4"/>
       <c r="M250" s="4"/>
@@ -8120,7 +8285,7 @@
       <c r="G251" s="4"/>
       <c r="H251" s="4"/>
       <c r="I251" s="4"/>
-      <c r="J251" s="4"/>
+      <c r="J251" s="7"/>
       <c r="K251" s="4"/>
       <c r="L251" s="4"/>
       <c r="M251" s="4"/>
@@ -8150,7 +8315,7 @@
       <c r="G252" s="4"/>
       <c r="H252" s="4"/>
       <c r="I252" s="4"/>
-      <c r="J252" s="4"/>
+      <c r="J252" s="7"/>
       <c r="K252" s="4"/>
       <c r="L252" s="4"/>
       <c r="M252" s="4"/>
@@ -8180,7 +8345,7 @@
       <c r="G253" s="4"/>
       <c r="H253" s="4"/>
       <c r="I253" s="4"/>
-      <c r="J253" s="4"/>
+      <c r="J253" s="7"/>
       <c r="K253" s="4"/>
       <c r="L253" s="4"/>
       <c r="M253" s="4"/>
@@ -8210,7 +8375,7 @@
       <c r="G254" s="4"/>
       <c r="H254" s="4"/>
       <c r="I254" s="4"/>
-      <c r="J254" s="4"/>
+      <c r="J254" s="7"/>
       <c r="K254" s="4"/>
       <c r="L254" s="4"/>
       <c r="M254" s="4"/>
@@ -8240,7 +8405,7 @@
       <c r="G255" s="4"/>
       <c r="H255" s="4"/>
       <c r="I255" s="4"/>
-      <c r="J255" s="4"/>
+      <c r="J255" s="7"/>
       <c r="K255" s="4"/>
       <c r="L255" s="4"/>
       <c r="M255" s="4"/>
@@ -8270,7 +8435,7 @@
       <c r="G256" s="4"/>
       <c r="H256" s="4"/>
       <c r="I256" s="4"/>
-      <c r="J256" s="4"/>
+      <c r="J256" s="7"/>
       <c r="K256" s="4"/>
       <c r="L256" s="4"/>
       <c r="M256" s="4"/>
@@ -8300,7 +8465,7 @@
       <c r="G257" s="4"/>
       <c r="H257" s="4"/>
       <c r="I257" s="4"/>
-      <c r="J257" s="4"/>
+      <c r="J257" s="7"/>
       <c r="K257" s="4"/>
       <c r="L257" s="4"/>
       <c r="M257" s="4"/>
@@ -8330,7 +8495,7 @@
       <c r="G258" s="4"/>
       <c r="H258" s="4"/>
       <c r="I258" s="4"/>
-      <c r="J258" s="4"/>
+      <c r="J258" s="7"/>
       <c r="K258" s="4"/>
       <c r="L258" s="4"/>
       <c r="M258" s="4"/>
@@ -8360,7 +8525,7 @@
       <c r="G259" s="4"/>
       <c r="H259" s="4"/>
       <c r="I259" s="4"/>
-      <c r="J259" s="4"/>
+      <c r="J259" s="7"/>
       <c r="K259" s="4"/>
       <c r="L259" s="4"/>
       <c r="M259" s="4"/>
@@ -8390,7 +8555,7 @@
       <c r="G260" s="4"/>
       <c r="H260" s="4"/>
       <c r="I260" s="4"/>
-      <c r="J260" s="4"/>
+      <c r="J260" s="7"/>
       <c r="K260" s="4"/>
       <c r="L260" s="4"/>
       <c r="M260" s="4"/>
@@ -8420,7 +8585,7 @@
       <c r="G261" s="4"/>
       <c r="H261" s="4"/>
       <c r="I261" s="4"/>
-      <c r="J261" s="4"/>
+      <c r="J261" s="7"/>
       <c r="K261" s="4"/>
       <c r="L261" s="4"/>
       <c r="M261" s="4"/>
@@ -8450,7 +8615,7 @@
       <c r="G262" s="4"/>
       <c r="H262" s="4"/>
       <c r="I262" s="4"/>
-      <c r="J262" s="4"/>
+      <c r="J262" s="7"/>
       <c r="K262" s="4"/>
       <c r="L262" s="4"/>
       <c r="M262" s="4"/>
@@ -8480,7 +8645,7 @@
       <c r="G263" s="4"/>
       <c r="H263" s="4"/>
       <c r="I263" s="4"/>
-      <c r="J263" s="4"/>
+      <c r="J263" s="7"/>
       <c r="K263" s="4"/>
       <c r="L263" s="4"/>
       <c r="M263" s="4"/>
@@ -8510,7 +8675,7 @@
       <c r="G264" s="4"/>
       <c r="H264" s="4"/>
       <c r="I264" s="4"/>
-      <c r="J264" s="4"/>
+      <c r="J264" s="7"/>
       <c r="K264" s="4"/>
       <c r="L264" s="4"/>
       <c r="M264" s="4"/>
@@ -8540,7 +8705,7 @@
       <c r="G265" s="4"/>
       <c r="H265" s="4"/>
       <c r="I265" s="4"/>
-      <c r="J265" s="4"/>
+      <c r="J265" s="7"/>
       <c r="K265" s="4"/>
       <c r="L265" s="4"/>
       <c r="M265" s="4"/>
@@ -8570,7 +8735,7 @@
       <c r="G266" s="4"/>
       <c r="H266" s="4"/>
       <c r="I266" s="4"/>
-      <c r="J266" s="4"/>
+      <c r="J266" s="7"/>
       <c r="K266" s="4"/>
       <c r="L266" s="4"/>
       <c r="M266" s="4"/>
@@ -8600,7 +8765,7 @@
       <c r="G267" s="4"/>
       <c r="H267" s="4"/>
       <c r="I267" s="4"/>
-      <c r="J267" s="4"/>
+      <c r="J267" s="7"/>
       <c r="K267" s="4"/>
       <c r="L267" s="4"/>
       <c r="M267" s="4"/>
@@ -8630,7 +8795,7 @@
       <c r="G268" s="4"/>
       <c r="H268" s="4"/>
       <c r="I268" s="4"/>
-      <c r="J268" s="4"/>
+      <c r="J268" s="7"/>
       <c r="K268" s="4"/>
       <c r="L268" s="4"/>
       <c r="M268" s="4"/>
@@ -8660,7 +8825,7 @@
       <c r="G269" s="4"/>
       <c r="H269" s="4"/>
       <c r="I269" s="4"/>
-      <c r="J269" s="4"/>
+      <c r="J269" s="7"/>
       <c r="K269" s="4"/>
       <c r="L269" s="4"/>
       <c r="M269" s="4"/>
@@ -8690,7 +8855,7 @@
       <c r="G270" s="4"/>
       <c r="H270" s="4"/>
       <c r="I270" s="4"/>
-      <c r="J270" s="4"/>
+      <c r="J270" s="7"/>
       <c r="K270" s="4"/>
       <c r="L270" s="4"/>
       <c r="M270" s="4"/>
@@ -8720,7 +8885,7 @@
       <c r="G271" s="4"/>
       <c r="H271" s="4"/>
       <c r="I271" s="4"/>
-      <c r="J271" s="4"/>
+      <c r="J271" s="7"/>
       <c r="K271" s="4"/>
       <c r="L271" s="4"/>
       <c r="M271" s="4"/>
@@ -8750,7 +8915,7 @@
       <c r="G272" s="4"/>
       <c r="H272" s="4"/>
       <c r="I272" s="4"/>
-      <c r="J272" s="4"/>
+      <c r="J272" s="7"/>
       <c r="K272" s="4"/>
       <c r="L272" s="4"/>
       <c r="M272" s="4"/>
@@ -8780,7 +8945,7 @@
       <c r="G273" s="4"/>
       <c r="H273" s="4"/>
       <c r="I273" s="4"/>
-      <c r="J273" s="4"/>
+      <c r="J273" s="7"/>
       <c r="K273" s="4"/>
       <c r="L273" s="4"/>
       <c r="M273" s="4"/>
@@ -8810,7 +8975,7 @@
       <c r="G274" s="4"/>
       <c r="H274" s="4"/>
       <c r="I274" s="4"/>
-      <c r="J274" s="4"/>
+      <c r="J274" s="7"/>
       <c r="K274" s="4"/>
       <c r="L274" s="4"/>
       <c r="M274" s="4"/>
@@ -8840,7 +9005,7 @@
       <c r="G275" s="4"/>
       <c r="H275" s="4"/>
       <c r="I275" s="4"/>
-      <c r="J275" s="4"/>
+      <c r="J275" s="7"/>
       <c r="K275" s="4"/>
       <c r="L275" s="4"/>
       <c r="M275" s="4"/>
@@ -8870,7 +9035,7 @@
       <c r="G276" s="4"/>
       <c r="H276" s="4"/>
       <c r="I276" s="4"/>
-      <c r="J276" s="4"/>
+      <c r="J276" s="7"/>
       <c r="K276" s="4"/>
       <c r="L276" s="4"/>
       <c r="M276" s="4"/>
@@ -8900,7 +9065,7 @@
       <c r="G277" s="4"/>
       <c r="H277" s="4"/>
       <c r="I277" s="4"/>
-      <c r="J277" s="4"/>
+      <c r="J277" s="7"/>
       <c r="K277" s="4"/>
       <c r="L277" s="4"/>
       <c r="M277" s="4"/>
@@ -8930,7 +9095,7 @@
       <c r="G278" s="4"/>
       <c r="H278" s="4"/>
       <c r="I278" s="4"/>
-      <c r="J278" s="4"/>
+      <c r="J278" s="7"/>
       <c r="K278" s="4"/>
       <c r="L278" s="4"/>
       <c r="M278" s="4"/>
@@ -8960,7 +9125,7 @@
       <c r="G279" s="4"/>
       <c r="H279" s="4"/>
       <c r="I279" s="4"/>
-      <c r="J279" s="4"/>
+      <c r="J279" s="7"/>
       <c r="K279" s="4"/>
       <c r="L279" s="4"/>
       <c r="M279" s="4"/>
@@ -8990,7 +9155,7 @@
       <c r="G280" s="4"/>
       <c r="H280" s="4"/>
       <c r="I280" s="4"/>
-      <c r="J280" s="4"/>
+      <c r="J280" s="7"/>
       <c r="K280" s="4"/>
       <c r="L280" s="4"/>
       <c r="M280" s="4"/>
@@ -9020,7 +9185,7 @@
       <c r="G281" s="4"/>
       <c r="H281" s="4"/>
       <c r="I281" s="4"/>
-      <c r="J281" s="4"/>
+      <c r="J281" s="7"/>
       <c r="K281" s="4"/>
       <c r="L281" s="4"/>
       <c r="M281" s="4"/>
@@ -9050,7 +9215,7 @@
       <c r="G282" s="4"/>
       <c r="H282" s="4"/>
       <c r="I282" s="4"/>
-      <c r="J282" s="4"/>
+      <c r="J282" s="7"/>
       <c r="K282" s="4"/>
       <c r="L282" s="4"/>
       <c r="M282" s="4"/>
@@ -9080,7 +9245,7 @@
       <c r="G283" s="4"/>
       <c r="H283" s="4"/>
       <c r="I283" s="4"/>
-      <c r="J283" s="4"/>
+      <c r="J283" s="7"/>
       <c r="K283" s="4"/>
       <c r="L283" s="4"/>
       <c r="M283" s="4"/>
@@ -9110,7 +9275,7 @@
       <c r="G284" s="4"/>
       <c r="H284" s="4"/>
       <c r="I284" s="4"/>
-      <c r="J284" s="4"/>
+      <c r="J284" s="7"/>
       <c r="K284" s="4"/>
       <c r="L284" s="4"/>
       <c r="M284" s="4"/>
@@ -9140,7 +9305,7 @@
       <c r="G285" s="4"/>
       <c r="H285" s="4"/>
       <c r="I285" s="4"/>
-      <c r="J285" s="4"/>
+      <c r="J285" s="7"/>
       <c r="K285" s="4"/>
       <c r="L285" s="4"/>
       <c r="M285" s="4"/>
@@ -9170,7 +9335,7 @@
       <c r="G286" s="4"/>
       <c r="H286" s="4"/>
       <c r="I286" s="4"/>
-      <c r="J286" s="4"/>
+      <c r="J286" s="7"/>
       <c r="K286" s="4"/>
       <c r="L286" s="4"/>
       <c r="M286" s="4"/>
@@ -9200,7 +9365,7 @@
       <c r="G287" s="4"/>
       <c r="H287" s="4"/>
       <c r="I287" s="4"/>
-      <c r="J287" s="4"/>
+      <c r="J287" s="7"/>
       <c r="K287" s="4"/>
       <c r="L287" s="4"/>
       <c r="M287" s="4"/>
@@ -9230,7 +9395,7 @@
       <c r="G288" s="4"/>
       <c r="H288" s="4"/>
       <c r="I288" s="4"/>
-      <c r="J288" s="4"/>
+      <c r="J288" s="7"/>
       <c r="K288" s="4"/>
       <c r="L288" s="4"/>
       <c r="M288" s="4"/>
@@ -9260,7 +9425,7 @@
       <c r="G289" s="4"/>
       <c r="H289" s="4"/>
       <c r="I289" s="4"/>
-      <c r="J289" s="4"/>
+      <c r="J289" s="7"/>
       <c r="K289" s="4"/>
       <c r="L289" s="4"/>
       <c r="M289" s="4"/>
@@ -9290,7 +9455,7 @@
       <c r="G290" s="4"/>
       <c r="H290" s="4"/>
       <c r="I290" s="4"/>
-      <c r="J290" s="4"/>
+      <c r="J290" s="7"/>
       <c r="K290" s="4"/>
       <c r="L290" s="4"/>
       <c r="M290" s="4"/>
@@ -9320,7 +9485,7 @@
       <c r="G291" s="4"/>
       <c r="H291" s="4"/>
       <c r="I291" s="4"/>
-      <c r="J291" s="4"/>
+      <c r="J291" s="7"/>
       <c r="K291" s="4"/>
       <c r="L291" s="4"/>
       <c r="M291" s="4"/>
@@ -9350,7 +9515,7 @@
       <c r="G292" s="4"/>
       <c r="H292" s="4"/>
       <c r="I292" s="4"/>
-      <c r="J292" s="4"/>
+      <c r="J292" s="7"/>
       <c r="K292" s="4"/>
       <c r="L292" s="4"/>
       <c r="M292" s="4"/>
@@ -9380,7 +9545,7 @@
       <c r="G293" s="4"/>
       <c r="H293" s="4"/>
       <c r="I293" s="4"/>
-      <c r="J293" s="4"/>
+      <c r="J293" s="7"/>
       <c r="K293" s="4"/>
       <c r="L293" s="4"/>
       <c r="M293" s="4"/>
@@ -9410,7 +9575,7 @@
       <c r="G294" s="4"/>
       <c r="H294" s="4"/>
       <c r="I294" s="4"/>
-      <c r="J294" s="4"/>
+      <c r="J294" s="7"/>
       <c r="K294" s="4"/>
       <c r="L294" s="4"/>
       <c r="M294" s="4"/>
@@ -9440,7 +9605,7 @@
       <c r="G295" s="4"/>
       <c r="H295" s="4"/>
       <c r="I295" s="4"/>
-      <c r="J295" s="4"/>
+      <c r="J295" s="7"/>
       <c r="K295" s="4"/>
       <c r="L295" s="4"/>
       <c r="M295" s="4"/>
@@ -9470,7 +9635,7 @@
       <c r="G296" s="4"/>
       <c r="H296" s="4"/>
       <c r="I296" s="4"/>
-      <c r="J296" s="4"/>
+      <c r="J296" s="7"/>
       <c r="K296" s="4"/>
       <c r="L296" s="4"/>
       <c r="M296" s="4"/>
@@ -9500,7 +9665,7 @@
       <c r="G297" s="4"/>
       <c r="H297" s="4"/>
       <c r="I297" s="4"/>
-      <c r="J297" s="4"/>
+      <c r="J297" s="7"/>
       <c r="K297" s="4"/>
       <c r="L297" s="4"/>
       <c r="M297" s="4"/>
@@ -9530,7 +9695,7 @@
       <c r="G298" s="4"/>
       <c r="H298" s="4"/>
       <c r="I298" s="4"/>
-      <c r="J298" s="4"/>
+      <c r="J298" s="7"/>
       <c r="K298" s="4"/>
       <c r="L298" s="4"/>
       <c r="M298" s="4"/>
@@ -9560,7 +9725,7 @@
       <c r="G299" s="4"/>
       <c r="H299" s="4"/>
       <c r="I299" s="4"/>
-      <c r="J299" s="4"/>
+      <c r="J299" s="7"/>
       <c r="K299" s="4"/>
       <c r="L299" s="4"/>
       <c r="M299" s="4"/>
@@ -9590,7 +9755,7 @@
       <c r="G300" s="4"/>
       <c r="H300" s="4"/>
       <c r="I300" s="4"/>
-      <c r="J300" s="4"/>
+      <c r="J300" s="7"/>
       <c r="K300" s="4"/>
       <c r="L300" s="4"/>
       <c r="M300" s="4"/>
@@ -9620,7 +9785,7 @@
       <c r="G301" s="4"/>
       <c r="H301" s="4"/>
       <c r="I301" s="4"/>
-      <c r="J301" s="4"/>
+      <c r="J301" s="7"/>
       <c r="K301" s="4"/>
       <c r="L301" s="4"/>
       <c r="M301" s="4"/>
@@ -9650,7 +9815,7 @@
       <c r="G302" s="4"/>
       <c r="H302" s="4"/>
       <c r="I302" s="4"/>
-      <c r="J302" s="4"/>
+      <c r="J302" s="7"/>
       <c r="K302" s="4"/>
       <c r="L302" s="4"/>
       <c r="M302" s="4"/>
@@ -9680,7 +9845,7 @@
       <c r="G303" s="4"/>
       <c r="H303" s="4"/>
       <c r="I303" s="4"/>
-      <c r="J303" s="4"/>
+      <c r="J303" s="7"/>
       <c r="K303" s="4"/>
       <c r="L303" s="4"/>
       <c r="M303" s="4"/>
@@ -9710,7 +9875,7 @@
       <c r="G304" s="4"/>
       <c r="H304" s="4"/>
       <c r="I304" s="4"/>
-      <c r="J304" s="4"/>
+      <c r="J304" s="7"/>
       <c r="K304" s="4"/>
       <c r="L304" s="4"/>
       <c r="M304" s="4"/>
@@ -9740,7 +9905,7 @@
       <c r="G305" s="4"/>
       <c r="H305" s="4"/>
       <c r="I305" s="4"/>
-      <c r="J305" s="4"/>
+      <c r="J305" s="7"/>
       <c r="K305" s="4"/>
       <c r="L305" s="4"/>
       <c r="M305" s="4"/>
@@ -9770,7 +9935,7 @@
       <c r="G306" s="4"/>
       <c r="H306" s="4"/>
       <c r="I306" s="4"/>
-      <c r="J306" s="4"/>
+      <c r="J306" s="7"/>
       <c r="K306" s="4"/>
       <c r="L306" s="4"/>
       <c r="M306" s="4"/>
@@ -9800,7 +9965,7 @@
       <c r="G307" s="4"/>
       <c r="H307" s="4"/>
       <c r="I307" s="4"/>
-      <c r="J307" s="4"/>
+      <c r="J307" s="7"/>
       <c r="K307" s="4"/>
       <c r="L307" s="4"/>
       <c r="M307" s="4"/>
@@ -9830,7 +9995,7 @@
       <c r="G308" s="4"/>
       <c r="H308" s="4"/>
       <c r="I308" s="4"/>
-      <c r="J308" s="4"/>
+      <c r="J308" s="7"/>
       <c r="K308" s="4"/>
       <c r="L308" s="4"/>
       <c r="M308" s="4"/>
@@ -9860,7 +10025,7 @@
       <c r="G309" s="4"/>
       <c r="H309" s="4"/>
       <c r="I309" s="4"/>
-      <c r="J309" s="4"/>
+      <c r="J309" s="7"/>
       <c r="K309" s="4"/>
       <c r="L309" s="4"/>
       <c r="M309" s="4"/>
@@ -9890,7 +10055,7 @@
       <c r="G310" s="4"/>
       <c r="H310" s="4"/>
       <c r="I310" s="4"/>
-      <c r="J310" s="4"/>
+      <c r="J310" s="7"/>
       <c r="K310" s="4"/>
       <c r="L310" s="4"/>
       <c r="M310" s="4"/>
@@ -9920,7 +10085,7 @@
       <c r="G311" s="4"/>
       <c r="H311" s="4"/>
       <c r="I311" s="4"/>
-      <c r="J311" s="4"/>
+      <c r="J311" s="7"/>
       <c r="K311" s="4"/>
       <c r="L311" s="4"/>
       <c r="M311" s="4"/>
@@ -9950,7 +10115,7 @@
       <c r="G312" s="4"/>
       <c r="H312" s="4"/>
       <c r="I312" s="4"/>
-      <c r="J312" s="4"/>
+      <c r="J312" s="7"/>
       <c r="K312" s="4"/>
       <c r="L312" s="4"/>
       <c r="M312" s="4"/>
@@ -9980,7 +10145,7 @@
       <c r="G313" s="4"/>
       <c r="H313" s="4"/>
       <c r="I313" s="4"/>
-      <c r="J313" s="4"/>
+      <c r="J313" s="7"/>
       <c r="K313" s="4"/>
       <c r="L313" s="4"/>
       <c r="M313" s="4"/>
@@ -10010,7 +10175,7 @@
       <c r="G314" s="4"/>
       <c r="H314" s="4"/>
       <c r="I314" s="4"/>
-      <c r="J314" s="4"/>
+      <c r="J314" s="7"/>
       <c r="K314" s="4"/>
       <c r="L314" s="4"/>
       <c r="M314" s="4"/>
@@ -10040,7 +10205,7 @@
       <c r="G315" s="4"/>
       <c r="H315" s="4"/>
       <c r="I315" s="4"/>
-      <c r="J315" s="4"/>
+      <c r="J315" s="7"/>
       <c r="K315" s="4"/>
       <c r="L315" s="4"/>
       <c r="M315" s="4"/>
@@ -10070,7 +10235,7 @@
       <c r="G316" s="4"/>
       <c r="H316" s="4"/>
       <c r="I316" s="4"/>
-      <c r="J316" s="4"/>
+      <c r="J316" s="7"/>
       <c r="K316" s="4"/>
       <c r="L316" s="4"/>
       <c r="M316" s="4"/>
@@ -10100,7 +10265,7 @@
       <c r="G317" s="4"/>
       <c r="H317" s="4"/>
       <c r="I317" s="4"/>
-      <c r="J317" s="4"/>
+      <c r="J317" s="7"/>
       <c r="K317" s="4"/>
       <c r="L317" s="4"/>
       <c r="M317" s="4"/>
@@ -10130,7 +10295,7 @@
       <c r="G318" s="4"/>
       <c r="H318" s="4"/>
       <c r="I318" s="4"/>
-      <c r="J318" s="4"/>
+      <c r="J318" s="7"/>
       <c r="K318" s="4"/>
       <c r="L318" s="4"/>
       <c r="M318" s="4"/>
@@ -10160,7 +10325,7 @@
       <c r="G319" s="4"/>
       <c r="H319" s="4"/>
       <c r="I319" s="4"/>
-      <c r="J319" s="4"/>
+      <c r="J319" s="7"/>
       <c r="K319" s="4"/>
       <c r="L319" s="4"/>
       <c r="M319" s="4"/>
@@ -10190,7 +10355,7 @@
       <c r="G320" s="4"/>
       <c r="H320" s="4"/>
       <c r="I320" s="4"/>
-      <c r="J320" s="4"/>
+      <c r="J320" s="7"/>
       <c r="K320" s="4"/>
       <c r="L320" s="4"/>
       <c r="M320" s="4"/>
@@ -10220,7 +10385,7 @@
       <c r="G321" s="4"/>
       <c r="H321" s="4"/>
       <c r="I321" s="4"/>
-      <c r="J321" s="4"/>
+      <c r="J321" s="7"/>
       <c r="K321" s="4"/>
       <c r="L321" s="4"/>
       <c r="M321" s="4"/>
@@ -10250,7 +10415,7 @@
       <c r="G322" s="4"/>
       <c r="H322" s="4"/>
       <c r="I322" s="4"/>
-      <c r="J322" s="4"/>
+      <c r="J322" s="7"/>
       <c r="K322" s="4"/>
       <c r="L322" s="4"/>
       <c r="M322" s="4"/>
@@ -10280,7 +10445,7 @@
       <c r="G323" s="4"/>
       <c r="H323" s="4"/>
       <c r="I323" s="4"/>
-      <c r="J323" s="4"/>
+      <c r="J323" s="7"/>
       <c r="K323" s="4"/>
       <c r="L323" s="4"/>
       <c r="M323" s="4"/>
@@ -10310,7 +10475,7 @@
       <c r="G324" s="4"/>
       <c r="H324" s="4"/>
       <c r="I324" s="4"/>
-      <c r="J324" s="4"/>
+      <c r="J324" s="7"/>
       <c r="K324" s="4"/>
       <c r="L324" s="4"/>
       <c r="M324" s="4"/>
@@ -10340,7 +10505,7 @@
       <c r="G325" s="4"/>
       <c r="H325" s="4"/>
       <c r="I325" s="4"/>
-      <c r="J325" s="4"/>
+      <c r="J325" s="7"/>
       <c r="K325" s="4"/>
       <c r="L325" s="4"/>
       <c r="M325" s="4"/>
@@ -10370,7 +10535,7 @@
       <c r="G326" s="4"/>
       <c r="H326" s="4"/>
       <c r="I326" s="4"/>
-      <c r="J326" s="4"/>
+      <c r="J326" s="7"/>
       <c r="K326" s="4"/>
       <c r="L326" s="4"/>
       <c r="M326" s="4"/>
@@ -10400,7 +10565,7 @@
       <c r="G327" s="4"/>
       <c r="H327" s="4"/>
       <c r="I327" s="4"/>
-      <c r="J327" s="4"/>
+      <c r="J327" s="7"/>
       <c r="K327" s="4"/>
       <c r="L327" s="4"/>
       <c r="M327" s="4"/>
@@ -10430,7 +10595,7 @@
       <c r="G328" s="4"/>
       <c r="H328" s="4"/>
       <c r="I328" s="4"/>
-      <c r="J328" s="4"/>
+      <c r="J328" s="7"/>
       <c r="K328" s="4"/>
       <c r="L328" s="4"/>
       <c r="M328" s="4"/>
@@ -10460,7 +10625,7 @@
       <c r="G329" s="4"/>
       <c r="H329" s="4"/>
       <c r="I329" s="4"/>
-      <c r="J329" s="4"/>
+      <c r="J329" s="7"/>
       <c r="K329" s="4"/>
       <c r="L329" s="4"/>
       <c r="M329" s="4"/>
@@ -10490,7 +10655,7 @@
       <c r="G330" s="4"/>
       <c r="H330" s="4"/>
       <c r="I330" s="4"/>
-      <c r="J330" s="4"/>
+      <c r="J330" s="7"/>
       <c r="K330" s="4"/>
       <c r="L330" s="4"/>
       <c r="M330" s="4"/>
@@ -10520,7 +10685,7 @@
       <c r="G331" s="4"/>
       <c r="H331" s="4"/>
       <c r="I331" s="4"/>
-      <c r="J331" s="4"/>
+      <c r="J331" s="7"/>
       <c r="K331" s="4"/>
       <c r="L331" s="4"/>
       <c r="M331" s="4"/>
@@ -10550,7 +10715,7 @@
       <c r="G332" s="4"/>
       <c r="H332" s="4"/>
       <c r="I332" s="4"/>
-      <c r="J332" s="4"/>
+      <c r="J332" s="7"/>
       <c r="K332" s="4"/>
       <c r="L332" s="4"/>
       <c r="M332" s="4"/>
@@ -10580,7 +10745,7 @@
       <c r="G333" s="4"/>
       <c r="H333" s="4"/>
       <c r="I333" s="4"/>
-      <c r="J333" s="4"/>
+      <c r="J333" s="7"/>
       <c r="K333" s="4"/>
       <c r="L333" s="4"/>
       <c r="M333" s="4"/>
@@ -10610,7 +10775,7 @@
       <c r="G334" s="4"/>
       <c r="H334" s="4"/>
       <c r="I334" s="4"/>
-      <c r="J334" s="4"/>
+      <c r="J334" s="7"/>
       <c r="K334" s="4"/>
       <c r="L334" s="4"/>
       <c r="M334" s="4"/>
@@ -10640,7 +10805,7 @@
       <c r="G335" s="4"/>
       <c r="H335" s="4"/>
       <c r="I335" s="4"/>
-      <c r="J335" s="4"/>
+      <c r="J335" s="7"/>
       <c r="K335" s="4"/>
       <c r="L335" s="4"/>
       <c r="M335" s="4"/>
@@ -10670,7 +10835,7 @@
       <c r="G336" s="4"/>
       <c r="H336" s="4"/>
       <c r="I336" s="4"/>
-      <c r="J336" s="4"/>
+      <c r="J336" s="7"/>
       <c r="K336" s="4"/>
       <c r="L336" s="4"/>
       <c r="M336" s="4"/>
@@ -10700,7 +10865,7 @@
       <c r="G337" s="4"/>
       <c r="H337" s="4"/>
       <c r="I337" s="4"/>
-      <c r="J337" s="4"/>
+      <c r="J337" s="7"/>
       <c r="K337" s="4"/>
       <c r="L337" s="4"/>
       <c r="M337" s="4"/>
@@ -10730,7 +10895,7 @@
       <c r="G338" s="4"/>
       <c r="H338" s="4"/>
       <c r="I338" s="4"/>
-      <c r="J338" s="4"/>
+      <c r="J338" s="7"/>
       <c r="K338" s="4"/>
       <c r="L338" s="4"/>
       <c r="M338" s="4"/>
@@ -10760,7 +10925,7 @@
       <c r="G339" s="4"/>
       <c r="H339" s="4"/>
       <c r="I339" s="4"/>
-      <c r="J339" s="4"/>
+      <c r="J339" s="7"/>
       <c r="K339" s="4"/>
       <c r="L339" s="4"/>
       <c r="M339" s="4"/>
@@ -10790,7 +10955,7 @@
       <c r="G340" s="4"/>
       <c r="H340" s="4"/>
       <c r="I340" s="4"/>
-      <c r="J340" s="4"/>
+      <c r="J340" s="7"/>
       <c r="K340" s="4"/>
       <c r="L340" s="4"/>
       <c r="M340" s="4"/>
@@ -10820,7 +10985,7 @@
       <c r="G341" s="4"/>
       <c r="H341" s="4"/>
       <c r="I341" s="4"/>
-      <c r="J341" s="4"/>
+      <c r="J341" s="7"/>
       <c r="K341" s="4"/>
       <c r="L341" s="4"/>
       <c r="M341" s="4"/>
@@ -10850,7 +11015,7 @@
       <c r="G342" s="4"/>
       <c r="H342" s="4"/>
       <c r="I342" s="4"/>
-      <c r="J342" s="4"/>
+      <c r="J342" s="7"/>
       <c r="K342" s="4"/>
       <c r="L342" s="4"/>
       <c r="M342" s="4"/>
@@ -10880,7 +11045,7 @@
       <c r="G343" s="4"/>
       <c r="H343" s="4"/>
       <c r="I343" s="4"/>
-      <c r="J343" s="4"/>
+      <c r="J343" s="7"/>
       <c r="K343" s="4"/>
       <c r="L343" s="4"/>
       <c r="M343" s="4"/>
@@ -10910,7 +11075,7 @@
       <c r="G344" s="4"/>
       <c r="H344" s="4"/>
       <c r="I344" s="4"/>
-      <c r="J344" s="4"/>
+      <c r="J344" s="7"/>
       <c r="K344" s="4"/>
       <c r="L344" s="4"/>
       <c r="M344" s="4"/>
@@ -10940,7 +11105,7 @@
       <c r="G345" s="4"/>
       <c r="H345" s="4"/>
       <c r="I345" s="4"/>
-      <c r="J345" s="4"/>
+      <c r="J345" s="7"/>
       <c r="K345" s="4"/>
       <c r="L345" s="4"/>
       <c r="M345" s="4"/>
@@ -10970,7 +11135,7 @@
       <c r="G346" s="4"/>
       <c r="H346" s="4"/>
       <c r="I346" s="4"/>
-      <c r="J346" s="4"/>
+      <c r="J346" s="7"/>
       <c r="K346" s="4"/>
       <c r="L346" s="4"/>
       <c r="M346" s="4"/>
@@ -11000,7 +11165,7 @@
       <c r="G347" s="4"/>
       <c r="H347" s="4"/>
       <c r="I347" s="4"/>
-      <c r="J347" s="4"/>
+      <c r="J347" s="7"/>
       <c r="K347" s="4"/>
       <c r="L347" s="4"/>
       <c r="M347" s="4"/>
@@ -11030,7 +11195,7 @@
       <c r="G348" s="4"/>
       <c r="H348" s="4"/>
       <c r="I348" s="4"/>
-      <c r="J348" s="4"/>
+      <c r="J348" s="7"/>
       <c r="K348" s="4"/>
       <c r="L348" s="4"/>
       <c r="M348" s="4"/>
@@ -11060,7 +11225,7 @@
       <c r="G349" s="4"/>
       <c r="H349" s="4"/>
       <c r="I349" s="4"/>
-      <c r="J349" s="4"/>
+      <c r="J349" s="7"/>
       <c r="K349" s="4"/>
       <c r="L349" s="4"/>
       <c r="M349" s="4"/>
@@ -11090,7 +11255,7 @@
       <c r="G350" s="4"/>
       <c r="H350" s="4"/>
       <c r="I350" s="4"/>
-      <c r="J350" s="4"/>
+      <c r="J350" s="7"/>
       <c r="K350" s="4"/>
       <c r="L350" s="4"/>
       <c r="M350" s="4"/>
@@ -11120,7 +11285,7 @@
       <c r="G351" s="4"/>
       <c r="H351" s="4"/>
       <c r="I351" s="4"/>
-      <c r="J351" s="4"/>
+      <c r="J351" s="7"/>
       <c r="K351" s="4"/>
       <c r="L351" s="4"/>
       <c r="M351" s="4"/>
@@ -11150,7 +11315,7 @@
       <c r="G352" s="4"/>
       <c r="H352" s="4"/>
       <c r="I352" s="4"/>
-      <c r="J352" s="4"/>
+      <c r="J352" s="7"/>
       <c r="K352" s="4"/>
       <c r="L352" s="4"/>
       <c r="M352" s="4"/>
@@ -11180,7 +11345,7 @@
       <c r="G353" s="4"/>
       <c r="H353" s="4"/>
       <c r="I353" s="4"/>
-      <c r="J353" s="4"/>
+      <c r="J353" s="7"/>
       <c r="K353" s="4"/>
       <c r="L353" s="4"/>
       <c r="M353" s="4"/>
@@ -11210,7 +11375,7 @@
       <c r="G354" s="4"/>
       <c r="H354" s="4"/>
       <c r="I354" s="4"/>
-      <c r="J354" s="4"/>
+      <c r="J354" s="7"/>
       <c r="K354" s="4"/>
       <c r="L354" s="4"/>
       <c r="M354" s="4"/>
@@ -11240,7 +11405,7 @@
       <c r="G355" s="4"/>
       <c r="H355" s="4"/>
       <c r="I355" s="4"/>
-      <c r="J355" s="4"/>
+      <c r="J355" s="7"/>
       <c r="K355" s="4"/>
       <c r="L355" s="4"/>
       <c r="M355" s="4"/>
@@ -11270,7 +11435,7 @@
       <c r="G356" s="4"/>
       <c r="H356" s="4"/>
       <c r="I356" s="4"/>
-      <c r="J356" s="4"/>
+      <c r="J356" s="7"/>
       <c r="K356" s="4"/>
       <c r="L356" s="4"/>
       <c r="M356" s="4"/>
@@ -11300,7 +11465,7 @@
       <c r="G357" s="4"/>
       <c r="H357" s="4"/>
       <c r="I357" s="4"/>
-      <c r="J357" s="4"/>
+      <c r="J357" s="7"/>
       <c r="K357" s="4"/>
       <c r="L357" s="4"/>
       <c r="M357" s="4"/>
@@ -11330,7 +11495,7 @@
       <c r="G358" s="4"/>
       <c r="H358" s="4"/>
       <c r="I358" s="4"/>
-      <c r="J358" s="4"/>
+      <c r="J358" s="7"/>
       <c r="K358" s="4"/>
       <c r="L358" s="4"/>
       <c r="M358" s="4"/>
@@ -11360,7 +11525,7 @@
       <c r="G359" s="4"/>
       <c r="H359" s="4"/>
       <c r="I359" s="4"/>
-      <c r="J359" s="4"/>
+      <c r="J359" s="7"/>
       <c r="K359" s="4"/>
       <c r="L359" s="4"/>
       <c r="M359" s="4"/>
@@ -11390,7 +11555,7 @@
       <c r="G360" s="4"/>
       <c r="H360" s="4"/>
       <c r="I360" s="4"/>
-      <c r="J360" s="4"/>
+      <c r="J360" s="7"/>
       <c r="K360" s="4"/>
       <c r="L360" s="4"/>
       <c r="M360" s="4"/>
@@ -11420,7 +11585,7 @@
       <c r="G361" s="4"/>
       <c r="H361" s="4"/>
       <c r="I361" s="4"/>
-      <c r="J361" s="4"/>
+      <c r="J361" s="7"/>
       <c r="K361" s="4"/>
       <c r="L361" s="4"/>
       <c r="M361" s="4"/>
@@ -11450,7 +11615,7 @@
       <c r="G362" s="4"/>
       <c r="H362" s="4"/>
       <c r="I362" s="4"/>
-      <c r="J362" s="4"/>
+      <c r="J362" s="7"/>
       <c r="K362" s="4"/>
       <c r="L362" s="4"/>
       <c r="M362" s="4"/>
@@ -11480,7 +11645,7 @@
       <c r="G363" s="4"/>
       <c r="H363" s="4"/>
       <c r="I363" s="4"/>
-      <c r="J363" s="4"/>
+      <c r="J363" s="7"/>
       <c r="K363" s="4"/>
       <c r="L363" s="4"/>
       <c r="M363" s="4"/>
@@ -11510,7 +11675,7 @@
       <c r="G364" s="4"/>
       <c r="H364" s="4"/>
       <c r="I364" s="4"/>
-      <c r="J364" s="4"/>
+      <c r="J364" s="7"/>
       <c r="K364" s="4"/>
       <c r="L364" s="4"/>
       <c r="M364" s="4"/>
@@ -11540,7 +11705,7 @@
       <c r="G365" s="4"/>
       <c r="H365" s="4"/>
       <c r="I365" s="4"/>
-      <c r="J365" s="4"/>
+      <c r="J365" s="7"/>
       <c r="K365" s="4"/>
       <c r="L365" s="4"/>
       <c r="M365" s="4"/>
@@ -11570,7 +11735,7 @@
       <c r="G366" s="4"/>
       <c r="H366" s="4"/>
       <c r="I366" s="4"/>
-      <c r="J366" s="4"/>
+      <c r="J366" s="7"/>
       <c r="K366" s="4"/>
       <c r="L366" s="4"/>
       <c r="M366" s="4"/>
@@ -11600,7 +11765,7 @@
       <c r="G367" s="4"/>
       <c r="H367" s="4"/>
       <c r="I367" s="4"/>
-      <c r="J367" s="4"/>
+      <c r="J367" s="7"/>
       <c r="K367" s="4"/>
       <c r="L367" s="4"/>
       <c r="M367" s="4"/>
@@ -11630,7 +11795,7 @@
       <c r="G368" s="4"/>
       <c r="H368" s="4"/>
       <c r="I368" s="4"/>
-      <c r="J368" s="4"/>
+      <c r="J368" s="7"/>
       <c r="K368" s="4"/>
       <c r="L368" s="4"/>
       <c r="M368" s="4"/>
@@ -11660,7 +11825,7 @@
       <c r="G369" s="4"/>
       <c r="H369" s="4"/>
       <c r="I369" s="4"/>
-      <c r="J369" s="4"/>
+      <c r="J369" s="7"/>
       <c r="K369" s="4"/>
       <c r="L369" s="4"/>
       <c r="M369" s="4"/>
@@ -11690,7 +11855,7 @@
       <c r="G370" s="4"/>
       <c r="H370" s="4"/>
       <c r="I370" s="4"/>
-      <c r="J370" s="4"/>
+      <c r="J370" s="7"/>
       <c r="K370" s="4"/>
       <c r="L370" s="4"/>
       <c r="M370" s="4"/>
@@ -11720,7 +11885,7 @@
       <c r="G371" s="4"/>
       <c r="H371" s="4"/>
       <c r="I371" s="4"/>
-      <c r="J371" s="4"/>
+      <c r="J371" s="7"/>
       <c r="K371" s="4"/>
       <c r="L371" s="4"/>
       <c r="M371" s="4"/>
@@ -11750,7 +11915,7 @@
       <c r="G372" s="4"/>
       <c r="H372" s="4"/>
       <c r="I372" s="4"/>
-      <c r="J372" s="4"/>
+      <c r="J372" s="7"/>
       <c r="K372" s="4"/>
       <c r="L372" s="4"/>
       <c r="M372" s="4"/>
@@ -11780,7 +11945,7 @@
       <c r="G373" s="4"/>
       <c r="H373" s="4"/>
       <c r="I373" s="4"/>
-      <c r="J373" s="4"/>
+      <c r="J373" s="7"/>
       <c r="K373" s="4"/>
       <c r="L373" s="4"/>
       <c r="M373" s="4"/>
@@ -11810,7 +11975,7 @@
       <c r="G374" s="4"/>
       <c r="H374" s="4"/>
       <c r="I374" s="4"/>
-      <c r="J374" s="4"/>
+      <c r="J374" s="7"/>
       <c r="K374" s="4"/>
       <c r="L374" s="4"/>
       <c r="M374" s="4"/>
@@ -11840,7 +12005,7 @@
       <c r="G375" s="4"/>
       <c r="H375" s="4"/>
       <c r="I375" s="4"/>
-      <c r="J375" s="4"/>
+      <c r="J375" s="7"/>
       <c r="K375" s="4"/>
       <c r="L375" s="4"/>
       <c r="M375" s="4"/>
@@ -11870,7 +12035,7 @@
       <c r="G376" s="4"/>
       <c r="H376" s="4"/>
       <c r="I376" s="4"/>
-      <c r="J376" s="4"/>
+      <c r="J376" s="7"/>
       <c r="K376" s="4"/>
       <c r="L376" s="4"/>
       <c r="M376" s="4"/>
@@ -11900,7 +12065,7 @@
       <c r="G377" s="4"/>
       <c r="H377" s="4"/>
       <c r="I377" s="4"/>
-      <c r="J377" s="4"/>
+      <c r="J377" s="7"/>
       <c r="K377" s="4"/>
       <c r="L377" s="4"/>
       <c r="M377" s="4"/>
@@ -11930,7 +12095,7 @@
       <c r="G378" s="4"/>
       <c r="H378" s="4"/>
       <c r="I378" s="4"/>
-      <c r="J378" s="4"/>
+      <c r="J378" s="7"/>
       <c r="K378" s="4"/>
       <c r="L378" s="4"/>
       <c r="M378" s="4"/>
@@ -11960,7 +12125,7 @@
       <c r="G379" s="4"/>
       <c r="H379" s="4"/>
       <c r="I379" s="4"/>
-      <c r="J379" s="4"/>
+      <c r="J379" s="7"/>
       <c r="K379" s="4"/>
       <c r="L379" s="4"/>
       <c r="M379" s="4"/>
@@ -11990,7 +12155,7 @@
       <c r="G380" s="4"/>
       <c r="H380" s="4"/>
       <c r="I380" s="4"/>
-      <c r="J380" s="4"/>
+      <c r="J380" s="7"/>
       <c r="K380" s="4"/>
       <c r="L380" s="4"/>
       <c r="M380" s="4"/>
@@ -12020,7 +12185,7 @@
       <c r="G381" s="4"/>
       <c r="H381" s="4"/>
       <c r="I381" s="4"/>
-      <c r="J381" s="4"/>
+      <c r="J381" s="7"/>
       <c r="K381" s="4"/>
       <c r="L381" s="4"/>
       <c r="M381" s="4"/>
@@ -12050,7 +12215,7 @@
       <c r="G382" s="4"/>
       <c r="H382" s="4"/>
       <c r="I382" s="4"/>
-      <c r="J382" s="4"/>
+      <c r="J382" s="7"/>
       <c r="K382" s="4"/>
       <c r="L382" s="4"/>
       <c r="M382" s="4"/>
@@ -12080,7 +12245,7 @@
       <c r="G383" s="4"/>
       <c r="H383" s="4"/>
       <c r="I383" s="4"/>
-      <c r="J383" s="4"/>
+      <c r="J383" s="7"/>
       <c r="K383" s="4"/>
       <c r="L383" s="4"/>
       <c r="M383" s="4"/>
@@ -12110,7 +12275,7 @@
       <c r="G384" s="4"/>
       <c r="H384" s="4"/>
       <c r="I384" s="4"/>
-      <c r="J384" s="4"/>
+      <c r="J384" s="7"/>
       <c r="K384" s="4"/>
       <c r="L384" s="4"/>
       <c r="M384" s="4"/>
@@ -12140,7 +12305,7 @@
       <c r="G385" s="4"/>
       <c r="H385" s="4"/>
       <c r="I385" s="4"/>
-      <c r="J385" s="4"/>
+      <c r="J385" s="7"/>
       <c r="K385" s="4"/>
       <c r="L385" s="4"/>
       <c r="M385" s="4"/>
@@ -12170,7 +12335,7 @@
       <c r="G386" s="4"/>
       <c r="H386" s="4"/>
       <c r="I386" s="4"/>
-      <c r="J386" s="4"/>
+      <c r="J386" s="7"/>
       <c r="K386" s="4"/>
       <c r="L386" s="4"/>
       <c r="M386" s="4"/>
@@ -12200,7 +12365,7 @@
       <c r="G387" s="4"/>
       <c r="H387" s="4"/>
       <c r="I387" s="4"/>
-      <c r="J387" s="4"/>
+      <c r="J387" s="7"/>
       <c r="K387" s="4"/>
       <c r="L387" s="4"/>
       <c r="M387" s="4"/>
@@ -12230,7 +12395,7 @@
       <c r="G388" s="4"/>
       <c r="H388" s="4"/>
       <c r="I388" s="4"/>
-      <c r="J388" s="4"/>
+      <c r="J388" s="7"/>
       <c r="K388" s="4"/>
       <c r="L388" s="4"/>
       <c r="M388" s="4"/>
@@ -12260,7 +12425,7 @@
       <c r="G389" s="4"/>
       <c r="H389" s="4"/>
       <c r="I389" s="4"/>
-      <c r="J389" s="4"/>
+      <c r="J389" s="7"/>
       <c r="K389" s="4"/>
       <c r="L389" s="4"/>
       <c r="M389" s="4"/>
@@ -12290,7 +12455,7 @@
       <c r="G390" s="4"/>
       <c r="H390" s="4"/>
       <c r="I390" s="4"/>
-      <c r="J390" s="4"/>
+      <c r="J390" s="7"/>
       <c r="K390" s="4"/>
       <c r="L390" s="4"/>
       <c r="M390" s="4"/>
@@ -12320,7 +12485,7 @@
       <c r="G391" s="4"/>
       <c r="H391" s="4"/>
       <c r="I391" s="4"/>
-      <c r="J391" s="4"/>
+      <c r="J391" s="7"/>
       <c r="K391" s="4"/>
       <c r="L391" s="4"/>
       <c r="M391" s="4"/>
@@ -12350,7 +12515,7 @@
       <c r="G392" s="4"/>
       <c r="H392" s="4"/>
       <c r="I392" s="4"/>
-      <c r="J392" s="4"/>
+      <c r="J392" s="7"/>
       <c r="K392" s="4"/>
       <c r="L392" s="4"/>
       <c r="M392" s="4"/>
@@ -12380,7 +12545,7 @@
       <c r="G393" s="4"/>
       <c r="H393" s="4"/>
       <c r="I393" s="4"/>
-      <c r="J393" s="4"/>
+      <c r="J393" s="7"/>
       <c r="K393" s="4"/>
       <c r="L393" s="4"/>
       <c r="M393" s="4"/>
@@ -12410,7 +12575,7 @@
       <c r="G394" s="4"/>
       <c r="H394" s="4"/>
       <c r="I394" s="4"/>
-      <c r="J394" s="4"/>
+      <c r="J394" s="7"/>
       <c r="K394" s="4"/>
       <c r="L394" s="4"/>
       <c r="M394" s="4"/>
@@ -12440,7 +12605,7 @@
       <c r="G395" s="4"/>
       <c r="H395" s="4"/>
       <c r="I395" s="4"/>
-      <c r="J395" s="4"/>
+      <c r="J395" s="7"/>
       <c r="K395" s="4"/>
       <c r="L395" s="4"/>
       <c r="M395" s="4"/>
@@ -12470,7 +12635,7 @@
       <c r="G396" s="4"/>
       <c r="H396" s="4"/>
       <c r="I396" s="4"/>
-      <c r="J396" s="4"/>
+      <c r="J396" s="7"/>
       <c r="K396" s="4"/>
       <c r="L396" s="4"/>
       <c r="M396" s="4"/>
@@ -12500,7 +12665,7 @@
       <c r="G397" s="4"/>
       <c r="H397" s="4"/>
       <c r="I397" s="4"/>
-      <c r="J397" s="4"/>
+      <c r="J397" s="7"/>
       <c r="K397" s="4"/>
       <c r="L397" s="4"/>
       <c r="M397" s="4"/>
@@ -12530,7 +12695,7 @@
       <c r="G398" s="4"/>
       <c r="H398" s="4"/>
       <c r="I398" s="4"/>
-      <c r="J398" s="4"/>
+      <c r="J398" s="7"/>
       <c r="K398" s="4"/>
       <c r="L398" s="4"/>
       <c r="M398" s="4"/>
@@ -12560,7 +12725,7 @@
       <c r="G399" s="4"/>
       <c r="H399" s="4"/>
       <c r="I399" s="4"/>
-      <c r="J399" s="4"/>
+      <c r="J399" s="7"/>
       <c r="K399" s="4"/>
       <c r="L399" s="4"/>
       <c r="M399" s="4"/>
@@ -12590,7 +12755,7 @@
       <c r="G400" s="4"/>
       <c r="H400" s="4"/>
       <c r="I400" s="4"/>
-      <c r="J400" s="4"/>
+      <c r="J400" s="7"/>
       <c r="K400" s="4"/>
       <c r="L400" s="4"/>
       <c r="M400" s="4"/>
@@ -12620,7 +12785,7 @@
       <c r="G401" s="4"/>
       <c r="H401" s="4"/>
       <c r="I401" s="4"/>
-      <c r="J401" s="4"/>
+      <c r="J401" s="7"/>
       <c r="K401" s="4"/>
       <c r="L401" s="4"/>
       <c r="M401" s="4"/>
@@ -12650,7 +12815,7 @@
       <c r="G402" s="4"/>
       <c r="H402" s="4"/>
       <c r="I402" s="4"/>
-      <c r="J402" s="4"/>
+      <c r="J402" s="7"/>
       <c r="K402" s="4"/>
       <c r="L402" s="4"/>
       <c r="M402" s="4"/>
@@ -12680,7 +12845,7 @@
       <c r="G403" s="4"/>
       <c r="H403" s="4"/>
       <c r="I403" s="4"/>
-      <c r="J403" s="4"/>
+      <c r="J403" s="7"/>
       <c r="K403" s="4"/>
       <c r="L403" s="4"/>
       <c r="M403" s="4"/>
@@ -12710,7 +12875,7 @@
       <c r="G404" s="4"/>
       <c r="H404" s="4"/>
       <c r="I404" s="4"/>
-      <c r="J404" s="4"/>
+      <c r="J404" s="7"/>
       <c r="K404" s="4"/>
       <c r="L404" s="4"/>
       <c r="M404" s="4"/>
@@ -12740,7 +12905,7 @@
       <c r="G405" s="4"/>
       <c r="H405" s="4"/>
       <c r="I405" s="4"/>
-      <c r="J405" s="4"/>
+      <c r="J405" s="7"/>
       <c r="K405" s="4"/>
       <c r="L405" s="4"/>
       <c r="M405" s="4"/>
@@ -12770,7 +12935,7 @@
       <c r="G406" s="4"/>
       <c r="H406" s="4"/>
       <c r="I406" s="4"/>
-      <c r="J406" s="4"/>
+      <c r="J406" s="7"/>
       <c r="K406" s="4"/>
       <c r="L406" s="4"/>
       <c r="M406" s="4"/>
@@ -12800,7 +12965,7 @@
       <c r="G407" s="4"/>
       <c r="H407" s="4"/>
       <c r="I407" s="4"/>
-      <c r="J407" s="4"/>
+      <c r="J407" s="7"/>
       <c r="K407" s="4"/>
       <c r="L407" s="4"/>
       <c r="M407" s="4"/>
@@ -12830,7 +12995,7 @@
       <c r="G408" s="4"/>
       <c r="H408" s="4"/>
       <c r="I408" s="4"/>
-      <c r="J408" s="4"/>
+      <c r="J408" s="7"/>
       <c r="K408" s="4"/>
       <c r="L408" s="4"/>
       <c r="M408" s="4"/>
@@ -12860,7 +13025,7 @@
       <c r="G409" s="4"/>
       <c r="H409" s="4"/>
       <c r="I409" s="4"/>
-      <c r="J409" s="4"/>
+      <c r="J409" s="7"/>
       <c r="K409" s="4"/>
       <c r="L409" s="4"/>
       <c r="M409" s="4"/>
@@ -12890,7 +13055,7 @@
       <c r="G410" s="4"/>
       <c r="H410" s="4"/>
       <c r="I410" s="4"/>
-      <c r="J410" s="4"/>
+      <c r="J410" s="7"/>
       <c r="K410" s="4"/>
       <c r="L410" s="4"/>
       <c r="M410" s="4"/>
@@ -12920,7 +13085,7 @@
       <c r="G411" s="4"/>
       <c r="H411" s="4"/>
       <c r="I411" s="4"/>
-      <c r="J411" s="4"/>
+      <c r="J411" s="7"/>
       <c r="K411" s="4"/>
       <c r="L411" s="4"/>
       <c r="M411" s="4"/>
@@ -12950,7 +13115,7 @@
       <c r="G412" s="4"/>
       <c r="H412" s="4"/>
       <c r="I412" s="4"/>
-      <c r="J412" s="4"/>
+      <c r="J412" s="7"/>
       <c r="K412" s="4"/>
       <c r="L412" s="4"/>
       <c r="M412" s="4"/>
@@ -12980,7 +13145,7 @@
       <c r="G413" s="4"/>
       <c r="H413" s="4"/>
       <c r="I413" s="4"/>
-      <c r="J413" s="4"/>
+      <c r="J413" s="7"/>
       <c r="K413" s="4"/>
       <c r="L413" s="4"/>
       <c r="M413" s="4"/>
@@ -13010,7 +13175,7 @@
       <c r="G414" s="4"/>
       <c r="H414" s="4"/>
       <c r="I414" s="4"/>
-      <c r="J414" s="4"/>
+      <c r="J414" s="7"/>
       <c r="K414" s="4"/>
       <c r="L414" s="4"/>
       <c r="M414" s="4"/>
@@ -13040,7 +13205,7 @@
       <c r="G415" s="4"/>
       <c r="H415" s="4"/>
       <c r="I415" s="4"/>
-      <c r="J415" s="4"/>
+      <c r="J415" s="7"/>
       <c r="K415" s="4"/>
       <c r="L415" s="4"/>
       <c r="M415" s="4"/>
@@ -13070,7 +13235,7 @@
       <c r="G416" s="4"/>
       <c r="H416" s="4"/>
       <c r="I416" s="4"/>
-      <c r="J416" s="4"/>
+      <c r="J416" s="7"/>
       <c r="K416" s="4"/>
       <c r="L416" s="4"/>
       <c r="M416" s="4"/>
@@ -13100,7 +13265,7 @@
       <c r="G417" s="4"/>
       <c r="H417" s="4"/>
       <c r="I417" s="4"/>
-      <c r="J417" s="4"/>
+      <c r="J417" s="7"/>
       <c r="K417" s="4"/>
       <c r="L417" s="4"/>
       <c r="M417" s="4"/>
@@ -13130,7 +13295,7 @@
       <c r="G418" s="4"/>
       <c r="H418" s="4"/>
       <c r="I418" s="4"/>
-      <c r="J418" s="4"/>
+      <c r="J418" s="7"/>
       <c r="K418" s="4"/>
       <c r="L418" s="4"/>
       <c r="M418" s="4"/>
@@ -13160,7 +13325,7 @@
       <c r="G419" s="4"/>
       <c r="H419" s="4"/>
       <c r="I419" s="4"/>
-      <c r="J419" s="4"/>
+      <c r="J419" s="7"/>
       <c r="K419" s="4"/>
       <c r="L419" s="4"/>
       <c r="M419" s="4"/>
@@ -13190,7 +13355,7 @@
       <c r="G420" s="4"/>
       <c r="H420" s="4"/>
       <c r="I420" s="4"/>
-      <c r="J420" s="4"/>
+      <c r="J420" s="7"/>
       <c r="K420" s="4"/>
       <c r="L420" s="4"/>
       <c r="M420" s="4"/>
@@ -13220,7 +13385,7 @@
       <c r="G421" s="4"/>
       <c r="H421" s="4"/>
       <c r="I421" s="4"/>
-      <c r="J421" s="4"/>
+      <c r="J421" s="7"/>
       <c r="K421" s="4"/>
       <c r="L421" s="4"/>
       <c r="M421" s="4"/>
@@ -13250,7 +13415,7 @@
       <c r="G422" s="4"/>
       <c r="H422" s="4"/>
       <c r="I422" s="4"/>
-      <c r="J422" s="4"/>
+      <c r="J422" s="7"/>
       <c r="K422" s="4"/>
       <c r="L422" s="4"/>
       <c r="M422" s="4"/>
@@ -13280,7 +13445,7 @@
       <c r="G423" s="4"/>
       <c r="H423" s="4"/>
       <c r="I423" s="4"/>
-      <c r="J423" s="4"/>
+      <c r="J423" s="7"/>
       <c r="K423" s="4"/>
       <c r="L423" s="4"/>
       <c r="M423" s="4"/>
@@ -13310,7 +13475,7 @@
       <c r="G424" s="4"/>
       <c r="H424" s="4"/>
       <c r="I424" s="4"/>
-      <c r="J424" s="4"/>
+      <c r="J424" s="7"/>
       <c r="K424" s="4"/>
       <c r="L424" s="4"/>
       <c r="M424" s="4"/>
@@ -13340,7 +13505,7 @@
       <c r="G425" s="4"/>
       <c r="H425" s="4"/>
       <c r="I425" s="4"/>
-      <c r="J425" s="4"/>
+      <c r="J425" s="7"/>
       <c r="K425" s="4"/>
       <c r="L425" s="4"/>
       <c r="M425" s="4"/>
@@ -13370,7 +13535,7 @@
       <c r="G426" s="4"/>
       <c r="H426" s="4"/>
       <c r="I426" s="4"/>
-      <c r="J426" s="4"/>
+      <c r="J426" s="7"/>
       <c r="K426" s="4"/>
       <c r="L426" s="4"/>
       <c r="M426" s="4"/>
@@ -13400,7 +13565,7 @@
       <c r="G427" s="4"/>
       <c r="H427" s="4"/>
       <c r="I427" s="4"/>
-      <c r="J427" s="4"/>
+      <c r="J427" s="7"/>
       <c r="K427" s="4"/>
       <c r="L427" s="4"/>
       <c r="M427" s="4"/>
@@ -13430,7 +13595,7 @@
       <c r="G428" s="4"/>
       <c r="H428" s="4"/>
       <c r="I428" s="4"/>
-      <c r="J428" s="4"/>
+      <c r="J428" s="7"/>
       <c r="K428" s="4"/>
       <c r="L428" s="4"/>
       <c r="M428" s="4"/>
@@ -13460,7 +13625,7 @@
       <c r="G429" s="4"/>
       <c r="H429" s="4"/>
       <c r="I429" s="4"/>
-      <c r="J429" s="4"/>
+      <c r="J429" s="7"/>
       <c r="K429" s="4"/>
       <c r="L429" s="4"/>
       <c r="M429" s="4"/>
@@ -13490,7 +13655,7 @@
       <c r="G430" s="4"/>
       <c r="H430" s="4"/>
       <c r="I430" s="4"/>
-      <c r="J430" s="4"/>
+      <c r="J430" s="7"/>
       <c r="K430" s="4"/>
       <c r="L430" s="4"/>
       <c r="M430" s="4"/>
@@ -13520,7 +13685,7 @@
       <c r="G431" s="4"/>
       <c r="H431" s="4"/>
       <c r="I431" s="4"/>
-      <c r="J431" s="4"/>
+      <c r="J431" s="7"/>
       <c r="K431" s="4"/>
       <c r="L431" s="4"/>
       <c r="M431" s="4"/>
@@ -13550,7 +13715,7 @@
       <c r="G432" s="4"/>
       <c r="H432" s="4"/>
       <c r="I432" s="4"/>
-      <c r="J432" s="4"/>
+      <c r="J432" s="7"/>
       <c r="K432" s="4"/>
       <c r="L432" s="4"/>
       <c r="M432" s="4"/>
@@ -13580,7 +13745,7 @@
       <c r="G433" s="4"/>
       <c r="H433" s="4"/>
       <c r="I433" s="4"/>
-      <c r="J433" s="4"/>
+      <c r="J433" s="7"/>
       <c r="K433" s="4"/>
       <c r="L433" s="4"/>
       <c r="M433" s="4"/>
@@ -13610,7 +13775,7 @@
       <c r="G434" s="4"/>
       <c r="H434" s="4"/>
       <c r="I434" s="4"/>
-      <c r="J434" s="4"/>
+      <c r="J434" s="7"/>
       <c r="K434" s="4"/>
       <c r="L434" s="4"/>
       <c r="M434" s="4"/>
@@ -13640,7 +13805,7 @@
       <c r="G435" s="4"/>
       <c r="H435" s="4"/>
       <c r="I435" s="4"/>
-      <c r="J435" s="4"/>
+      <c r="J435" s="7"/>
       <c r="K435" s="4"/>
       <c r="L435" s="4"/>
       <c r="M435" s="4"/>
@@ -13670,7 +13835,7 @@
       <c r="G436" s="4"/>
       <c r="H436" s="4"/>
       <c r="I436" s="4"/>
-      <c r="J436" s="4"/>
+      <c r="J436" s="7"/>
       <c r="K436" s="4"/>
       <c r="L436" s="4"/>
       <c r="M436" s="4"/>
@@ -13700,7 +13865,7 @@
       <c r="G437" s="4"/>
       <c r="H437" s="4"/>
       <c r="I437" s="4"/>
-      <c r="J437" s="4"/>
+      <c r="J437" s="7"/>
       <c r="K437" s="4"/>
       <c r="L437" s="4"/>
       <c r="M437" s="4"/>
@@ -13730,7 +13895,7 @@
       <c r="G438" s="4"/>
       <c r="H438" s="4"/>
       <c r="I438" s="4"/>
-      <c r="J438" s="4"/>
+      <c r="J438" s="7"/>
       <c r="K438" s="4"/>
       <c r="L438" s="4"/>
       <c r="M438" s="4"/>
@@ -13760,7 +13925,7 @@
       <c r="G439" s="4"/>
       <c r="H439" s="4"/>
       <c r="I439" s="4"/>
-      <c r="J439" s="4"/>
+      <c r="J439" s="7"/>
       <c r="K439" s="4"/>
       <c r="L439" s="4"/>
       <c r="M439" s="4"/>
@@ -13790,7 +13955,7 @@
       <c r="G440" s="4"/>
       <c r="H440" s="4"/>
       <c r="I440" s="4"/>
-      <c r="J440" s="4"/>
+      <c r="J440" s="7"/>
       <c r="K440" s="4"/>
       <c r="L440" s="4"/>
       <c r="M440" s="4"/>
@@ -13820,7 +13985,7 @@
       <c r="G441" s="4"/>
       <c r="H441" s="4"/>
       <c r="I441" s="4"/>
-      <c r="J441" s="4"/>
+      <c r="J441" s="7"/>
       <c r="K441" s="4"/>
       <c r="L441" s="4"/>
       <c r="M441" s="4"/>
@@ -13850,7 +14015,7 @@
       <c r="G442" s="4"/>
       <c r="H442" s="4"/>
       <c r="I442" s="4"/>
-      <c r="J442" s="4"/>
+      <c r="J442" s="7"/>
       <c r="K442" s="4"/>
       <c r="L442" s="4"/>
       <c r="M442" s="4"/>
@@ -13880,7 +14045,7 @@
       <c r="G443" s="4"/>
       <c r="H443" s="4"/>
       <c r="I443" s="4"/>
-      <c r="J443" s="4"/>
+      <c r="J443" s="7"/>
       <c r="K443" s="4"/>
       <c r="L443" s="4"/>
       <c r="M443" s="4"/>
@@ -13910,7 +14075,7 @@
       <c r="G444" s="4"/>
       <c r="H444" s="4"/>
       <c r="I444" s="4"/>
-      <c r="J444" s="4"/>
+      <c r="J444" s="7"/>
       <c r="K444" s="4"/>
       <c r="L444" s="4"/>
       <c r="M444" s="4"/>
@@ -13940,7 +14105,7 @@
       <c r="G445" s="4"/>
       <c r="H445" s="4"/>
       <c r="I445" s="4"/>
-      <c r="J445" s="4"/>
+      <c r="J445" s="7"/>
       <c r="K445" s="4"/>
       <c r="L445" s="4"/>
       <c r="M445" s="4"/>
@@ -13970,7 +14135,7 @@
       <c r="G446" s="4"/>
       <c r="H446" s="4"/>
       <c r="I446" s="4"/>
-      <c r="J446" s="4"/>
+      <c r="J446" s="7"/>
       <c r="K446" s="4"/>
       <c r="L446" s="4"/>
       <c r="M446" s="4"/>
@@ -14000,7 +14165,7 @@
       <c r="G447" s="4"/>
       <c r="H447" s="4"/>
       <c r="I447" s="4"/>
-      <c r="J447" s="4"/>
+      <c r="J447" s="7"/>
       <c r="K447" s="4"/>
       <c r="L447" s="4"/>
       <c r="M447" s="4"/>
@@ -14030,7 +14195,7 @@
       <c r="G448" s="4"/>
       <c r="H448" s="4"/>
       <c r="I448" s="4"/>
-      <c r="J448" s="4"/>
+      <c r="J448" s="7"/>
       <c r="K448" s="4"/>
       <c r="L448" s="4"/>
       <c r="M448" s="4"/>
@@ -14060,7 +14225,7 @@
       <c r="G449" s="4"/>
       <c r="H449" s="4"/>
       <c r="I449" s="4"/>
-      <c r="J449" s="4"/>
+      <c r="J449" s="7"/>
       <c r="K449" s="4"/>
       <c r="L449" s="4"/>
       <c r="M449" s="4"/>
@@ -14090,7 +14255,7 @@
       <c r="G450" s="4"/>
       <c r="H450" s="4"/>
       <c r="I450" s="4"/>
-      <c r="J450" s="4"/>
+      <c r="J450" s="7"/>
       <c r="K450" s="4"/>
       <c r="L450" s="4"/>
       <c r="M450" s="4"/>
@@ -14120,7 +14285,7 @@
       <c r="G451" s="4"/>
       <c r="H451" s="4"/>
       <c r="I451" s="4"/>
-      <c r="J451" s="4"/>
+      <c r="J451" s="7"/>
       <c r="K451" s="4"/>
       <c r="L451" s="4"/>
       <c r="M451" s="4"/>
@@ -14150,7 +14315,7 @@
       <c r="G452" s="4"/>
       <c r="H452" s="4"/>
       <c r="I452" s="4"/>
-      <c r="J452" s="4"/>
+      <c r="J452" s="7"/>
       <c r="K452" s="4"/>
       <c r="L452" s="4"/>
       <c r="M452" s="4"/>
@@ -14180,7 +14345,7 @@
       <c r="G453" s="4"/>
       <c r="H453" s="4"/>
       <c r="I453" s="4"/>
-      <c r="J453" s="4"/>
+      <c r="J453" s="7"/>
       <c r="K453" s="4"/>
       <c r="L453" s="4"/>
       <c r="M453" s="4"/>
@@ -14210,7 +14375,7 @@
       <c r="G454" s="4"/>
       <c r="H454" s="4"/>
       <c r="I454" s="4"/>
-      <c r="J454" s="4"/>
+      <c r="J454" s="7"/>
       <c r="K454" s="4"/>
       <c r="L454" s="4"/>
       <c r="M454" s="4"/>
@@ -14240,7 +14405,7 @@
       <c r="G455" s="4"/>
       <c r="H455" s="4"/>
       <c r="I455" s="4"/>
-      <c r="J455" s="4"/>
+      <c r="J455" s="7"/>
       <c r="K455" s="4"/>
       <c r="L455" s="4"/>
       <c r="M455" s="4"/>
@@ -14270,7 +14435,7 @@
       <c r="G456" s="4"/>
       <c r="H456" s="4"/>
       <c r="I456" s="4"/>
-      <c r="J456" s="4"/>
+      <c r="J456" s="7"/>
       <c r="K456" s="4"/>
       <c r="L456" s="4"/>
       <c r="M456" s="4"/>
@@ -14300,7 +14465,7 @@
       <c r="G457" s="4"/>
       <c r="H457" s="4"/>
       <c r="I457" s="4"/>
-      <c r="J457" s="4"/>
+      <c r="J457" s="7"/>
       <c r="K457" s="4"/>
       <c r="L457" s="4"/>
       <c r="M457" s="4"/>
@@ -14330,7 +14495,7 @@
       <c r="G458" s="4"/>
       <c r="H458" s="4"/>
       <c r="I458" s="4"/>
-      <c r="J458" s="4"/>
+      <c r="J458" s="7"/>
       <c r="K458" s="4"/>
       <c r="L458" s="4"/>
       <c r="M458" s="4"/>
@@ -14360,7 +14525,7 @@
       <c r="G459" s="4"/>
       <c r="H459" s="4"/>
       <c r="I459" s="4"/>
-      <c r="J459" s="4"/>
+      <c r="J459" s="7"/>
       <c r="K459" s="4"/>
       <c r="L459" s="4"/>
       <c r="M459" s="4"/>
@@ -14390,7 +14555,7 @@
       <c r="G460" s="4"/>
       <c r="H460" s="4"/>
       <c r="I460" s="4"/>
-      <c r="J460" s="4"/>
+      <c r="J460" s="7"/>
       <c r="K460" s="4"/>
       <c r="L460" s="4"/>
       <c r="M460" s="4"/>
@@ -14420,7 +14585,7 @@
       <c r="G461" s="4"/>
       <c r="H461" s="4"/>
       <c r="I461" s="4"/>
-      <c r="J461" s="4"/>
+      <c r="J461" s="7"/>
       <c r="K461" s="4"/>
       <c r="L461" s="4"/>
       <c r="M461" s="4"/>
@@ -14450,7 +14615,7 @@
       <c r="G462" s="4"/>
       <c r="H462" s="4"/>
       <c r="I462" s="4"/>
-      <c r="J462" s="4"/>
+      <c r="J462" s="7"/>
       <c r="K462" s="4"/>
       <c r="L462" s="4"/>
       <c r="M462" s="4"/>
@@ -14480,7 +14645,7 @@
       <c r="G463" s="4"/>
       <c r="H463" s="4"/>
       <c r="I463" s="4"/>
-      <c r="J463" s="4"/>
+      <c r="J463" s="7"/>
       <c r="K463" s="4"/>
       <c r="L463" s="4"/>
       <c r="M463" s="4"/>
@@ -14510,7 +14675,7 @@
       <c r="G464" s="4"/>
       <c r="H464" s="4"/>
       <c r="I464" s="4"/>
-      <c r="J464" s="4"/>
+      <c r="J464" s="7"/>
       <c r="K464" s="4"/>
       <c r="L464" s="4"/>
       <c r="M464" s="4"/>
@@ -14540,7 +14705,7 @@
       <c r="G465" s="4"/>
       <c r="H465" s="4"/>
       <c r="I465" s="4"/>
-      <c r="J465" s="4"/>
+      <c r="J465" s="7"/>
       <c r="K465" s="4"/>
       <c r="L465" s="4"/>
       <c r="M465" s="4"/>
@@ -14570,7 +14735,7 @@
       <c r="G466" s="4"/>
       <c r="H466" s="4"/>
       <c r="I466" s="4"/>
-      <c r="J466" s="4"/>
+      <c r="J466" s="7"/>
       <c r="K466" s="4"/>
       <c r="L466" s="4"/>
       <c r="M466" s="4"/>
@@ -14600,7 +14765,7 @@
       <c r="G467" s="4"/>
       <c r="H467" s="4"/>
       <c r="I467" s="4"/>
-      <c r="J467" s="4"/>
+      <c r="J467" s="7"/>
       <c r="K467" s="4"/>
       <c r="L467" s="4"/>
       <c r="M467" s="4"/>
@@ -14630,7 +14795,7 @@
       <c r="G468" s="4"/>
       <c r="H468" s="4"/>
       <c r="I468" s="4"/>
-      <c r="J468" s="4"/>
+      <c r="J468" s="7"/>
       <c r="K468" s="4"/>
       <c r="L468" s="4"/>
       <c r="M468" s="4"/>
@@ -14660,7 +14825,7 @@
       <c r="G469" s="4"/>
       <c r="H469" s="4"/>
       <c r="I469" s="4"/>
-      <c r="J469" s="4"/>
+      <c r="J469" s="7"/>
       <c r="K469" s="4"/>
       <c r="L469" s="4"/>
       <c r="M469" s="4"/>
@@ -14690,7 +14855,7 @@
       <c r="G470" s="4"/>
       <c r="H470" s="4"/>
       <c r="I470" s="4"/>
-      <c r="J470" s="4"/>
+      <c r="J470" s="7"/>
       <c r="K470" s="4"/>
       <c r="L470" s="4"/>
       <c r="M470" s="4"/>
@@ -14720,7 +14885,7 @@
       <c r="G471" s="4"/>
       <c r="H471" s="4"/>
       <c r="I471" s="4"/>
-      <c r="J471" s="4"/>
+      <c r="J471" s="7"/>
       <c r="K471" s="4"/>
       <c r="L471" s="4"/>
       <c r="M471" s="4"/>
@@ -14750,7 +14915,7 @@
       <c r="G472" s="4"/>
       <c r="H472" s="4"/>
       <c r="I472" s="4"/>
-      <c r="J472" s="4"/>
+      <c r="J472" s="7"/>
       <c r="K472" s="4"/>
       <c r="L472" s="4"/>
       <c r="M472" s="4"/>
@@ -14780,7 +14945,7 @@
       <c r="G473" s="4"/>
       <c r="H473" s="4"/>
       <c r="I473" s="4"/>
-      <c r="J473" s="4"/>
+      <c r="J473" s="7"/>
       <c r="K473" s="4"/>
       <c r="L473" s="4"/>
       <c r="M473" s="4"/>
@@ -14810,7 +14975,7 @@
       <c r="G474" s="4"/>
       <c r="H474" s="4"/>
       <c r="I474" s="4"/>
-      <c r="J474" s="4"/>
+      <c r="J474" s="7"/>
       <c r="K474" s="4"/>
       <c r="L474" s="4"/>
       <c r="M474" s="4"/>
@@ -14840,7 +15005,7 @@
       <c r="G475" s="4"/>
       <c r="H475" s="4"/>
       <c r="I475" s="4"/>
-      <c r="J475" s="4"/>
+      <c r="J475" s="7"/>
       <c r="K475" s="4"/>
       <c r="L475" s="4"/>
       <c r="M475" s="4"/>
@@ -14870,7 +15035,7 @@
       <c r="G476" s="4"/>
       <c r="H476" s="4"/>
       <c r="I476" s="4"/>
-      <c r="J476" s="4"/>
+      <c r="J476" s="7"/>
       <c r="K476" s="4"/>
       <c r="L476" s="4"/>
       <c r="M476" s="4"/>
@@ -14900,7 +15065,7 @@
       <c r="G477" s="4"/>
       <c r="H477" s="4"/>
       <c r="I477" s="4"/>
-      <c r="J477" s="4"/>
+      <c r="J477" s="7"/>
       <c r="K477" s="4"/>
       <c r="L477" s="4"/>
       <c r="M477" s="4"/>
@@ -14930,7 +15095,7 @@
       <c r="G478" s="4"/>
       <c r="H478" s="4"/>
       <c r="I478" s="4"/>
-      <c r="J478" s="4"/>
+      <c r="J478" s="7"/>
       <c r="K478" s="4"/>
       <c r="L478" s="4"/>
       <c r="M478" s="4"/>
@@ -14960,7 +15125,7 @@
       <c r="G479" s="4"/>
       <c r="H479" s="4"/>
       <c r="I479" s="4"/>
-      <c r="J479" s="4"/>
+      <c r="J479" s="7"/>
       <c r="K479" s="4"/>
       <c r="L479" s="4"/>
       <c r="M479" s="4"/>
@@ -14990,7 +15155,7 @@
       <c r="G480" s="4"/>
       <c r="H480" s="4"/>
       <c r="I480" s="4"/>
-      <c r="J480" s="4"/>
+      <c r="J480" s="7"/>
       <c r="K480" s="4"/>
       <c r="L480" s="4"/>
       <c r="M480" s="4"/>
@@ -15020,7 +15185,7 @@
       <c r="G481" s="4"/>
       <c r="H481" s="4"/>
       <c r="I481" s="4"/>
-      <c r="J481" s="4"/>
+      <c r="J481" s="7"/>
       <c r="K481" s="4"/>
       <c r="L481" s="4"/>
       <c r="M481" s="4"/>
@@ -15050,7 +15215,7 @@
       <c r="G482" s="4"/>
       <c r="H482" s="4"/>
       <c r="I482" s="4"/>
-      <c r="J482" s="4"/>
+      <c r="J482" s="7"/>
       <c r="K482" s="4"/>
       <c r="L482" s="4"/>
       <c r="M482" s="4"/>
@@ -15080,7 +15245,7 @@
       <c r="G483" s="4"/>
       <c r="H483" s="4"/>
       <c r="I483" s="4"/>
-      <c r="J483" s="4"/>
+      <c r="J483" s="7"/>
       <c r="K483" s="4"/>
       <c r="L483" s="4"/>
       <c r="M483" s="4"/>
@@ -15110,7 +15275,7 @@
       <c r="G484" s="4"/>
       <c r="H484" s="4"/>
       <c r="I484" s="4"/>
-      <c r="J484" s="4"/>
+      <c r="J484" s="7"/>
       <c r="K484" s="4"/>
       <c r="L484" s="4"/>
       <c r="M484" s="4"/>
@@ -15140,7 +15305,7 @@
       <c r="G485" s="4"/>
       <c r="H485" s="4"/>
       <c r="I485" s="4"/>
-      <c r="J485" s="4"/>
+      <c r="J485" s="7"/>
       <c r="K485" s="4"/>
       <c r="L485" s="4"/>
       <c r="M485" s="4"/>
@@ -15170,7 +15335,7 @@
       <c r="G486" s="4"/>
       <c r="H486" s="4"/>
       <c r="I486" s="4"/>
-      <c r="J486" s="4"/>
+      <c r="J486" s="7"/>
       <c r="K486" s="4"/>
       <c r="L486" s="4"/>
       <c r="M486" s="4"/>
@@ -15200,7 +15365,7 @@
       <c r="G487" s="4"/>
       <c r="H487" s="4"/>
       <c r="I487" s="4"/>
-      <c r="J487" s="4"/>
+      <c r="J487" s="7"/>
       <c r="K487" s="4"/>
       <c r="L487" s="4"/>
       <c r="M487" s="4"/>
@@ -15230,7 +15395,7 @@
       <c r="G488" s="4"/>
       <c r="H488" s="4"/>
       <c r="I488" s="4"/>
-      <c r="J488" s="4"/>
+      <c r="J488" s="7"/>
       <c r="K488" s="4"/>
       <c r="L488" s="4"/>
       <c r="M488" s="4"/>
@@ -15260,7 +15425,7 @@
       <c r="G489" s="4"/>
       <c r="H489" s="4"/>
       <c r="I489" s="4"/>
-      <c r="J489" s="4"/>
+      <c r="J489" s="7"/>
       <c r="K489" s="4"/>
       <c r="L489" s="4"/>
       <c r="M489" s="4"/>
@@ -15290,7 +15455,7 @@
       <c r="G490" s="4"/>
       <c r="H490" s="4"/>
       <c r="I490" s="4"/>
-      <c r="J490" s="4"/>
+      <c r="J490" s="7"/>
       <c r="K490" s="4"/>
       <c r="L490" s="4"/>
       <c r="M490" s="4"/>
@@ -15320,7 +15485,7 @@
       <c r="G491" s="4"/>
       <c r="H491" s="4"/>
       <c r="I491" s="4"/>
-      <c r="J491" s="4"/>
+      <c r="J491" s="7"/>
       <c r="K491" s="4"/>
       <c r="L491" s="4"/>
       <c r="M491" s="4"/>
@@ -15350,7 +15515,7 @@
       <c r="G492" s="4"/>
       <c r="H492" s="4"/>
       <c r="I492" s="4"/>
-      <c r="J492" s="4"/>
+      <c r="J492" s="7"/>
       <c r="K492" s="4"/>
       <c r="L492" s="4"/>
       <c r="M492" s="4"/>
@@ -15380,7 +15545,7 @@
       <c r="G493" s="4"/>
       <c r="H493" s="4"/>
       <c r="I493" s="4"/>
-      <c r="J493" s="4"/>
+      <c r="J493" s="7"/>
       <c r="K493" s="4"/>
       <c r="L493" s="4"/>
       <c r="M493" s="4"/>
@@ -15410,7 +15575,7 @@
       <c r="G494" s="4"/>
       <c r="H494" s="4"/>
       <c r="I494" s="4"/>
-      <c r="J494" s="4"/>
+      <c r="J494" s="7"/>
       <c r="K494" s="4"/>
       <c r="L494" s="4"/>
       <c r="M494" s="4"/>
@@ -15440,7 +15605,7 @@
       <c r="G495" s="4"/>
       <c r="H495" s="4"/>
       <c r="I495" s="4"/>
-      <c r="J495" s="4"/>
+      <c r="J495" s="7"/>
       <c r="K495" s="4"/>
       <c r="L495" s="4"/>
       <c r="M495" s="4"/>
@@ -15470,7 +15635,7 @@
       <c r="G496" s="4"/>
       <c r="H496" s="4"/>
       <c r="I496" s="4"/>
-      <c r="J496" s="4"/>
+      <c r="J496" s="7"/>
       <c r="K496" s="4"/>
       <c r="L496" s="4"/>
       <c r="M496" s="4"/>
@@ -15500,7 +15665,7 @@
       <c r="G497" s="4"/>
       <c r="H497" s="4"/>
       <c r="I497" s="4"/>
-      <c r="J497" s="4"/>
+      <c r="J497" s="7"/>
       <c r="K497" s="4"/>
       <c r="L497" s="4"/>
       <c r="M497" s="4"/>
@@ -15530,7 +15695,7 @@
       <c r="G498" s="4"/>
       <c r="H498" s="4"/>
       <c r="I498" s="4"/>
-      <c r="J498" s="4"/>
+      <c r="J498" s="7"/>
       <c r="K498" s="4"/>
       <c r="L498" s="4"/>
       <c r="M498" s="4"/>
@@ -15560,7 +15725,7 @@
       <c r="G499" s="4"/>
       <c r="H499" s="4"/>
       <c r="I499" s="4"/>
-      <c r="J499" s="4"/>
+      <c r="J499" s="7"/>
       <c r="K499" s="4"/>
       <c r="L499" s="4"/>
       <c r="M499" s="4"/>
@@ -15590,7 +15755,7 @@
       <c r="G500" s="4"/>
       <c r="H500" s="4"/>
       <c r="I500" s="4"/>
-      <c r="J500" s="4"/>
+      <c r="J500" s="7"/>
       <c r="K500" s="4"/>
       <c r="L500" s="4"/>
       <c r="M500" s="4"/>
@@ -15620,7 +15785,7 @@
       <c r="G501" s="4"/>
       <c r="H501" s="4"/>
       <c r="I501" s="4"/>
-      <c r="J501" s="4"/>
+      <c r="J501" s="7"/>
       <c r="K501" s="4"/>
       <c r="L501" s="4"/>
       <c r="M501" s="4"/>
@@ -15650,7 +15815,7 @@
       <c r="G502" s="4"/>
       <c r="H502" s="4"/>
       <c r="I502" s="4"/>
-      <c r="J502" s="4"/>
+      <c r="J502" s="7"/>
       <c r="K502" s="4"/>
       <c r="L502" s="4"/>
       <c r="M502" s="4"/>
@@ -15680,7 +15845,7 @@
       <c r="G503" s="4"/>
       <c r="H503" s="4"/>
       <c r="I503" s="4"/>
-      <c r="J503" s="4"/>
+      <c r="J503" s="7"/>
       <c r="K503" s="4"/>
       <c r="L503" s="4"/>
       <c r="M503" s="4"/>
@@ -15710,7 +15875,7 @@
       <c r="G504" s="4"/>
       <c r="H504" s="4"/>
       <c r="I504" s="4"/>
-      <c r="J504" s="4"/>
+      <c r="J504" s="7"/>
       <c r="K504" s="4"/>
       <c r="L504" s="4"/>
       <c r="M504" s="4"/>
@@ -15740,7 +15905,7 @@
       <c r="G505" s="4"/>
       <c r="H505" s="4"/>
       <c r="I505" s="4"/>
-      <c r="J505" s="4"/>
+      <c r="J505" s="7"/>
       <c r="K505" s="4"/>
       <c r="L505" s="4"/>
       <c r="M505" s="4"/>
@@ -15770,7 +15935,7 @@
       <c r="G506" s="4"/>
       <c r="H506" s="4"/>
       <c r="I506" s="4"/>
-      <c r="J506" s="4"/>
+      <c r="J506" s="7"/>
       <c r="K506" s="4"/>
       <c r="L506" s="4"/>
       <c r="M506" s="4"/>
@@ -15800,7 +15965,7 @@
       <c r="G507" s="4"/>
       <c r="H507" s="4"/>
       <c r="I507" s="4"/>
-      <c r="J507" s="4"/>
+      <c r="J507" s="7"/>
       <c r="K507" s="4"/>
       <c r="L507" s="4"/>
       <c r="M507" s="4"/>
@@ -15830,7 +15995,7 @@
       <c r="G508" s="4"/>
       <c r="H508" s="4"/>
       <c r="I508" s="4"/>
-      <c r="J508" s="4"/>
+      <c r="J508" s="7"/>
       <c r="K508" s="4"/>
       <c r="L508" s="4"/>
       <c r="M508" s="4"/>
@@ -15860,7 +16025,7 @@
       <c r="G509" s="4"/>
       <c r="H509" s="4"/>
       <c r="I509" s="4"/>
-      <c r="J509" s="4"/>
+      <c r="J509" s="7"/>
       <c r="K509" s="4"/>
       <c r="L509" s="4"/>
       <c r="M509" s="4"/>
@@ -15890,7 +16055,7 @@
       <c r="G510" s="4"/>
       <c r="H510" s="4"/>
       <c r="I510" s="4"/>
-      <c r="J510" s="4"/>
+      <c r="J510" s="7"/>
       <c r="K510" s="4"/>
       <c r="L510" s="4"/>
       <c r="M510" s="4"/>
@@ -15920,7 +16085,7 @@
       <c r="G511" s="4"/>
       <c r="H511" s="4"/>
       <c r="I511" s="4"/>
-      <c r="J511" s="4"/>
+      <c r="J511" s="7"/>
       <c r="K511" s="4"/>
       <c r="L511" s="4"/>
       <c r="M511" s="4"/>
@@ -15950,7 +16115,7 @@
       <c r="G512" s="4"/>
       <c r="H512" s="4"/>
       <c r="I512" s="4"/>
-      <c r="J512" s="4"/>
+      <c r="J512" s="7"/>
       <c r="K512" s="4"/>
       <c r="L512" s="4"/>
       <c r="M512" s="4"/>
@@ -15980,7 +16145,7 @@
       <c r="G513" s="4"/>
       <c r="H513" s="4"/>
       <c r="I513" s="4"/>
-      <c r="J513" s="4"/>
+      <c r="J513" s="7"/>
       <c r="K513" s="4"/>
       <c r="L513" s="4"/>
       <c r="M513" s="4"/>
@@ -16010,7 +16175,7 @@
       <c r="G514" s="4"/>
       <c r="H514" s="4"/>
       <c r="I514" s="4"/>
-      <c r="J514" s="4"/>
+      <c r="J514" s="7"/>
       <c r="K514" s="4"/>
       <c r="L514" s="4"/>
       <c r="M514" s="4"/>
@@ -16040,7 +16205,7 @@
       <c r="G515" s="4"/>
       <c r="H515" s="4"/>
       <c r="I515" s="4"/>
-      <c r="J515" s="4"/>
+      <c r="J515" s="7"/>
       <c r="K515" s="4"/>
       <c r="L515" s="4"/>
       <c r="M515" s="4"/>
@@ -16070,7 +16235,7 @@
       <c r="G516" s="4"/>
       <c r="H516" s="4"/>
       <c r="I516" s="4"/>
-      <c r="J516" s="4"/>
+      <c r="J516" s="7"/>
       <c r="K516" s="4"/>
       <c r="L516" s="4"/>
       <c r="M516" s="4"/>
@@ -16100,7 +16265,7 @@
       <c r="G517" s="4"/>
       <c r="H517" s="4"/>
       <c r="I517" s="4"/>
-      <c r="J517" s="4"/>
+      <c r="J517" s="7"/>
       <c r="K517" s="4"/>
       <c r="L517" s="4"/>
       <c r="M517" s="4"/>
@@ -16130,7 +16295,7 @@
       <c r="G518" s="4"/>
       <c r="H518" s="4"/>
       <c r="I518" s="4"/>
-      <c r="J518" s="4"/>
+      <c r="J518" s="7"/>
       <c r="K518" s="4"/>
       <c r="L518" s="4"/>
       <c r="M518" s="4"/>
@@ -16160,7 +16325,7 @@
       <c r="G519" s="4"/>
       <c r="H519" s="4"/>
       <c r="I519" s="4"/>
-      <c r="J519" s="4"/>
+      <c r="J519" s="7"/>
       <c r="K519" s="4"/>
       <c r="L519" s="4"/>
       <c r="M519" s="4"/>
@@ -16190,7 +16355,7 @@
       <c r="G520" s="4"/>
       <c r="H520" s="4"/>
       <c r="I520" s="4"/>
-      <c r="J520" s="4"/>
+      <c r="J520" s="7"/>
       <c r="K520" s="4"/>
       <c r="L520" s="4"/>
       <c r="M520" s="4"/>
@@ -16220,7 +16385,7 @@
       <c r="G521" s="4"/>
       <c r="H521" s="4"/>
       <c r="I521" s="4"/>
-      <c r="J521" s="4"/>
+      <c r="J521" s="7"/>
       <c r="K521" s="4"/>
       <c r="L521" s="4"/>
       <c r="M521" s="4"/>
@@ -16250,7 +16415,7 @@
       <c r="G522" s="4"/>
       <c r="H522" s="4"/>
       <c r="I522" s="4"/>
-      <c r="J522" s="4"/>
+      <c r="J522" s="7"/>
       <c r="K522" s="4"/>
       <c r="L522" s="4"/>
       <c r="M522" s="4"/>
@@ -16280,7 +16445,7 @@
       <c r="G523" s="4"/>
       <c r="H523" s="4"/>
       <c r="I523" s="4"/>
-      <c r="J523" s="4"/>
+      <c r="J523" s="7"/>
       <c r="K523" s="4"/>
       <c r="L523" s="4"/>
       <c r="M523" s="4"/>
@@ -16310,7 +16475,7 @@
       <c r="G524" s="4"/>
       <c r="H524" s="4"/>
       <c r="I524" s="4"/>
-      <c r="J524" s="4"/>
+      <c r="J524" s="7"/>
       <c r="K524" s="4"/>
       <c r="L524" s="4"/>
       <c r="M524" s="4"/>
@@ -16340,7 +16505,7 @@
       <c r="G525" s="4"/>
       <c r="H525" s="4"/>
       <c r="I525" s="4"/>
-      <c r="J525" s="4"/>
+      <c r="J525" s="7"/>
       <c r="K525" s="4"/>
       <c r="L525" s="4"/>
       <c r="M525" s="4"/>
@@ -16370,7 +16535,7 @@
       <c r="G526" s="4"/>
       <c r="H526" s="4"/>
       <c r="I526" s="4"/>
-      <c r="J526" s="4"/>
+      <c r="J526" s="7"/>
       <c r="K526" s="4"/>
       <c r="L526" s="4"/>
       <c r="M526" s="4"/>
@@ -16400,7 +16565,7 @@
       <c r="G527" s="4"/>
       <c r="H527" s="4"/>
       <c r="I527" s="4"/>
-      <c r="J527" s="4"/>
+      <c r="J527" s="7"/>
       <c r="K527" s="4"/>
       <c r="L527" s="4"/>
       <c r="M527" s="4"/>
@@ -16430,7 +16595,7 @@
       <c r="G528" s="4"/>
       <c r="H528" s="4"/>
       <c r="I528" s="4"/>
-      <c r="J528" s="4"/>
+      <c r="J528" s="7"/>
       <c r="K528" s="4"/>
       <c r="L528" s="4"/>
       <c r="M528" s="4"/>
@@ -16460,7 +16625,7 @@
       <c r="G529" s="4"/>
       <c r="H529" s="4"/>
       <c r="I529" s="4"/>
-      <c r="J529" s="4"/>
+      <c r="J529" s="7"/>
       <c r="K529" s="4"/>
       <c r="L529" s="4"/>
       <c r="M529" s="4"/>
@@ -16490,7 +16655,7 @@
       <c r="G530" s="4"/>
       <c r="H530" s="4"/>
       <c r="I530" s="4"/>
-      <c r="J530" s="4"/>
+      <c r="J530" s="7"/>
       <c r="K530" s="4"/>
       <c r="L530" s="4"/>
       <c r="M530" s="4"/>
@@ -16520,7 +16685,7 @@
       <c r="G531" s="4"/>
       <c r="H531" s="4"/>
       <c r="I531" s="4"/>
-      <c r="J531" s="4"/>
+      <c r="J531" s="7"/>
       <c r="K531" s="4"/>
       <c r="L531" s="4"/>
       <c r="M531" s="4"/>
@@ -16550,7 +16715,7 @@
       <c r="G532" s="4"/>
       <c r="H532" s="4"/>
       <c r="I532" s="4"/>
-      <c r="J532" s="4"/>
+      <c r="J532" s="7"/>
       <c r="K532" s="4"/>
       <c r="L532" s="4"/>
       <c r="M532" s="4"/>
@@ -16580,7 +16745,7 @@
       <c r="G533" s="4"/>
       <c r="H533" s="4"/>
       <c r="I533" s="4"/>
-      <c r="J533" s="4"/>
+      <c r="J533" s="7"/>
       <c r="K533" s="4"/>
       <c r="L533" s="4"/>
       <c r="M533" s="4"/>
@@ -16610,7 +16775,7 @@
       <c r="G534" s="4"/>
       <c r="H534" s="4"/>
       <c r="I534" s="4"/>
-      <c r="J534" s="4"/>
+      <c r="J534" s="7"/>
       <c r="K534" s="4"/>
       <c r="L534" s="4"/>
       <c r="M534" s="4"/>
@@ -16640,7 +16805,7 @@
       <c r="G535" s="4"/>
       <c r="H535" s="4"/>
       <c r="I535" s="4"/>
-      <c r="J535" s="4"/>
+      <c r="J535" s="7"/>
       <c r="K535" s="4"/>
       <c r="L535" s="4"/>
       <c r="M535" s="4"/>
@@ -16670,7 +16835,7 @@
       <c r="G536" s="4"/>
       <c r="H536" s="4"/>
       <c r="I536" s="4"/>
-      <c r="J536" s="4"/>
+      <c r="J536" s="7"/>
       <c r="K536" s="4"/>
       <c r="L536" s="4"/>
       <c r="M536" s="4"/>
@@ -16700,7 +16865,7 @@
       <c r="G537" s="4"/>
       <c r="H537" s="4"/>
       <c r="I537" s="4"/>
-      <c r="J537" s="4"/>
+      <c r="J537" s="7"/>
       <c r="K537" s="4"/>
       <c r="L537" s="4"/>
       <c r="M537" s="4"/>
@@ -16730,7 +16895,7 @@
       <c r="G538" s="4"/>
       <c r="H538" s="4"/>
       <c r="I538" s="4"/>
-      <c r="J538" s="4"/>
+      <c r="J538" s="7"/>
       <c r="K538" s="4"/>
       <c r="L538" s="4"/>
       <c r="M538" s="4"/>
@@ -16760,7 +16925,7 @@
       <c r="G539" s="4"/>
       <c r="H539" s="4"/>
       <c r="I539" s="4"/>
-      <c r="J539" s="4"/>
+      <c r="J539" s="7"/>
       <c r="K539" s="4"/>
       <c r="L539" s="4"/>
       <c r="M539" s="4"/>
@@ -16790,7 +16955,7 @@
       <c r="G540" s="4"/>
       <c r="H540" s="4"/>
       <c r="I540" s="4"/>
-      <c r="J540" s="4"/>
+      <c r="J540" s="7"/>
       <c r="K540" s="4"/>
       <c r="L540" s="4"/>
       <c r="M540" s="4"/>
@@ -16820,7 +16985,7 @@
       <c r="G541" s="4"/>
       <c r="H541" s="4"/>
       <c r="I541" s="4"/>
-      <c r="J541" s="4"/>
+      <c r="J541" s="7"/>
       <c r="K541" s="4"/>
       <c r="L541" s="4"/>
       <c r="M541" s="4"/>
@@ -16850,7 +17015,7 @@
       <c r="G542" s="4"/>
       <c r="H542" s="4"/>
       <c r="I542" s="4"/>
-      <c r="J542" s="4"/>
+      <c r="J542" s="7"/>
       <c r="K542" s="4"/>
       <c r="L542" s="4"/>
       <c r="M542" s="4"/>
@@ -16880,7 +17045,7 @@
       <c r="G543" s="4"/>
       <c r="H543" s="4"/>
       <c r="I543" s="4"/>
-      <c r="J543" s="4"/>
+      <c r="J543" s="7"/>
       <c r="K543" s="4"/>
       <c r="L543" s="4"/>
       <c r="M543" s="4"/>
@@ -16910,7 +17075,7 @@
       <c r="G544" s="4"/>
       <c r="H544" s="4"/>
       <c r="I544" s="4"/>
-      <c r="J544" s="4"/>
+      <c r="J544" s="7"/>
       <c r="K544" s="4"/>
       <c r="L544" s="4"/>
       <c r="M544" s="4"/>
@@ -16940,7 +17105,7 @@
       <c r="G545" s="4"/>
       <c r="H545" s="4"/>
       <c r="I545" s="4"/>
-      <c r="J545" s="4"/>
+      <c r="J545" s="7"/>
       <c r="K545" s="4"/>
       <c r="L545" s="4"/>
       <c r="M545" s="4"/>
@@ -16970,7 +17135,7 @@
       <c r="G546" s="4"/>
       <c r="H546" s="4"/>
       <c r="I546" s="4"/>
-      <c r="J546" s="4"/>
+      <c r="J546" s="7"/>
       <c r="K546" s="4"/>
       <c r="L546" s="4"/>
       <c r="M546" s="4"/>
@@ -17000,7 +17165,7 @@
       <c r="G547" s="4"/>
       <c r="H547" s="4"/>
       <c r="I547" s="4"/>
-      <c r="J547" s="4"/>
+      <c r="J547" s="7"/>
       <c r="K547" s="4"/>
       <c r="L547" s="4"/>
       <c r="M547" s="4"/>
@@ -17030,7 +17195,7 @@
       <c r="G548" s="4"/>
       <c r="H548" s="4"/>
       <c r="I548" s="4"/>
-      <c r="J548" s="4"/>
+      <c r="J548" s="7"/>
       <c r="K548" s="4"/>
       <c r="L548" s="4"/>
       <c r="M548" s="4"/>
@@ -17060,7 +17225,7 @@
       <c r="G549" s="4"/>
       <c r="H549" s="4"/>
       <c r="I549" s="4"/>
-      <c r="J549" s="4"/>
+      <c r="J549" s="7"/>
       <c r="K549" s="4"/>
       <c r="L549" s="4"/>
       <c r="M549" s="4"/>
@@ -17090,7 +17255,7 @@
       <c r="G550" s="4"/>
       <c r="H550" s="4"/>
       <c r="I550" s="4"/>
-      <c r="J550" s="4"/>
+      <c r="J550" s="7"/>
       <c r="K550" s="4"/>
       <c r="L550" s="4"/>
       <c r="M550" s="4"/>
@@ -17120,7 +17285,7 @@
       <c r="G551" s="4"/>
       <c r="H551" s="4"/>
       <c r="I551" s="4"/>
-      <c r="J551" s="4"/>
+      <c r="J551" s="7"/>
       <c r="K551" s="4"/>
       <c r="L551" s="4"/>
       <c r="M551" s="4"/>
@@ -17150,7 +17315,7 @@
       <c r="G552" s="4"/>
       <c r="H552" s="4"/>
       <c r="I552" s="4"/>
-      <c r="J552" s="4"/>
+      <c r="J552" s="7"/>
       <c r="K552" s="4"/>
       <c r="L552" s="4"/>
       <c r="M552" s="4"/>
@@ -17180,7 +17345,7 @@
       <c r="G553" s="4"/>
       <c r="H553" s="4"/>
       <c r="I553" s="4"/>
-      <c r="J553" s="4"/>
+      <c r="J553" s="7"/>
       <c r="K553" s="4"/>
       <c r="L553" s="4"/>
       <c r="M553" s="4"/>
@@ -17210,7 +17375,7 @@
       <c r="G554" s="4"/>
       <c r="H554" s="4"/>
       <c r="I554" s="4"/>
-      <c r="J554" s="4"/>
+      <c r="J554" s="7"/>
       <c r="K554" s="4"/>
       <c r="L554" s="4"/>
       <c r="M554" s="4"/>
@@ -17240,7 +17405,7 @@
       <c r="G555" s="4"/>
       <c r="H555" s="4"/>
       <c r="I555" s="4"/>
-      <c r="J555" s="4"/>
+      <c r="J555" s="7"/>
       <c r="K555" s="4"/>
       <c r="L555" s="4"/>
       <c r="M555" s="4"/>
@@ -17270,7 +17435,7 @@
       <c r="G556" s="4"/>
       <c r="H556" s="4"/>
       <c r="I556" s="4"/>
-      <c r="J556" s="4"/>
+      <c r="J556" s="7"/>
       <c r="K556" s="4"/>
       <c r="L556" s="4"/>
       <c r="M556" s="4"/>
@@ -17300,7 +17465,7 @@
       <c r="G557" s="4"/>
       <c r="H557" s="4"/>
       <c r="I557" s="4"/>
-      <c r="J557" s="4"/>
+      <c r="J557" s="7"/>
       <c r="K557" s="4"/>
       <c r="L557" s="4"/>
       <c r="M557" s="4"/>
@@ -17330,7 +17495,7 @@
       <c r="G558" s="4"/>
       <c r="H558" s="4"/>
       <c r="I558" s="4"/>
-      <c r="J558" s="4"/>
+      <c r="J558" s="7"/>
       <c r="K558" s="4"/>
       <c r="L558" s="4"/>
       <c r="M558" s="4"/>
@@ -17360,7 +17525,7 @@
       <c r="G559" s="4"/>
       <c r="H559" s="4"/>
       <c r="I559" s="4"/>
-      <c r="J559" s="4"/>
+      <c r="J559" s="7"/>
       <c r="K559" s="4"/>
       <c r="L559" s="4"/>
       <c r="M559" s="4"/>
@@ -17390,7 +17555,7 @@
       <c r="G560" s="4"/>
       <c r="H560" s="4"/>
       <c r="I560" s="4"/>
-      <c r="J560" s="4"/>
+      <c r="J560" s="7"/>
       <c r="K560" s="4"/>
       <c r="L560" s="4"/>
       <c r="M560" s="4"/>
@@ -17420,7 +17585,7 @@
       <c r="G561" s="4"/>
       <c r="H561" s="4"/>
       <c r="I561" s="4"/>
-      <c r="J561" s="4"/>
+      <c r="J561" s="7"/>
       <c r="K561" s="4"/>
       <c r="L561" s="4"/>
       <c r="M561" s="4"/>
@@ -17450,7 +17615,7 @@
       <c r="G562" s="4"/>
       <c r="H562" s="4"/>
       <c r="I562" s="4"/>
-      <c r="J562" s="4"/>
+      <c r="J562" s="7"/>
       <c r="K562" s="4"/>
       <c r="L562" s="4"/>
       <c r="M562" s="4"/>
@@ -17480,7 +17645,7 @@
       <c r="G563" s="4"/>
       <c r="H563" s="4"/>
       <c r="I563" s="4"/>
-      <c r="J563" s="4"/>
+      <c r="J563" s="7"/>
       <c r="K563" s="4"/>
       <c r="L563" s="4"/>
       <c r="M563" s="4"/>
@@ -17510,7 +17675,7 @@
       <c r="G564" s="4"/>
       <c r="H564" s="4"/>
       <c r="I564" s="4"/>
-      <c r="J564" s="4"/>
+      <c r="J564" s="7"/>
       <c r="K564" s="4"/>
       <c r="L564" s="4"/>
       <c r="M564" s="4"/>
@@ -17540,7 +17705,7 @@
       <c r="G565" s="4"/>
       <c r="H565" s="4"/>
       <c r="I565" s="4"/>
-      <c r="J565" s="4"/>
+      <c r="J565" s="7"/>
       <c r="K565" s="4"/>
       <c r="L565" s="4"/>
       <c r="M565" s="4"/>
@@ -17570,7 +17735,7 @@
       <c r="G566" s="4"/>
       <c r="H566" s="4"/>
       <c r="I566" s="4"/>
-      <c r="J566" s="4"/>
+      <c r="J566" s="7"/>
       <c r="K566" s="4"/>
       <c r="L566" s="4"/>
       <c r="M566" s="4"/>
@@ -17600,7 +17765,7 @@
       <c r="G567" s="4"/>
       <c r="H567" s="4"/>
       <c r="I567" s="4"/>
-      <c r="J567" s="4"/>
+      <c r="J567" s="7"/>
       <c r="K567" s="4"/>
       <c r="L567" s="4"/>
       <c r="M567" s="4"/>
@@ -17630,7 +17795,7 @@
       <c r="G568" s="4"/>
       <c r="H568" s="4"/>
       <c r="I568" s="4"/>
-      <c r="J568" s="4"/>
+      <c r="J568" s="7"/>
       <c r="K568" s="4"/>
       <c r="L568" s="4"/>
       <c r="M568" s="4"/>
@@ -17660,7 +17825,7 @@
       <c r="G569" s="4"/>
       <c r="H569" s="4"/>
       <c r="I569" s="4"/>
-      <c r="J569" s="4"/>
+      <c r="J569" s="7"/>
       <c r="K569" s="4"/>
       <c r="L569" s="4"/>
       <c r="M569" s="4"/>
@@ -17690,7 +17855,7 @@
       <c r="G570" s="4"/>
       <c r="H570" s="4"/>
       <c r="I570" s="4"/>
-      <c r="J570" s="4"/>
+      <c r="J570" s="7"/>
       <c r="K570" s="4"/>
       <c r="L570" s="4"/>
       <c r="M570" s="4"/>
@@ -17720,7 +17885,7 @@
       <c r="G571" s="4"/>
       <c r="H571" s="4"/>
       <c r="I571" s="4"/>
-      <c r="J571" s="4"/>
+      <c r="J571" s="7"/>
       <c r="K571" s="4"/>
       <c r="L571" s="4"/>
       <c r="M571" s="4"/>
@@ -17750,7 +17915,7 @@
       <c r="G572" s="4"/>
       <c r="H572" s="4"/>
       <c r="I572" s="4"/>
-      <c r="J572" s="4"/>
+      <c r="J572" s="7"/>
       <c r="K572" s="4"/>
       <c r="L572" s="4"/>
       <c r="M572" s="4"/>
@@ -17780,7 +17945,7 @@
       <c r="G573" s="4"/>
       <c r="H573" s="4"/>
       <c r="I573" s="4"/>
-      <c r="J573" s="4"/>
+      <c r="J573" s="7"/>
       <c r="K573" s="4"/>
       <c r="L573" s="4"/>
       <c r="M573" s="4"/>
@@ -17810,7 +17975,7 @@
       <c r="G574" s="4"/>
       <c r="H574" s="4"/>
       <c r="I574" s="4"/>
-      <c r="J574" s="4"/>
+      <c r="J574" s="7"/>
       <c r="K574" s="4"/>
       <c r="L574" s="4"/>
       <c r="M574" s="4"/>
@@ -17840,7 +18005,7 @@
       <c r="G575" s="4"/>
       <c r="H575" s="4"/>
       <c r="I575" s="4"/>
-      <c r="J575" s="4"/>
+      <c r="J575" s="7"/>
       <c r="K575" s="4"/>
       <c r="L575" s="4"/>
       <c r="M575" s="4"/>
@@ -17870,7 +18035,7 @@
       <c r="G576" s="4"/>
       <c r="H576" s="4"/>
       <c r="I576" s="4"/>
-      <c r="J576" s="4"/>
+      <c r="J576" s="7"/>
       <c r="K576" s="4"/>
       <c r="L576" s="4"/>
       <c r="M576" s="4"/>
@@ -17900,7 +18065,7 @@
       <c r="G577" s="4"/>
       <c r="H577" s="4"/>
       <c r="I577" s="4"/>
-      <c r="J577" s="4"/>
+      <c r="J577" s="7"/>
       <c r="K577" s="4"/>
       <c r="L577" s="4"/>
       <c r="M577" s="4"/>
@@ -17930,7 +18095,7 @@
       <c r="G578" s="4"/>
       <c r="H578" s="4"/>
       <c r="I578" s="4"/>
-      <c r="J578" s="4"/>
+      <c r="J578" s="7"/>
       <c r="K578" s="4"/>
       <c r="L578" s="4"/>
       <c r="M578" s="4"/>
@@ -17960,7 +18125,7 @@
       <c r="G579" s="4"/>
       <c r="H579" s="4"/>
       <c r="I579" s="4"/>
-      <c r="J579" s="4"/>
+      <c r="J579" s="7"/>
       <c r="K579" s="4"/>
       <c r="L579" s="4"/>
       <c r="M579" s="4"/>
@@ -17990,7 +18155,7 @@
       <c r="G580" s="4"/>
       <c r="H580" s="4"/>
       <c r="I580" s="4"/>
-      <c r="J580" s="4"/>
+      <c r="J580" s="7"/>
       <c r="K580" s="4"/>
       <c r="L580" s="4"/>
       <c r="M580" s="4"/>
@@ -18020,7 +18185,7 @@
       <c r="G581" s="4"/>
       <c r="H581" s="4"/>
       <c r="I581" s="4"/>
-      <c r="J581" s="4"/>
+      <c r="J581" s="7"/>
       <c r="K581" s="4"/>
       <c r="L581" s="4"/>
       <c r="M581" s="4"/>
@@ -18050,7 +18215,7 @@
       <c r="G582" s="4"/>
       <c r="H582" s="4"/>
       <c r="I582" s="4"/>
-      <c r="J582" s="4"/>
+      <c r="J582" s="7"/>
       <c r="K582" s="4"/>
       <c r="L582" s="4"/>
       <c r="M582" s="4"/>
@@ -18080,7 +18245,7 @@
       <c r="G583" s="4"/>
       <c r="H583" s="4"/>
       <c r="I583" s="4"/>
-      <c r="J583" s="4"/>
+      <c r="J583" s="7"/>
       <c r="K583" s="4"/>
       <c r="L583" s="4"/>
       <c r="M583" s="4"/>
@@ -18110,7 +18275,7 @@
       <c r="G584" s="4"/>
       <c r="H584" s="4"/>
       <c r="I584" s="4"/>
-      <c r="J584" s="4"/>
+      <c r="J584" s="7"/>
       <c r="K584" s="4"/>
       <c r="L584" s="4"/>
       <c r="M584" s="4"/>
@@ -18140,7 +18305,7 @@
       <c r="G585" s="4"/>
       <c r="H585" s="4"/>
       <c r="I585" s="4"/>
-      <c r="J585" s="4"/>
+      <c r="J585" s="7"/>
       <c r="K585" s="4"/>
       <c r="L585" s="4"/>
       <c r="M585" s="4"/>
@@ -18170,7 +18335,7 @@
       <c r="G586" s="4"/>
       <c r="H586" s="4"/>
       <c r="I586" s="4"/>
-      <c r="J586" s="4"/>
+      <c r="J586" s="7"/>
       <c r="K586" s="4"/>
       <c r="L586" s="4"/>
       <c r="M586" s="4"/>
@@ -18200,7 +18365,7 @@
       <c r="G587" s="4"/>
       <c r="H587" s="4"/>
       <c r="I587" s="4"/>
-      <c r="J587" s="4"/>
+      <c r="J587" s="7"/>
       <c r="K587" s="4"/>
       <c r="L587" s="4"/>
       <c r="M587" s="4"/>
@@ -18230,7 +18395,7 @@
       <c r="G588" s="4"/>
       <c r="H588" s="4"/>
       <c r="I588" s="4"/>
-      <c r="J588" s="4"/>
+      <c r="J588" s="7"/>
       <c r="K588" s="4"/>
       <c r="L588" s="4"/>
       <c r="M588" s="4"/>
@@ -18260,7 +18425,7 @@
       <c r="G589" s="4"/>
       <c r="H589" s="4"/>
       <c r="I589" s="4"/>
-      <c r="J589" s="4"/>
+      <c r="J589" s="7"/>
       <c r="K589" s="4"/>
       <c r="L589" s="4"/>
       <c r="M589" s="4"/>
@@ -18290,7 +18455,7 @@
       <c r="G590" s="4"/>
       <c r="H590" s="4"/>
       <c r="I590" s="4"/>
-      <c r="J590" s="4"/>
+      <c r="J590" s="7"/>
       <c r="K590" s="4"/>
       <c r="L590" s="4"/>
       <c r="M590" s="4"/>
@@ -18320,7 +18485,7 @@
       <c r="G591" s="4"/>
       <c r="H591" s="4"/>
       <c r="I591" s="4"/>
-      <c r="J591" s="4"/>
+      <c r="J591" s="7"/>
       <c r="K591" s="4"/>
       <c r="L591" s="4"/>
       <c r="M591" s="4"/>
@@ -18350,7 +18515,7 @@
       <c r="G592" s="4"/>
       <c r="H592" s="4"/>
       <c r="I592" s="4"/>
-      <c r="J592" s="4"/>
+      <c r="J592" s="7"/>
       <c r="K592" s="4"/>
       <c r="L592" s="4"/>
       <c r="M592" s="4"/>
@@ -18380,7 +18545,7 @@
       <c r="G593" s="4"/>
       <c r="H593" s="4"/>
       <c r="I593" s="4"/>
-      <c r="J593" s="4"/>
+      <c r="J593" s="7"/>
       <c r="K593" s="4"/>
       <c r="L593" s="4"/>
       <c r="M593" s="4"/>
@@ -18410,7 +18575,7 @@
       <c r="G594" s="4"/>
       <c r="H594" s="4"/>
       <c r="I594" s="4"/>
-      <c r="J594" s="4"/>
+      <c r="J594" s="7"/>
       <c r="K594" s="4"/>
       <c r="L594" s="4"/>
       <c r="M594" s="4"/>
@@ -18440,7 +18605,7 @@
       <c r="G595" s="4"/>
       <c r="H595" s="4"/>
       <c r="I595" s="4"/>
-      <c r="J595" s="4"/>
+      <c r="J595" s="7"/>
       <c r="K595" s="4"/>
       <c r="L595" s="4"/>
       <c r="M595" s="4"/>
@@ -18470,7 +18635,7 @@
       <c r="G596" s="4"/>
       <c r="H596" s="4"/>
       <c r="I596" s="4"/>
-      <c r="J596" s="4"/>
+      <c r="J596" s="7"/>
       <c r="K596" s="4"/>
       <c r="L596" s="4"/>
       <c r="M596" s="4"/>
@@ -18500,7 +18665,7 @@
       <c r="G597" s="4"/>
       <c r="H597" s="4"/>
       <c r="I597" s="4"/>
-      <c r="J597" s="4"/>
+      <c r="J597" s="7"/>
       <c r="K597" s="4"/>
       <c r="L597" s="4"/>
       <c r="M597" s="4"/>
@@ -18530,7 +18695,7 @@
       <c r="G598" s="4"/>
       <c r="H598" s="4"/>
       <c r="I598" s="4"/>
-      <c r="J598" s="4"/>
+      <c r="J598" s="7"/>
       <c r="K598" s="4"/>
       <c r="L598" s="4"/>
       <c r="M598" s="4"/>
@@ -18560,7 +18725,7 @@
       <c r="G599" s="4"/>
       <c r="H599" s="4"/>
       <c r="I599" s="4"/>
-      <c r="J599" s="4"/>
+      <c r="J599" s="7"/>
       <c r="K599" s="4"/>
       <c r="L599" s="4"/>
       <c r="M599" s="4"/>
@@ -18590,7 +18755,7 @@
       <c r="G600" s="4"/>
       <c r="H600" s="4"/>
       <c r="I600" s="4"/>
-      <c r="J600" s="4"/>
+      <c r="J600" s="7"/>
       <c r="K600" s="4"/>
       <c r="L600" s="4"/>
       <c r="M600" s="4"/>
@@ -18620,7 +18785,7 @@
       <c r="G601" s="4"/>
       <c r="H601" s="4"/>
       <c r="I601" s="4"/>
-      <c r="J601" s="4"/>
+      <c r="J601" s="7"/>
       <c r="K601" s="4"/>
       <c r="L601" s="4"/>
       <c r="M601" s="4"/>
@@ -18650,7 +18815,7 @@
       <c r="G602" s="4"/>
       <c r="H602" s="4"/>
       <c r="I602" s="4"/>
-      <c r="J602" s="4"/>
+      <c r="J602" s="7"/>
       <c r="K602" s="4"/>
       <c r="L602" s="4"/>
       <c r="M602" s="4"/>
@@ -18680,7 +18845,7 @@
       <c r="G603" s="4"/>
       <c r="H603" s="4"/>
       <c r="I603" s="4"/>
-      <c r="J603" s="4"/>
+      <c r="J603" s="7"/>
       <c r="K603" s="4"/>
       <c r="L603" s="4"/>
       <c r="M603" s="4"/>
@@ -18710,7 +18875,7 @@
       <c r="G604" s="4"/>
       <c r="H604" s="4"/>
       <c r="I604" s="4"/>
-      <c r="J604" s="4"/>
+      <c r="J604" s="7"/>
       <c r="K604" s="4"/>
       <c r="L604" s="4"/>
       <c r="M604" s="4"/>
@@ -18740,7 +18905,7 @@
       <c r="G605" s="4"/>
       <c r="H605" s="4"/>
       <c r="I605" s="4"/>
-      <c r="J605" s="4"/>
+      <c r="J605" s="7"/>
       <c r="K605" s="4"/>
       <c r="L605" s="4"/>
       <c r="M605" s="4"/>
@@ -18770,7 +18935,7 @@
       <c r="G606" s="4"/>
       <c r="H606" s="4"/>
       <c r="I606" s="4"/>
-      <c r="J606" s="4"/>
+      <c r="J606" s="7"/>
       <c r="K606" s="4"/>
       <c r="L606" s="4"/>
       <c r="M606" s="4"/>
@@ -18800,7 +18965,7 @@
       <c r="G607" s="4"/>
       <c r="H607" s="4"/>
       <c r="I607" s="4"/>
-      <c r="J607" s="4"/>
+      <c r="J607" s="7"/>
       <c r="K607" s="4"/>
       <c r="L607" s="4"/>
       <c r="M607" s="4"/>
@@ -18830,7 +18995,7 @@
       <c r="G608" s="4"/>
       <c r="H608" s="4"/>
       <c r="I608" s="4"/>
-      <c r="J608" s="4"/>
+      <c r="J608" s="7"/>
       <c r="K608" s="4"/>
       <c r="L608" s="4"/>
       <c r="M608" s="4"/>
@@ -18860,7 +19025,7 @@
       <c r="G609" s="4"/>
       <c r="H609" s="4"/>
       <c r="I609" s="4"/>
-      <c r="J609" s="4"/>
+      <c r="J609" s="7"/>
       <c r="K609" s="4"/>
       <c r="L609" s="4"/>
       <c r="M609" s="4"/>
@@ -18890,7 +19055,7 @@
       <c r="G610" s="4"/>
       <c r="H610" s="4"/>
       <c r="I610" s="4"/>
-      <c r="J610" s="4"/>
+      <c r="J610" s="7"/>
       <c r="K610" s="4"/>
       <c r="L610" s="4"/>
       <c r="M610" s="4"/>
@@ -18920,7 +19085,7 @@
       <c r="G611" s="4"/>
       <c r="H611" s="4"/>
       <c r="I611" s="4"/>
-      <c r="J611" s="4"/>
+      <c r="J611" s="7"/>
       <c r="K611" s="4"/>
       <c r="L611" s="4"/>
       <c r="M611" s="4"/>
@@ -18950,7 +19115,7 @@
       <c r="G612" s="4"/>
       <c r="H612" s="4"/>
       <c r="I612" s="4"/>
-      <c r="J612" s="4"/>
+      <c r="J612" s="7"/>
       <c r="K612" s="4"/>
       <c r="L612" s="4"/>
       <c r="M612" s="4"/>
@@ -18980,7 +19145,7 @@
       <c r="G613" s="4"/>
       <c r="H613" s="4"/>
       <c r="I613" s="4"/>
-      <c r="J613" s="4"/>
+      <c r="J613" s="7"/>
       <c r="K613" s="4"/>
       <c r="L613" s="4"/>
       <c r="M613" s="4"/>
@@ -19010,7 +19175,7 @@
       <c r="G614" s="4"/>
       <c r="H614" s="4"/>
       <c r="I614" s="4"/>
-      <c r="J614" s="4"/>
+      <c r="J614" s="7"/>
       <c r="K614" s="4"/>
       <c r="L614" s="4"/>
       <c r="M614" s="4"/>
@@ -19040,7 +19205,7 @@
       <c r="G615" s="4"/>
       <c r="H615" s="4"/>
       <c r="I615" s="4"/>
-      <c r="J615" s="4"/>
+      <c r="J615" s="7"/>
       <c r="K615" s="4"/>
       <c r="L615" s="4"/>
       <c r="M615" s="4"/>
@@ -19070,7 +19235,7 @@
       <c r="G616" s="4"/>
       <c r="H616" s="4"/>
       <c r="I616" s="4"/>
-      <c r="J616" s="4"/>
+      <c r="J616" s="7"/>
       <c r="K616" s="4"/>
       <c r="L616" s="4"/>
       <c r="M616" s="4"/>
@@ -19100,7 +19265,7 @@
       <c r="G617" s="4"/>
       <c r="H617" s="4"/>
       <c r="I617" s="4"/>
-      <c r="J617" s="4"/>
+      <c r="J617" s="7"/>
       <c r="K617" s="4"/>
       <c r="L617" s="4"/>
       <c r="M617" s="4"/>
@@ -19130,7 +19295,7 @@
       <c r="G618" s="4"/>
       <c r="H618" s="4"/>
       <c r="I618" s="4"/>
-      <c r="J618" s="4"/>
+      <c r="J618" s="7"/>
       <c r="K618" s="4"/>
       <c r="L618" s="4"/>
       <c r="M618" s="4"/>
@@ -19160,7 +19325,7 @@
       <c r="G619" s="4"/>
       <c r="H619" s="4"/>
       <c r="I619" s="4"/>
-      <c r="J619" s="4"/>
+      <c r="J619" s="7"/>
       <c r="K619" s="4"/>
       <c r="L619" s="4"/>
       <c r="M619" s="4"/>
@@ -19190,7 +19355,7 @@
       <c r="G620" s="4"/>
       <c r="H620" s="4"/>
       <c r="I620" s="4"/>
-      <c r="J620" s="4"/>
+      <c r="J620" s="7"/>
       <c r="K620" s="4"/>
       <c r="L620" s="4"/>
       <c r="M620" s="4"/>
@@ -19220,7 +19385,7 @@
       <c r="G621" s="4"/>
       <c r="H621" s="4"/>
       <c r="I621" s="4"/>
-      <c r="J621" s="4"/>
+      <c r="J621" s="7"/>
       <c r="K621" s="4"/>
       <c r="L621" s="4"/>
       <c r="M621" s="4"/>
@@ -19250,7 +19415,7 @@
       <c r="G622" s="4"/>
       <c r="H622" s="4"/>
       <c r="I622" s="4"/>
-      <c r="J622" s="4"/>
+      <c r="J622" s="7"/>
       <c r="K622" s="4"/>
       <c r="L622" s="4"/>
       <c r="M622" s="4"/>
@@ -19280,7 +19445,7 @@
       <c r="G623" s="4"/>
       <c r="H623" s="4"/>
       <c r="I623" s="4"/>
-      <c r="J623" s="4"/>
+      <c r="J623" s="7"/>
       <c r="K623" s="4"/>
       <c r="L623" s="4"/>
       <c r="M623" s="4"/>
@@ -19310,7 +19475,7 @@
       <c r="G624" s="4"/>
       <c r="H624" s="4"/>
       <c r="I624" s="4"/>
-      <c r="J624" s="4"/>
+      <c r="J624" s="7"/>
       <c r="K624" s="4"/>
       <c r="L624" s="4"/>
       <c r="M624" s="4"/>
@@ -19340,7 +19505,7 @@
       <c r="G625" s="4"/>
       <c r="H625" s="4"/>
       <c r="I625" s="4"/>
-      <c r="J625" s="4"/>
+      <c r="J625" s="7"/>
       <c r="K625" s="4"/>
       <c r="L625" s="4"/>
       <c r="M625" s="4"/>
@@ -19370,7 +19535,7 @@
       <c r="G626" s="4"/>
       <c r="H626" s="4"/>
       <c r="I626" s="4"/>
-      <c r="J626" s="4"/>
+      <c r="J626" s="7"/>
       <c r="K626" s="4"/>
       <c r="L626" s="4"/>
       <c r="M626" s="4"/>
@@ -19400,7 +19565,7 @@
       <c r="G627" s="4"/>
       <c r="H627" s="4"/>
       <c r="I627" s="4"/>
-      <c r="J627" s="4"/>
+      <c r="J627" s="7"/>
       <c r="K627" s="4"/>
       <c r="L627" s="4"/>
       <c r="M627" s="4"/>
@@ -19430,7 +19595,7 @@
       <c r="G628" s="4"/>
       <c r="H628" s="4"/>
       <c r="I628" s="4"/>
-      <c r="J628" s="4"/>
+      <c r="J628" s="7"/>
       <c r="K628" s="4"/>
       <c r="L628" s="4"/>
       <c r="M628" s="4"/>
@@ -19460,7 +19625,7 @@
       <c r="G629" s="4"/>
       <c r="H629" s="4"/>
       <c r="I629" s="4"/>
-      <c r="J629" s="4"/>
+      <c r="J629" s="7"/>
       <c r="K629" s="4"/>
       <c r="L629" s="4"/>
       <c r="M629" s="4"/>
@@ -19490,7 +19655,7 @@
       <c r="G630" s="4"/>
       <c r="H630" s="4"/>
       <c r="I630" s="4"/>
-      <c r="J630" s="4"/>
+      <c r="J630" s="7"/>
       <c r="K630" s="4"/>
       <c r="L630" s="4"/>
       <c r="M630" s="4"/>
@@ -19520,7 +19685,7 @@
       <c r="G631" s="4"/>
       <c r="H631" s="4"/>
       <c r="I631" s="4"/>
-      <c r="J631" s="4"/>
+      <c r="J631" s="7"/>
       <c r="K631" s="4"/>
       <c r="L631" s="4"/>
       <c r="M631" s="4"/>
@@ -19550,7 +19715,7 @@
       <c r="G632" s="4"/>
       <c r="H632" s="4"/>
       <c r="I632" s="4"/>
-      <c r="J632" s="4"/>
+      <c r="J632" s="7"/>
       <c r="K632" s="4"/>
       <c r="L632" s="4"/>
       <c r="M632" s="4"/>
@@ -19580,7 +19745,7 @@
       <c r="G633" s="4"/>
       <c r="H633" s="4"/>
       <c r="I633" s="4"/>
-      <c r="J633" s="4"/>
+      <c r="J633" s="7"/>
       <c r="K633" s="4"/>
       <c r="L633" s="4"/>
       <c r="M633" s="4"/>
@@ -19610,7 +19775,7 @@
       <c r="G634" s="4"/>
       <c r="H634" s="4"/>
       <c r="I634" s="4"/>
-      <c r="J634" s="4"/>
+      <c r="J634" s="7"/>
       <c r="K634" s="4"/>
       <c r="L634" s="4"/>
       <c r="M634" s="4"/>
@@ -19640,7 +19805,7 @@
       <c r="G635" s="4"/>
       <c r="H635" s="4"/>
       <c r="I635" s="4"/>
-      <c r="J635" s="4"/>
+      <c r="J635" s="7"/>
       <c r="K635" s="4"/>
       <c r="L635" s="4"/>
       <c r="M635" s="4"/>
@@ -19670,7 +19835,7 @@
       <c r="G636" s="4"/>
       <c r="H636" s="4"/>
       <c r="I636" s="4"/>
-      <c r="J636" s="4"/>
+      <c r="J636" s="7"/>
       <c r="K636" s="4"/>
       <c r="L636" s="4"/>
       <c r="M636" s="4"/>
@@ -19700,7 +19865,7 @@
       <c r="G637" s="4"/>
       <c r="H637" s="4"/>
       <c r="I637" s="4"/>
-      <c r="J637" s="4"/>
+      <c r="J637" s="7"/>
       <c r="K637" s="4"/>
       <c r="L637" s="4"/>
       <c r="M637" s="4"/>
@@ -19730,7 +19895,7 @@
       <c r="G638" s="4"/>
       <c r="H638" s="4"/>
       <c r="I638" s="4"/>
-      <c r="J638" s="4"/>
+      <c r="J638" s="7"/>
       <c r="K638" s="4"/>
       <c r="L638" s="4"/>
       <c r="M638" s="4"/>
@@ -19760,7 +19925,7 @@
       <c r="G639" s="4"/>
       <c r="H639" s="4"/>
       <c r="I639" s="4"/>
-      <c r="J639" s="4"/>
+      <c r="J639" s="7"/>
       <c r="K639" s="4"/>
       <c r="L639" s="4"/>
       <c r="M639" s="4"/>
@@ -19790,7 +19955,7 @@
       <c r="G640" s="4"/>
       <c r="H640" s="4"/>
       <c r="I640" s="4"/>
-      <c r="J640" s="4"/>
+      <c r="J640" s="7"/>
       <c r="K640" s="4"/>
       <c r="L640" s="4"/>
       <c r="M640" s="4"/>
@@ -19820,7 +19985,7 @@
       <c r="G641" s="4"/>
       <c r="H641" s="4"/>
       <c r="I641" s="4"/>
-      <c r="J641" s="4"/>
+      <c r="J641" s="7"/>
       <c r="K641" s="4"/>
       <c r="L641" s="4"/>
       <c r="M641" s="4"/>
@@ -19850,7 +20015,7 @@
       <c r="G642" s="4"/>
       <c r="H642" s="4"/>
       <c r="I642" s="4"/>
-      <c r="J642" s="4"/>
+      <c r="J642" s="7"/>
       <c r="K642" s="4"/>
       <c r="L642" s="4"/>
       <c r="M642" s="4"/>
@@ -19880,7 +20045,7 @@
       <c r="G643" s="4"/>
       <c r="H643" s="4"/>
       <c r="I643" s="4"/>
-      <c r="J643" s="4"/>
+      <c r="J643" s="7"/>
       <c r="K643" s="4"/>
       <c r="L643" s="4"/>
       <c r="M643" s="4"/>
@@ -19910,7 +20075,7 @@
       <c r="G644" s="4"/>
       <c r="H644" s="4"/>
       <c r="I644" s="4"/>
-      <c r="J644" s="4"/>
+      <c r="J644" s="7"/>
       <c r="K644" s="4"/>
       <c r="L644" s="4"/>
       <c r="M644" s="4"/>
@@ -19940,7 +20105,7 @@
       <c r="G645" s="4"/>
       <c r="H645" s="4"/>
       <c r="I645" s="4"/>
-      <c r="J645" s="4"/>
+      <c r="J645" s="7"/>
       <c r="K645" s="4"/>
       <c r="L645" s="4"/>
       <c r="M645" s="4"/>
@@ -19970,7 +20135,7 @@
       <c r="G646" s="4"/>
       <c r="H646" s="4"/>
       <c r="I646" s="4"/>
-      <c r="J646" s="4"/>
+      <c r="J646" s="7"/>
       <c r="K646" s="4"/>
       <c r="L646" s="4"/>
       <c r="M646" s="4"/>
@@ -20000,7 +20165,7 @@
       <c r="G647" s="4"/>
       <c r="H647" s="4"/>
       <c r="I647" s="4"/>
-      <c r="J647" s="4"/>
+      <c r="J647" s="7"/>
       <c r="K647" s="4"/>
       <c r="L647" s="4"/>
       <c r="M647" s="4"/>
@@ -20030,7 +20195,7 @@
       <c r="G648" s="4"/>
       <c r="H648" s="4"/>
       <c r="I648" s="4"/>
-      <c r="J648" s="4"/>
+      <c r="J648" s="7"/>
       <c r="K648" s="4"/>
       <c r="L648" s="4"/>
       <c r="M648" s="4"/>
@@ -20060,7 +20225,7 @@
       <c r="G649" s="4"/>
       <c r="H649" s="4"/>
       <c r="I649" s="4"/>
-      <c r="J649" s="4"/>
+      <c r="J649" s="7"/>
       <c r="K649" s="4"/>
       <c r="L649" s="4"/>
       <c r="M649" s="4"/>
@@ -20090,7 +20255,7 @@
       <c r="G650" s="4"/>
       <c r="H650" s="4"/>
       <c r="I650" s="4"/>
-      <c r="J650" s="4"/>
+      <c r="J650" s="7"/>
       <c r="K650" s="4"/>
       <c r="L650" s="4"/>
       <c r="M650" s="4"/>
@@ -20120,7 +20285,7 @@
       <c r="G651" s="4"/>
       <c r="H651" s="4"/>
       <c r="I651" s="4"/>
-      <c r="J651" s="4"/>
+      <c r="J651" s="7"/>
       <c r="K651" s="4"/>
       <c r="L651" s="4"/>
       <c r="M651" s="4"/>
@@ -20150,7 +20315,7 @@
       <c r="G652" s="4"/>
       <c r="H652" s="4"/>
       <c r="I652" s="4"/>
-      <c r="J652" s="4"/>
+      <c r="J652" s="7"/>
       <c r="K652" s="4"/>
       <c r="L652" s="4"/>
       <c r="M652" s="4"/>
@@ -20180,7 +20345,7 @@
       <c r="G653" s="4"/>
       <c r="H653" s="4"/>
       <c r="I653" s="4"/>
-      <c r="J653" s="4"/>
+      <c r="J653" s="7"/>
       <c r="K653" s="4"/>
       <c r="L653" s="4"/>
       <c r="M653" s="4"/>
@@ -20210,7 +20375,7 @@
       <c r="G654" s="4"/>
       <c r="H654" s="4"/>
       <c r="I654" s="4"/>
-      <c r="J654" s="4"/>
+      <c r="J654" s="7"/>
       <c r="K654" s="4"/>
       <c r="L654" s="4"/>
       <c r="M654" s="4"/>
@@ -20240,7 +20405,7 @@
       <c r="G655" s="4"/>
       <c r="H655" s="4"/>
       <c r="I655" s="4"/>
-      <c r="J655" s="4"/>
+      <c r="J655" s="7"/>
       <c r="K655" s="4"/>
       <c r="L655" s="4"/>
       <c r="M655" s="4"/>
@@ -20270,7 +20435,7 @@
       <c r="G656" s="4"/>
       <c r="H656" s="4"/>
       <c r="I656" s="4"/>
-      <c r="J656" s="4"/>
+      <c r="J656" s="7"/>
       <c r="K656" s="4"/>
       <c r="L656" s="4"/>
       <c r="M656" s="4"/>
@@ -20300,7 +20465,7 @@
       <c r="G657" s="4"/>
       <c r="H657" s="4"/>
       <c r="I657" s="4"/>
-      <c r="J657" s="4"/>
+      <c r="J657" s="7"/>
       <c r="K657" s="4"/>
       <c r="L657" s="4"/>
       <c r="M657" s="4"/>
@@ -20330,7 +20495,7 @@
       <c r="G658" s="4"/>
       <c r="H658" s="4"/>
       <c r="I658" s="4"/>
-      <c r="J658" s="4"/>
+      <c r="J658" s="7"/>
       <c r="K658" s="4"/>
       <c r="L658" s="4"/>
       <c r="M658" s="4"/>
@@ -20360,7 +20525,7 @@
       <c r="G659" s="4"/>
       <c r="H659" s="4"/>
       <c r="I659" s="4"/>
-      <c r="J659" s="4"/>
+      <c r="J659" s="7"/>
       <c r="K659" s="4"/>
       <c r="L659" s="4"/>
       <c r="M659" s="4"/>
@@ -20390,7 +20555,7 @@
       <c r="G660" s="4"/>
       <c r="H660" s="4"/>
       <c r="I660" s="4"/>
-      <c r="J660" s="4"/>
+      <c r="J660" s="7"/>
       <c r="K660" s="4"/>
       <c r="L660" s="4"/>
       <c r="M660" s="4"/>
@@ -20420,7 +20585,7 @@
       <c r="G661" s="4"/>
       <c r="H661" s="4"/>
       <c r="I661" s="4"/>
-      <c r="J661" s="4"/>
+      <c r="J661" s="7"/>
       <c r="K661" s="4"/>
       <c r="L661" s="4"/>
       <c r="M661" s="4"/>
@@ -20450,7 +20615,7 @@
       <c r="G662" s="4"/>
       <c r="H662" s="4"/>
       <c r="I662" s="4"/>
-      <c r="J662" s="4"/>
+      <c r="J662" s="7"/>
       <c r="K662" s="4"/>
       <c r="L662" s="4"/>
       <c r="M662" s="4"/>
@@ -20480,7 +20645,7 @@
       <c r="G663" s="4"/>
       <c r="H663" s="4"/>
       <c r="I663" s="4"/>
-      <c r="J663" s="4"/>
+      <c r="J663" s="7"/>
       <c r="K663" s="4"/>
       <c r="L663" s="4"/>
       <c r="M663" s="4"/>
@@ -20510,7 +20675,7 @@
       <c r="G664" s="4"/>
       <c r="H664" s="4"/>
       <c r="I664" s="4"/>
-      <c r="J664" s="4"/>
+      <c r="J664" s="7"/>
       <c r="K664" s="4"/>
       <c r="L664" s="4"/>
       <c r="M664" s="4"/>
@@ -20540,7 +20705,7 @@
       <c r="G665" s="4"/>
       <c r="H665" s="4"/>
       <c r="I665" s="4"/>
-      <c r="J665" s="4"/>
+      <c r="J665" s="7"/>
       <c r="K665" s="4"/>
       <c r="L665" s="4"/>
       <c r="M665" s="4"/>
@@ -20570,7 +20735,7 @@
       <c r="G666" s="4"/>
       <c r="H666" s="4"/>
       <c r="I666" s="4"/>
-      <c r="J666" s="4"/>
+      <c r="J666" s="7"/>
       <c r="K666" s="4"/>
       <c r="L666" s="4"/>
       <c r="M666" s="4"/>
@@ -20600,7 +20765,7 @@
       <c r="G667" s="4"/>
       <c r="H667" s="4"/>
       <c r="I667" s="4"/>
-      <c r="J667" s="4"/>
+      <c r="J667" s="7"/>
       <c r="K667" s="4"/>
       <c r="L667" s="4"/>
       <c r="M667" s="4"/>
@@ -20630,7 +20795,7 @@
       <c r="G668" s="4"/>
       <c r="H668" s="4"/>
       <c r="I668" s="4"/>
-      <c r="J668" s="4"/>
+      <c r="J668" s="7"/>
       <c r="K668" s="4"/>
       <c r="L668" s="4"/>
       <c r="M668" s="4"/>
@@ -20660,7 +20825,7 @@
       <c r="G669" s="4"/>
       <c r="H669" s="4"/>
       <c r="I669" s="4"/>
-      <c r="J669" s="4"/>
+      <c r="J669" s="7"/>
       <c r="K669" s="4"/>
       <c r="L669" s="4"/>
       <c r="M669" s="4"/>
@@ -20690,7 +20855,7 @@
       <c r="G670" s="4"/>
       <c r="H670" s="4"/>
       <c r="I670" s="4"/>
-      <c r="J670" s="4"/>
+      <c r="J670" s="7"/>
       <c r="K670" s="4"/>
       <c r="L670" s="4"/>
       <c r="M670" s="4"/>
@@ -20720,7 +20885,7 @@
       <c r="G671" s="4"/>
       <c r="H671" s="4"/>
       <c r="I671" s="4"/>
-      <c r="J671" s="4"/>
+      <c r="J671" s="7"/>
       <c r="K671" s="4"/>
       <c r="L671" s="4"/>
       <c r="M671" s="4"/>
@@ -20750,7 +20915,7 @@
       <c r="G672" s="4"/>
       <c r="H672" s="4"/>
       <c r="I672" s="4"/>
-      <c r="J672" s="4"/>
+      <c r="J672" s="7"/>
       <c r="K672" s="4"/>
       <c r="L672" s="4"/>
       <c r="M672" s="4"/>
@@ -20780,7 +20945,7 @@
       <c r="G673" s="4"/>
       <c r="H673" s="4"/>
       <c r="I673" s="4"/>
-      <c r="J673" s="4"/>
+      <c r="J673" s="7"/>
       <c r="K673" s="4"/>
       <c r="L673" s="4"/>
       <c r="M673" s="4"/>
@@ -20810,7 +20975,7 @@
       <c r="G674" s="4"/>
       <c r="H674" s="4"/>
       <c r="I674" s="4"/>
-      <c r="J674" s="4"/>
+      <c r="J674" s="7"/>
       <c r="K674" s="4"/>
       <c r="L674" s="4"/>
       <c r="M674" s="4"/>
@@ -20840,7 +21005,7 @@
       <c r="G675" s="4"/>
       <c r="H675" s="4"/>
       <c r="I675" s="4"/>
-      <c r="J675" s="4"/>
+      <c r="J675" s="7"/>
       <c r="K675" s="4"/>
       <c r="L675" s="4"/>
       <c r="M675" s="4"/>
@@ -20870,7 +21035,7 @@
       <c r="G676" s="4"/>
       <c r="H676" s="4"/>
       <c r="I676" s="4"/>
-      <c r="J676" s="4"/>
+      <c r="J676" s="7"/>
       <c r="K676" s="4"/>
       <c r="L676" s="4"/>
       <c r="M676" s="4"/>
@@ -20900,7 +21065,7 @@
       <c r="G677" s="4"/>
       <c r="H677" s="4"/>
       <c r="I677" s="4"/>
-      <c r="J677" s="4"/>
+      <c r="J677" s="7"/>
       <c r="K677" s="4"/>
       <c r="L677" s="4"/>
       <c r="M677" s="4"/>
@@ -20930,7 +21095,7 @@
       <c r="G678" s="4"/>
       <c r="H678" s="4"/>
       <c r="I678" s="4"/>
-      <c r="J678" s="4"/>
+      <c r="J678" s="7"/>
       <c r="K678" s="4"/>
       <c r="L678" s="4"/>
       <c r="M678" s="4"/>
@@ -20960,7 +21125,7 @@
       <c r="G679" s="4"/>
       <c r="H679" s="4"/>
       <c r="I679" s="4"/>
-      <c r="J679" s="4"/>
+      <c r="J679" s="7"/>
       <c r="K679" s="4"/>
       <c r="L679" s="4"/>
       <c r="M679" s="4"/>
@@ -20990,7 +21155,7 @@
       <c r="G680" s="4"/>
       <c r="H680" s="4"/>
       <c r="I680" s="4"/>
-      <c r="J680" s="4"/>
+      <c r="J680" s="7"/>
       <c r="K680" s="4"/>
       <c r="L680" s="4"/>
       <c r="M680" s="4"/>
@@ -21020,7 +21185,7 @@
       <c r="G681" s="4"/>
       <c r="H681" s="4"/>
       <c r="I681" s="4"/>
-      <c r="J681" s="4"/>
+      <c r="J681" s="7"/>
       <c r="K681" s="4"/>
       <c r="L681" s="4"/>
       <c r="M681" s="4"/>
@@ -21050,7 +21215,7 @@
       <c r="G682" s="4"/>
       <c r="H682" s="4"/>
       <c r="I682" s="4"/>
-      <c r="J682" s="4"/>
+      <c r="J682" s="7"/>
       <c r="K682" s="4"/>
       <c r="L682" s="4"/>
       <c r="M682" s="4"/>
@@ -21080,7 +21245,7 @@
       <c r="G683" s="4"/>
       <c r="H683" s="4"/>
       <c r="I683" s="4"/>
-      <c r="J683" s="4"/>
+      <c r="J683" s="7"/>
       <c r="K683" s="4"/>
       <c r="L683" s="4"/>
       <c r="M683" s="4"/>
@@ -21110,7 +21275,7 @@
       <c r="G684" s="4"/>
       <c r="H684" s="4"/>
       <c r="I684" s="4"/>
-      <c r="J684" s="4"/>
+      <c r="J684" s="7"/>
       <c r="K684" s="4"/>
       <c r="L684" s="4"/>
       <c r="M684" s="4"/>
@@ -21140,7 +21305,7 @@
       <c r="G685" s="4"/>
       <c r="H685" s="4"/>
       <c r="I685" s="4"/>
-      <c r="J685" s="4"/>
+      <c r="J685" s="7"/>
       <c r="K685" s="4"/>
       <c r="L685" s="4"/>
       <c r="M685" s="4"/>
@@ -21170,7 +21335,7 @@
       <c r="G686" s="4"/>
       <c r="H686" s="4"/>
       <c r="I686" s="4"/>
-      <c r="J686" s="4"/>
+      <c r="J686" s="7"/>
       <c r="K686" s="4"/>
       <c r="L686" s="4"/>
       <c r="M686" s="4"/>
@@ -21200,7 +21365,7 @@
       <c r="G687" s="4"/>
       <c r="H687" s="4"/>
       <c r="I687" s="4"/>
-      <c r="J687" s="4"/>
+      <c r="J687" s="7"/>
       <c r="K687" s="4"/>
       <c r="L687" s="4"/>
       <c r="M687" s="4"/>
@@ -21230,7 +21395,7 @@
       <c r="G688" s="4"/>
       <c r="H688" s="4"/>
       <c r="I688" s="4"/>
-      <c r="J688" s="4"/>
+      <c r="J688" s="7"/>
       <c r="K688" s="4"/>
       <c r="L688" s="4"/>
       <c r="M688" s="4"/>
@@ -21260,7 +21425,7 @@
       <c r="G689" s="4"/>
       <c r="H689" s="4"/>
       <c r="I689" s="4"/>
-      <c r="J689" s="4"/>
+      <c r="J689" s="7"/>
       <c r="K689" s="4"/>
       <c r="L689" s="4"/>
       <c r="M689" s="4"/>
@@ -21290,7 +21455,7 @@
       <c r="G690" s="4"/>
       <c r="H690" s="4"/>
       <c r="I690" s="4"/>
-      <c r="J690" s="4"/>
+      <c r="J690" s="7"/>
       <c r="K690" s="4"/>
       <c r="L690" s="4"/>
       <c r="M690" s="4"/>
@@ -21320,7 +21485,7 @@
       <c r="G691" s="4"/>
       <c r="H691" s="4"/>
       <c r="I691" s="4"/>
-      <c r="J691" s="4"/>
+      <c r="J691" s="7"/>
       <c r="K691" s="4"/>
       <c r="L691" s="4"/>
       <c r="M691" s="4"/>
@@ -21350,7 +21515,7 @@
       <c r="G692" s="4"/>
       <c r="H692" s="4"/>
       <c r="I692" s="4"/>
-      <c r="J692" s="4"/>
+      <c r="J692" s="7"/>
       <c r="K692" s="4"/>
       <c r="L692" s="4"/>
       <c r="M692" s="4"/>
@@ -21380,7 +21545,7 @@
       <c r="G693" s="4"/>
       <c r="H693" s="4"/>
       <c r="I693" s="4"/>
-      <c r="J693" s="4"/>
+      <c r="J693" s="7"/>
       <c r="K693" s="4"/>
       <c r="L693" s="4"/>
       <c r="M693" s="4"/>
@@ -21410,7 +21575,7 @@
       <c r="G694" s="4"/>
       <c r="H694" s="4"/>
       <c r="I694" s="4"/>
-      <c r="J694" s="4"/>
+      <c r="J694" s="7"/>
       <c r="K694" s="4"/>
       <c r="L694" s="4"/>
       <c r="M694" s="4"/>
@@ -21440,7 +21605,7 @@
       <c r="G695" s="4"/>
       <c r="H695" s="4"/>
       <c r="I695" s="4"/>
-      <c r="J695" s="4"/>
+      <c r="J695" s="7"/>
       <c r="K695" s="4"/>
       <c r="L695" s="4"/>
       <c r="M695" s="4"/>
@@ -21470,7 +21635,7 @@
       <c r="G696" s="4"/>
       <c r="H696" s="4"/>
       <c r="I696" s="4"/>
-      <c r="J696" s="4"/>
+      <c r="J696" s="7"/>
       <c r="K696" s="4"/>
       <c r="L696" s="4"/>
       <c r="M696" s="4"/>
@@ -21500,7 +21665,7 @@
       <c r="G697" s="4"/>
       <c r="H697" s="4"/>
       <c r="I697" s="4"/>
-      <c r="J697" s="4"/>
+      <c r="J697" s="7"/>
       <c r="K697" s="4"/>
       <c r="L697" s="4"/>
       <c r="M697" s="4"/>
@@ -21530,7 +21695,7 @@
       <c r="G698" s="4"/>
       <c r="H698" s="4"/>
       <c r="I698" s="4"/>
-      <c r="J698" s="4"/>
+      <c r="J698" s="7"/>
       <c r="K698" s="4"/>
       <c r="L698" s="4"/>
       <c r="M698" s="4"/>
@@ -21560,7 +21725,7 @@
       <c r="G699" s="4"/>
       <c r="H699" s="4"/>
       <c r="I699" s="4"/>
-      <c r="J699" s="4"/>
+      <c r="J699" s="7"/>
       <c r="K699" s="4"/>
       <c r="L699" s="4"/>
       <c r="M699" s="4"/>
@@ -21590,7 +21755,7 @@
       <c r="G700" s="4"/>
       <c r="H700" s="4"/>
       <c r="I700" s="4"/>
-      <c r="J700" s="4"/>
+      <c r="J700" s="7"/>
       <c r="K700" s="4"/>
       <c r="L700" s="4"/>
       <c r="M700" s="4"/>
@@ -21620,7 +21785,7 @@
       <c r="G701" s="4"/>
       <c r="H701" s="4"/>
       <c r="I701" s="4"/>
-      <c r="J701" s="4"/>
+      <c r="J701" s="7"/>
       <c r="K701" s="4"/>
       <c r="L701" s="4"/>
       <c r="M701" s="4"/>
@@ -21650,7 +21815,7 @@
       <c r="G702" s="4"/>
       <c r="H702" s="4"/>
       <c r="I702" s="4"/>
-      <c r="J702" s="4"/>
+      <c r="J702" s="7"/>
       <c r="K702" s="4"/>
       <c r="L702" s="4"/>
       <c r="M702" s="4"/>
@@ -21680,7 +21845,7 @@
       <c r="G703" s="4"/>
       <c r="H703" s="4"/>
       <c r="I703" s="4"/>
-      <c r="J703" s="4"/>
+      <c r="J703" s="7"/>
       <c r="K703" s="4"/>
       <c r="L703" s="4"/>
       <c r="M703" s="4"/>
@@ -21710,7 +21875,7 @@
       <c r="G704" s="4"/>
       <c r="H704" s="4"/>
       <c r="I704" s="4"/>
-      <c r="J704" s="4"/>
+      <c r="J704" s="7"/>
       <c r="K704" s="4"/>
       <c r="L704" s="4"/>
       <c r="M704" s="4"/>
@@ -21740,7 +21905,7 @@
       <c r="G705" s="4"/>
       <c r="H705" s="4"/>
       <c r="I705" s="4"/>
-      <c r="J705" s="4"/>
+      <c r="J705" s="7"/>
       <c r="K705" s="4"/>
       <c r="L705" s="4"/>
       <c r="M705" s="4"/>
@@ -21770,7 +21935,7 @@
       <c r="G706" s="4"/>
       <c r="H706" s="4"/>
       <c r="I706" s="4"/>
-      <c r="J706" s="4"/>
+      <c r="J706" s="7"/>
       <c r="K706" s="4"/>
       <c r="L706" s="4"/>
       <c r="M706" s="4"/>
@@ -21800,7 +21965,7 @@
       <c r="G707" s="4"/>
       <c r="H707" s="4"/>
       <c r="I707" s="4"/>
-      <c r="J707" s="4"/>
+      <c r="J707" s="7"/>
       <c r="K707" s="4"/>
       <c r="L707" s="4"/>
       <c r="M707" s="4"/>
@@ -21830,7 +21995,7 @@
       <c r="G708" s="4"/>
       <c r="H708" s="4"/>
       <c r="I708" s="4"/>
-      <c r="J708" s="4"/>
+      <c r="J708" s="7"/>
       <c r="K708" s="4"/>
       <c r="L708" s="4"/>
       <c r="M708" s="4"/>
@@ -21860,7 +22025,7 @@
       <c r="G709" s="4"/>
       <c r="H709" s="4"/>
       <c r="I709" s="4"/>
-      <c r="J709" s="4"/>
+      <c r="J709" s="7"/>
       <c r="K709" s="4"/>
       <c r="L709" s="4"/>
       <c r="M709" s="4"/>
@@ -21890,7 +22055,7 @@
       <c r="G710" s="4"/>
       <c r="H710" s="4"/>
       <c r="I710" s="4"/>
-      <c r="J710" s="4"/>
+      <c r="J710" s="7"/>
       <c r="K710" s="4"/>
       <c r="L710" s="4"/>
       <c r="M710" s="4"/>
@@ -21920,7 +22085,7 @@
       <c r="G711" s="4"/>
       <c r="H711" s="4"/>
       <c r="I711" s="4"/>
-      <c r="J711" s="4"/>
+      <c r="J711" s="7"/>
       <c r="K711" s="4"/>
       <c r="L711" s="4"/>
       <c r="M711" s="4"/>
@@ -21950,7 +22115,7 @@
       <c r="G712" s="4"/>
       <c r="H712" s="4"/>
       <c r="I712" s="4"/>
-      <c r="J712" s="4"/>
+      <c r="J712" s="7"/>
       <c r="K712" s="4"/>
       <c r="L712" s="4"/>
       <c r="M712" s="4"/>
@@ -21980,7 +22145,7 @@
       <c r="G713" s="4"/>
       <c r="H713" s="4"/>
       <c r="I713" s="4"/>
-      <c r="J713" s="4"/>
+      <c r="J713" s="7"/>
       <c r="K713" s="4"/>
       <c r="L713" s="4"/>
       <c r="M713" s="4"/>
@@ -22010,7 +22175,7 @@
       <c r="G714" s="4"/>
       <c r="H714" s="4"/>
       <c r="I714" s="4"/>
-      <c r="J714" s="4"/>
+      <c r="J714" s="7"/>
       <c r="K714" s="4"/>
       <c r="L714" s="4"/>
       <c r="M714" s="4"/>
@@ -22040,7 +22205,7 @@
       <c r="G715" s="4"/>
       <c r="H715" s="4"/>
       <c r="I715" s="4"/>
-      <c r="J715" s="4"/>
+      <c r="J715" s="7"/>
       <c r="K715" s="4"/>
       <c r="L715" s="4"/>
       <c r="M715" s="4"/>
@@ -22070,7 +22235,7 @@
       <c r="G716" s="4"/>
       <c r="H716" s="4"/>
       <c r="I716" s="4"/>
-      <c r="J716" s="4"/>
+      <c r="J716" s="7"/>
       <c r="K716" s="4"/>
       <c r="L716" s="4"/>
       <c r="M716" s="4"/>
@@ -22100,7 +22265,7 @@
       <c r="G717" s="4"/>
       <c r="H717" s="4"/>
       <c r="I717" s="4"/>
-      <c r="J717" s="4"/>
+      <c r="J717" s="7"/>
       <c r="K717" s="4"/>
       <c r="L717" s="4"/>
       <c r="M717" s="4"/>
@@ -22130,7 +22295,7 @@
       <c r="G718" s="4"/>
       <c r="H718" s="4"/>
       <c r="I718" s="4"/>
-      <c r="J718" s="4"/>
+      <c r="J718" s="7"/>
       <c r="K718" s="4"/>
       <c r="L718" s="4"/>
       <c r="M718" s="4"/>
@@ -22160,7 +22325,7 @@
       <c r="G719" s="4"/>
       <c r="H719" s="4"/>
       <c r="I719" s="4"/>
-      <c r="J719" s="4"/>
+      <c r="J719" s="7"/>
       <c r="K719" s="4"/>
       <c r="L719" s="4"/>
       <c r="M719" s="4"/>
@@ -22190,7 +22355,7 @@
       <c r="G720" s="4"/>
       <c r="H720" s="4"/>
       <c r="I720" s="4"/>
-      <c r="J720" s="4"/>
+      <c r="J720" s="7"/>
       <c r="K720" s="4"/>
       <c r="L720" s="4"/>
       <c r="M720" s="4"/>
@@ -22220,7 +22385,7 @@
       <c r="G721" s="4"/>
       <c r="H721" s="4"/>
       <c r="I721" s="4"/>
-      <c r="J721" s="4"/>
+      <c r="J721" s="7"/>
       <c r="K721" s="4"/>
       <c r="L721" s="4"/>
       <c r="M721" s="4"/>
@@ -22250,7 +22415,7 @@
       <c r="G722" s="4"/>
       <c r="H722" s="4"/>
       <c r="I722" s="4"/>
-      <c r="J722" s="4"/>
+      <c r="J722" s="7"/>
       <c r="K722" s="4"/>
       <c r="L722" s="4"/>
       <c r="M722" s="4"/>
@@ -22280,7 +22445,7 @@
       <c r="G723" s="4"/>
       <c r="H723" s="4"/>
       <c r="I723" s="4"/>
-      <c r="J723" s="4"/>
+      <c r="J723" s="7"/>
       <c r="K723" s="4"/>
       <c r="L723" s="4"/>
       <c r="M723" s="4"/>
@@ -22310,7 +22475,7 @@
       <c r="G724" s="4"/>
       <c r="H724" s="4"/>
       <c r="I724" s="4"/>
-      <c r="J724" s="4"/>
+      <c r="J724" s="7"/>
       <c r="K724" s="4"/>
       <c r="L724" s="4"/>
       <c r="M724" s="4"/>
@@ -22340,7 +22505,7 @@
       <c r="G725" s="4"/>
       <c r="H725" s="4"/>
       <c r="I725" s="4"/>
-      <c r="J725" s="4"/>
+      <c r="J725" s="7"/>
       <c r="K725" s="4"/>
       <c r="L725" s="4"/>
       <c r="M725" s="4"/>
@@ -22370,7 +22535,7 @@
       <c r="G726" s="4"/>
       <c r="H726" s="4"/>
       <c r="I726" s="4"/>
-      <c r="J726" s="4"/>
+      <c r="J726" s="7"/>
       <c r="K726" s="4"/>
       <c r="L726" s="4"/>
       <c r="M726" s="4"/>
@@ -22400,7 +22565,7 @@
       <c r="G727" s="4"/>
       <c r="H727" s="4"/>
       <c r="I727" s="4"/>
-      <c r="J727" s="4"/>
+      <c r="J727" s="7"/>
       <c r="K727" s="4"/>
       <c r="L727" s="4"/>
       <c r="M727" s="4"/>
@@ -22430,7 +22595,7 @@
       <c r="G728" s="4"/>
       <c r="H728" s="4"/>
       <c r="I728" s="4"/>
-      <c r="J728" s="4"/>
+      <c r="J728" s="7"/>
       <c r="K728" s="4"/>
       <c r="L728" s="4"/>
       <c r="M728" s="4"/>
@@ -22460,7 +22625,7 @@
       <c r="G729" s="4"/>
       <c r="H729" s="4"/>
       <c r="I729" s="4"/>
-      <c r="J729" s="4"/>
+      <c r="J729" s="7"/>
       <c r="K729" s="4"/>
       <c r="L729" s="4"/>
       <c r="M729" s="4"/>
@@ -22490,7 +22655,7 @@
       <c r="G730" s="4"/>
       <c r="H730" s="4"/>
       <c r="I730" s="4"/>
-      <c r="J730" s="4"/>
+      <c r="J730" s="7"/>
       <c r="K730" s="4"/>
       <c r="L730" s="4"/>
       <c r="M730" s="4"/>
@@ -22520,7 +22685,7 @@
       <c r="G731" s="4"/>
       <c r="H731" s="4"/>
       <c r="I731" s="4"/>
-      <c r="J731" s="4"/>
+      <c r="J731" s="7"/>
       <c r="K731" s="4"/>
       <c r="L731" s="4"/>
       <c r="M731" s="4"/>
@@ -22550,7 +22715,7 @@
       <c r="G732" s="4"/>
       <c r="H732" s="4"/>
       <c r="I732" s="4"/>
-      <c r="J732" s="4"/>
+      <c r="J732" s="7"/>
       <c r="K732" s="4"/>
       <c r="L732" s="4"/>
       <c r="M732" s="4"/>
@@ -22580,7 +22745,7 @@
       <c r="G733" s="4"/>
       <c r="H733" s="4"/>
       <c r="I733" s="4"/>
-      <c r="J733" s="4"/>
+      <c r="J733" s="7"/>
       <c r="K733" s="4"/>
       <c r="L733" s="4"/>
       <c r="M733" s="4"/>
@@ -22610,7 +22775,7 @@
       <c r="G734" s="4"/>
       <c r="H734" s="4"/>
       <c r="I734" s="4"/>
-      <c r="J734" s="4"/>
+      <c r="J734" s="7"/>
       <c r="K734" s="4"/>
       <c r="L734" s="4"/>
       <c r="M734" s="4"/>
@@ -22640,7 +22805,7 @@
       <c r="G735" s="4"/>
       <c r="H735" s="4"/>
       <c r="I735" s="4"/>
-      <c r="J735" s="4"/>
+      <c r="J735" s="7"/>
       <c r="K735" s="4"/>
       <c r="L735" s="4"/>
       <c r="M735" s="4"/>
@@ -22670,7 +22835,7 @@
       <c r="G736" s="4"/>
       <c r="H736" s="4"/>
       <c r="I736" s="4"/>
-      <c r="J736" s="4"/>
+      <c r="J736" s="7"/>
       <c r="K736" s="4"/>
       <c r="L736" s="4"/>
       <c r="M736" s="4"/>
@@ -22700,7 +22865,7 @@
       <c r="G737" s="4"/>
       <c r="H737" s="4"/>
       <c r="I737" s="4"/>
-      <c r="J737" s="4"/>
+      <c r="J737" s="7"/>
       <c r="K737" s="4"/>
       <c r="L737" s="4"/>
       <c r="M737" s="4"/>
@@ -22730,7 +22895,7 @@
       <c r="G738" s="4"/>
       <c r="H738" s="4"/>
       <c r="I738" s="4"/>
-      <c r="J738" s="4"/>
+      <c r="J738" s="7"/>
       <c r="K738" s="4"/>
       <c r="L738" s="4"/>
       <c r="M738" s="4"/>
@@ -22760,7 +22925,7 @@
       <c r="G739" s="4"/>
       <c r="H739" s="4"/>
       <c r="I739" s="4"/>
-      <c r="J739" s="4"/>
+      <c r="J739" s="7"/>
       <c r="K739" s="4"/>
       <c r="L739" s="4"/>
       <c r="M739" s="4"/>
@@ -22790,7 +22955,7 @@
       <c r="G740" s="4"/>
       <c r="H740" s="4"/>
       <c r="I740" s="4"/>
-      <c r="J740" s="4"/>
+      <c r="J740" s="7"/>
       <c r="K740" s="4"/>
       <c r="L740" s="4"/>
       <c r="M740" s="4"/>
@@ -22820,7 +22985,7 @@
       <c r="G741" s="4"/>
       <c r="H741" s="4"/>
       <c r="I741" s="4"/>
-      <c r="J741" s="4"/>
+      <c r="J741" s="7"/>
       <c r="K741" s="4"/>
       <c r="L741" s="4"/>
       <c r="M741" s="4"/>
@@ -22850,7 +23015,7 @@
       <c r="G742" s="4"/>
       <c r="H742" s="4"/>
       <c r="I742" s="4"/>
-      <c r="J742" s="4"/>
+      <c r="J742" s="7"/>
       <c r="K742" s="4"/>
       <c r="L742" s="4"/>
       <c r="M742" s="4"/>
@@ -22880,7 +23045,7 @@
       <c r="G743" s="4"/>
       <c r="H743" s="4"/>
       <c r="I743" s="4"/>
-      <c r="J743" s="4"/>
+      <c r="J743" s="7"/>
       <c r="K743" s="4"/>
       <c r="L743" s="4"/>
       <c r="M743" s="4"/>
@@ -22910,7 +23075,7 @@
       <c r="G744" s="4"/>
       <c r="H744" s="4"/>
       <c r="I744" s="4"/>
-      <c r="J744" s="4"/>
+      <c r="J744" s="7"/>
       <c r="K744" s="4"/>
       <c r="L744" s="4"/>
       <c r="M744" s="4"/>
@@ -22940,7 +23105,7 @@
       <c r="G745" s="4"/>
       <c r="H745" s="4"/>
       <c r="I745" s="4"/>
-      <c r="J745" s="4"/>
+      <c r="J745" s="7"/>
       <c r="K745" s="4"/>
       <c r="L745" s="4"/>
       <c r="M745" s="4"/>
@@ -22970,7 +23135,7 @@
       <c r="G746" s="4"/>
       <c r="H746" s="4"/>
       <c r="I746" s="4"/>
-      <c r="J746" s="4"/>
+      <c r="J746" s="7"/>
       <c r="K746" s="4"/>
       <c r="L746" s="4"/>
       <c r="M746" s="4"/>
@@ -23000,7 +23165,7 @@
       <c r="G747" s="4"/>
       <c r="H747" s="4"/>
       <c r="I747" s="4"/>
-      <c r="J747" s="4"/>
+      <c r="J747" s="7"/>
       <c r="K747" s="4"/>
       <c r="L747" s="4"/>
       <c r="M747" s="4"/>
@@ -23030,7 +23195,7 @@
       <c r="G748" s="4"/>
       <c r="H748" s="4"/>
       <c r="I748" s="4"/>
-      <c r="J748" s="4"/>
+      <c r="J748" s="7"/>
       <c r="K748" s="4"/>
       <c r="L748" s="4"/>
       <c r="M748" s="4"/>
@@ -23060,7 +23225,7 @@
       <c r="G749" s="4"/>
       <c r="H749" s="4"/>
       <c r="I749" s="4"/>
-      <c r="J749" s="4"/>
+      <c r="J749" s="7"/>
       <c r="K749" s="4"/>
       <c r="L749" s="4"/>
       <c r="M749" s="4"/>
@@ -23090,7 +23255,7 @@
       <c r="G750" s="4"/>
       <c r="H750" s="4"/>
       <c r="I750" s="4"/>
-      <c r="J750" s="4"/>
+      <c r="J750" s="7"/>
       <c r="K750" s="4"/>
       <c r="L750" s="4"/>
       <c r="M750" s="4"/>
@@ -23120,7 +23285,7 @@
       <c r="G751" s="4"/>
       <c r="H751" s="4"/>
       <c r="I751" s="4"/>
-      <c r="J751" s="4"/>
+      <c r="J751" s="7"/>
       <c r="K751" s="4"/>
       <c r="L751" s="4"/>
       <c r="M751" s="4"/>
@@ -23150,7 +23315,7 @@
       <c r="G752" s="4"/>
       <c r="H752" s="4"/>
       <c r="I752" s="4"/>
-      <c r="J752" s="4"/>
+      <c r="J752" s="7"/>
       <c r="K752" s="4"/>
       <c r="L752" s="4"/>
       <c r="M752" s="4"/>
@@ -23180,7 +23345,7 @@
       <c r="G753" s="4"/>
       <c r="H753" s="4"/>
       <c r="I753" s="4"/>
-      <c r="J753" s="4"/>
+      <c r="J753" s="7"/>
       <c r="K753" s="4"/>
       <c r="L753" s="4"/>
       <c r="M753" s="4"/>
@@ -23210,7 +23375,7 @@
       <c r="G754" s="4"/>
       <c r="H754" s="4"/>
       <c r="I754" s="4"/>
-      <c r="J754" s="4"/>
+      <c r="J754" s="7"/>
       <c r="K754" s="4"/>
       <c r="L754" s="4"/>
       <c r="M754" s="4"/>
@@ -23240,7 +23405,7 @@
       <c r="G755" s="4"/>
       <c r="H755" s="4"/>
       <c r="I755" s="4"/>
-      <c r="J755" s="4"/>
+      <c r="J755" s="7"/>
       <c r="K755" s="4"/>
       <c r="L755" s="4"/>
       <c r="M755" s="4"/>
@@ -23270,7 +23435,7 @@
       <c r="G756" s="4"/>
       <c r="H756" s="4"/>
       <c r="I756" s="4"/>
-      <c r="J756" s="4"/>
+      <c r="J756" s="7"/>
       <c r="K756" s="4"/>
       <c r="L756" s="4"/>
       <c r="M756" s="4"/>
@@ -23300,7 +23465,7 @@
       <c r="G757" s="4"/>
       <c r="H757" s="4"/>
       <c r="I757" s="4"/>
-      <c r="J757" s="4"/>
+      <c r="J757" s="7"/>
       <c r="K757" s="4"/>
       <c r="L757" s="4"/>
       <c r="M757" s="4"/>
@@ -23330,7 +23495,7 @@
       <c r="G758" s="4"/>
       <c r="H758" s="4"/>
       <c r="I758" s="4"/>
-      <c r="J758" s="4"/>
+      <c r="J758" s="7"/>
       <c r="K758" s="4"/>
       <c r="L758" s="4"/>
       <c r="M758" s="4"/>
@@ -23360,7 +23525,7 @@
       <c r="G759" s="4"/>
       <c r="H759" s="4"/>
       <c r="I759" s="4"/>
-      <c r="J759" s="4"/>
+      <c r="J759" s="7"/>
       <c r="K759" s="4"/>
       <c r="L759" s="4"/>
       <c r="M759" s="4"/>
@@ -23390,7 +23555,7 @@
       <c r="G760" s="4"/>
       <c r="H760" s="4"/>
       <c r="I760" s="4"/>
-      <c r="J760" s="4"/>
+      <c r="J760" s="7"/>
       <c r="K760" s="4"/>
       <c r="L760" s="4"/>
       <c r="M760" s="4"/>
@@ -23420,7 +23585,7 @@
       <c r="G761" s="4"/>
       <c r="H761" s="4"/>
       <c r="I761" s="4"/>
-      <c r="J761" s="4"/>
+      <c r="J761" s="7"/>
       <c r="K761" s="4"/>
       <c r="L761" s="4"/>
       <c r="M761" s="4"/>
@@ -23450,7 +23615,7 @@
       <c r="G762" s="4"/>
       <c r="H762" s="4"/>
       <c r="I762" s="4"/>
-      <c r="J762" s="4"/>
+      <c r="J762" s="7"/>
       <c r="K762" s="4"/>
       <c r="L762" s="4"/>
       <c r="M762" s="4"/>
@@ -23480,7 +23645,7 @@
       <c r="G763" s="4"/>
       <c r="H763" s="4"/>
       <c r="I763" s="4"/>
-      <c r="J763" s="4"/>
+      <c r="J763" s="7"/>
       <c r="K763" s="4"/>
       <c r="L763" s="4"/>
       <c r="M763" s="4"/>
@@ -23510,7 +23675,7 @@
       <c r="G764" s="4"/>
       <c r="H764" s="4"/>
       <c r="I764" s="4"/>
-      <c r="J764" s="4"/>
+      <c r="J764" s="7"/>
       <c r="K764" s="4"/>
       <c r="L764" s="4"/>
       <c r="M764" s="4"/>
@@ -23540,7 +23705,7 @@
       <c r="G765" s="4"/>
       <c r="H765" s="4"/>
       <c r="I765" s="4"/>
-      <c r="J765" s="4"/>
+      <c r="J765" s="7"/>
       <c r="K765" s="4"/>
       <c r="L765" s="4"/>
       <c r="M765" s="4"/>
@@ -23570,7 +23735,7 @@
       <c r="G766" s="4"/>
       <c r="H766" s="4"/>
       <c r="I766" s="4"/>
-      <c r="J766" s="4"/>
+      <c r="J766" s="7"/>
       <c r="K766" s="4"/>
       <c r="L766" s="4"/>
       <c r="M766" s="4"/>
@@ -23600,7 +23765,7 @@
       <c r="G767" s="4"/>
       <c r="H767" s="4"/>
       <c r="I767" s="4"/>
-      <c r="J767" s="4"/>
+      <c r="J767" s="7"/>
       <c r="K767" s="4"/>
       <c r="L767" s="4"/>
       <c r="M767" s="4"/>
@@ -23630,7 +23795,7 @@
       <c r="G768" s="4"/>
       <c r="H768" s="4"/>
       <c r="I768" s="4"/>
-      <c r="J768" s="4"/>
+      <c r="J768" s="7"/>
       <c r="K768" s="4"/>
       <c r="L768" s="4"/>
       <c r="M768" s="4"/>
@@ -23660,7 +23825,7 @@
       <c r="G769" s="4"/>
       <c r="H769" s="4"/>
       <c r="I769" s="4"/>
-      <c r="J769" s="4"/>
+      <c r="J769" s="7"/>
       <c r="K769" s="4"/>
       <c r="L769" s="4"/>
       <c r="M769" s="4"/>
@@ -23690,7 +23855,7 @@
       <c r="G770" s="4"/>
       <c r="H770" s="4"/>
       <c r="I770" s="4"/>
-      <c r="J770" s="4"/>
+      <c r="J770" s="7"/>
       <c r="K770" s="4"/>
       <c r="L770" s="4"/>
       <c r="M770" s="4"/>
@@ -23720,7 +23885,7 @@
       <c r="G771" s="4"/>
       <c r="H771" s="4"/>
       <c r="I771" s="4"/>
-      <c r="J771" s="4"/>
+      <c r="J771" s="7"/>
       <c r="K771" s="4"/>
       <c r="L771" s="4"/>
       <c r="M771" s="4"/>
@@ -23750,7 +23915,7 @@
       <c r="G772" s="4"/>
       <c r="H772" s="4"/>
       <c r="I772" s="4"/>
-      <c r="J772" s="4"/>
+      <c r="J772" s="7"/>
       <c r="K772" s="4"/>
       <c r="L772" s="4"/>
       <c r="M772" s="4"/>
@@ -23780,7 +23945,7 @@
       <c r="G773" s="4"/>
       <c r="H773" s="4"/>
       <c r="I773" s="4"/>
-      <c r="J773" s="4"/>
+      <c r="J773" s="7"/>
       <c r="K773" s="4"/>
       <c r="L773" s="4"/>
       <c r="M773" s="4"/>
@@ -23810,7 +23975,7 @@
       <c r="G774" s="4"/>
       <c r="H774" s="4"/>
       <c r="I774" s="4"/>
-      <c r="J774" s="4"/>
+      <c r="J774" s="7"/>
       <c r="K774" s="4"/>
       <c r="L774" s="4"/>
       <c r="M774" s="4"/>
@@ -23840,7 +24005,7 @@
       <c r="G775" s="4"/>
       <c r="H775" s="4"/>
       <c r="I775" s="4"/>
-      <c r="J775" s="4"/>
+      <c r="J775" s="7"/>
       <c r="K775" s="4"/>
       <c r="L775" s="4"/>
       <c r="M775" s="4"/>
@@ -23870,7 +24035,7 @@
       <c r="G776" s="4"/>
       <c r="H776" s="4"/>
       <c r="I776" s="4"/>
-      <c r="J776" s="4"/>
+      <c r="J776" s="7"/>
       <c r="K776" s="4"/>
       <c r="L776" s="4"/>
       <c r="M776" s="4"/>
@@ -23900,7 +24065,7 @@
       <c r="G777" s="4"/>
       <c r="H777" s="4"/>
       <c r="I777" s="4"/>
-      <c r="J777" s="4"/>
+      <c r="J777" s="7"/>
       <c r="K777" s="4"/>
       <c r="L777" s="4"/>
       <c r="M777" s="4"/>
@@ -23930,7 +24095,7 @@
       <c r="G778" s="4"/>
       <c r="H778" s="4"/>
       <c r="I778" s="4"/>
-      <c r="J778" s="4"/>
+      <c r="J778" s="7"/>
       <c r="K778" s="4"/>
       <c r="L778" s="4"/>
       <c r="M778" s="4"/>
@@ -23960,7 +24125,7 @@
       <c r="G779" s="4"/>
       <c r="H779" s="4"/>
       <c r="I779" s="4"/>
-      <c r="J779" s="4"/>
+      <c r="J779" s="7"/>
       <c r="K779" s="4"/>
       <c r="L779" s="4"/>
       <c r="M779" s="4"/>
@@ -23990,7 +24155,7 @@
       <c r="G780" s="4"/>
       <c r="H780" s="4"/>
       <c r="I780" s="4"/>
-      <c r="J780" s="4"/>
+      <c r="J780" s="7"/>
       <c r="K780" s="4"/>
       <c r="L780" s="4"/>
       <c r="M780" s="4"/>
@@ -24020,7 +24185,7 @@
       <c r="G781" s="4"/>
       <c r="H781" s="4"/>
       <c r="I781" s="4"/>
-      <c r="J781" s="4"/>
+      <c r="J781" s="7"/>
       <c r="K781" s="4"/>
       <c r="L781" s="4"/>
       <c r="M781" s="4"/>
@@ -24050,7 +24215,7 @@
       <c r="G782" s="4"/>
       <c r="H782" s="4"/>
       <c r="I782" s="4"/>
-      <c r="J782" s="4"/>
+      <c r="J782" s="7"/>
       <c r="K782" s="4"/>
       <c r="L782" s="4"/>
       <c r="M782" s="4"/>
@@ -24080,7 +24245,7 @@
       <c r="G783" s="4"/>
       <c r="H783" s="4"/>
       <c r="I783" s="4"/>
-      <c r="J783" s="4"/>
+      <c r="J783" s="7"/>
       <c r="K783" s="4"/>
       <c r="L783" s="4"/>
       <c r="M783" s="4"/>
@@ -24110,7 +24275,7 @@
       <c r="G784" s="4"/>
       <c r="H784" s="4"/>
       <c r="I784" s="4"/>
-      <c r="J784" s="4"/>
+      <c r="J784" s="7"/>
       <c r="K784" s="4"/>
       <c r="L784" s="4"/>
       <c r="M784" s="4"/>
@@ -24140,7 +24305,7 @@
       <c r="G785" s="4"/>
       <c r="H785" s="4"/>
       <c r="I785" s="4"/>
-      <c r="J785" s="4"/>
+      <c r="J785" s="7"/>
       <c r="K785" s="4"/>
       <c r="L785" s="4"/>
       <c r="M785" s="4"/>
@@ -24170,7 +24335,7 @@
       <c r="G786" s="4"/>
       <c r="H786" s="4"/>
       <c r="I786" s="4"/>
-      <c r="J786" s="4"/>
+      <c r="J786" s="7"/>
       <c r="K786" s="4"/>
       <c r="L786" s="4"/>
       <c r="M786" s="4"/>
@@ -24200,7 +24365,7 @@
       <c r="G787" s="4"/>
       <c r="H787" s="4"/>
       <c r="I787" s="4"/>
-      <c r="J787" s="4"/>
+      <c r="J787" s="7"/>
       <c r="K787" s="4"/>
       <c r="L787" s="4"/>
       <c r="M787" s="4"/>
@@ -24230,7 +24395,7 @@
       <c r="G788" s="4"/>
       <c r="H788" s="4"/>
       <c r="I788" s="4"/>
-      <c r="J788" s="4"/>
+      <c r="J788" s="7"/>
       <c r="K788" s="4"/>
       <c r="L788" s="4"/>
       <c r="M788" s="4"/>
@@ -24260,7 +24425,7 @@
       <c r="G789" s="4"/>
       <c r="H789" s="4"/>
       <c r="I789" s="4"/>
-      <c r="J789" s="4"/>
+      <c r="J789" s="7"/>
       <c r="K789" s="4"/>
       <c r="L789" s="4"/>
       <c r="M789" s="4"/>
@@ -24290,7 +24455,7 @@
       <c r="G790" s="4"/>
       <c r="H790" s="4"/>
       <c r="I790" s="4"/>
-      <c r="J790" s="4"/>
+      <c r="J790" s="7"/>
       <c r="K790" s="4"/>
       <c r="L790" s="4"/>
       <c r="M790" s="4"/>
@@ -24320,7 +24485,7 @@
       <c r="G791" s="4"/>
       <c r="H791" s="4"/>
       <c r="I791" s="4"/>
-      <c r="J791" s="4"/>
+      <c r="J791" s="7"/>
       <c r="K791" s="4"/>
       <c r="L791" s="4"/>
       <c r="M791" s="4"/>
@@ -24350,7 +24515,7 @@
       <c r="G792" s="4"/>
       <c r="H792" s="4"/>
       <c r="I792" s="4"/>
-      <c r="J792" s="4"/>
+      <c r="J792" s="7"/>
       <c r="K792" s="4"/>
       <c r="L792" s="4"/>
       <c r="M792" s="4"/>
@@ -24380,7 +24545,7 @@
       <c r="G793" s="4"/>
       <c r="H793" s="4"/>
       <c r="I793" s="4"/>
-      <c r="J793" s="4"/>
+      <c r="J793" s="7"/>
       <c r="K793" s="4"/>
       <c r="L793" s="4"/>
       <c r="M793" s="4"/>
@@ -24410,7 +24575,7 @@
       <c r="G794" s="4"/>
       <c r="H794" s="4"/>
       <c r="I794" s="4"/>
-      <c r="J794" s="4"/>
+      <c r="J794" s="7"/>
       <c r="K794" s="4"/>
       <c r="L794" s="4"/>
       <c r="M794" s="4"/>
@@ -24440,7 +24605,7 @@
       <c r="G795" s="4"/>
       <c r="H795" s="4"/>
       <c r="I795" s="4"/>
-      <c r="J795" s="4"/>
+      <c r="J795" s="7"/>
       <c r="K795" s="4"/>
       <c r="L795" s="4"/>
       <c r="M795" s="4"/>
@@ -24470,7 +24635,7 @@
       <c r="G796" s="4"/>
       <c r="H796" s="4"/>
       <c r="I796" s="4"/>
-      <c r="J796" s="4"/>
+      <c r="J796" s="7"/>
       <c r="K796" s="4"/>
       <c r="L796" s="4"/>
       <c r="M796" s="4"/>
@@ -24500,7 +24665,7 @@
       <c r="G797" s="4"/>
       <c r="H797" s="4"/>
       <c r="I797" s="4"/>
-      <c r="J797" s="4"/>
+      <c r="J797" s="7"/>
       <c r="K797" s="4"/>
       <c r="L797" s="4"/>
       <c r="M797" s="4"/>
@@ -24530,7 +24695,7 @@
       <c r="G798" s="4"/>
       <c r="H798" s="4"/>
       <c r="I798" s="4"/>
-      <c r="J798" s="4"/>
+      <c r="J798" s="7"/>
       <c r="K798" s="4"/>
       <c r="L798" s="4"/>
       <c r="M798" s="4"/>
@@ -24560,7 +24725,7 @@
       <c r="G799" s="4"/>
       <c r="H799" s="4"/>
       <c r="I799" s="4"/>
-      <c r="J799" s="4"/>
+      <c r="J799" s="7"/>
       <c r="K799" s="4"/>
       <c r="L799" s="4"/>
       <c r="M799" s="4"/>
@@ -24590,7 +24755,7 @@
       <c r="G800" s="4"/>
       <c r="H800" s="4"/>
       <c r="I800" s="4"/>
-      <c r="J800" s="4"/>
+      <c r="J800" s="7"/>
       <c r="K800" s="4"/>
       <c r="L800" s="4"/>
       <c r="M800" s="4"/>
@@ -24620,7 +24785,7 @@
       <c r="G801" s="4"/>
       <c r="H801" s="4"/>
       <c r="I801" s="4"/>
-      <c r="J801" s="4"/>
+      <c r="J801" s="7"/>
       <c r="K801" s="4"/>
       <c r="L801" s="4"/>
       <c r="M801" s="4"/>
@@ -24650,7 +24815,7 @@
       <c r="G802" s="4"/>
       <c r="H802" s="4"/>
       <c r="I802" s="4"/>
-      <c r="J802" s="4"/>
+      <c r="J802" s="7"/>
       <c r="K802" s="4"/>
       <c r="L802" s="4"/>
       <c r="M802" s="4"/>
@@ -24680,7 +24845,7 @@
       <c r="G803" s="4"/>
       <c r="H803" s="4"/>
       <c r="I803" s="4"/>
-      <c r="J803" s="4"/>
+      <c r="J803" s="7"/>
       <c r="K803" s="4"/>
       <c r="L803" s="4"/>
       <c r="M803" s="4"/>
@@ -24710,7 +24875,7 @@
       <c r="G804" s="4"/>
       <c r="H804" s="4"/>
       <c r="I804" s="4"/>
-      <c r="J804" s="4"/>
+      <c r="J804" s="7"/>
       <c r="K804" s="4"/>
       <c r="L804" s="4"/>
       <c r="M804" s="4"/>
@@ -24740,7 +24905,7 @@
       <c r="G805" s="4"/>
       <c r="H805" s="4"/>
       <c r="I805" s="4"/>
-      <c r="J805" s="4"/>
+      <c r="J805" s="7"/>
       <c r="K805" s="4"/>
       <c r="L805" s="4"/>
       <c r="M805" s="4"/>
@@ -24770,7 +24935,7 @@
       <c r="G806" s="4"/>
       <c r="H806" s="4"/>
       <c r="I806" s="4"/>
-      <c r="J806" s="4"/>
+      <c r="J806" s="7"/>
       <c r="K806" s="4"/>
       <c r="L806" s="4"/>
       <c r="M806" s="4"/>
@@ -24800,7 +24965,7 @@
       <c r="G807" s="4"/>
       <c r="H807" s="4"/>
       <c r="I807" s="4"/>
-      <c r="J807" s="4"/>
+      <c r="J807" s="7"/>
       <c r="K807" s="4"/>
       <c r="L807" s="4"/>
       <c r="M807" s="4"/>
@@ -24830,7 +24995,7 @@
       <c r="G808" s="4"/>
       <c r="H808" s="4"/>
       <c r="I808" s="4"/>
-      <c r="J808" s="4"/>
+      <c r="J808" s="7"/>
       <c r="K808" s="4"/>
       <c r="L808" s="4"/>
       <c r="M808" s="4"/>
@@ -24860,7 +25025,7 @@
       <c r="G809" s="4"/>
       <c r="H809" s="4"/>
       <c r="I809" s="4"/>
-      <c r="J809" s="4"/>
+      <c r="J809" s="7"/>
       <c r="K809" s="4"/>
       <c r="L809" s="4"/>
       <c r="M809" s="4"/>
@@ -24890,7 +25055,7 @@
       <c r="G810" s="4"/>
       <c r="H810" s="4"/>
       <c r="I810" s="4"/>
-      <c r="J810" s="4"/>
+      <c r="J810" s="7"/>
       <c r="K810" s="4"/>
       <c r="L810" s="4"/>
       <c r="M810" s="4"/>
@@ -24920,7 +25085,7 @@
       <c r="G811" s="4"/>
       <c r="H811" s="4"/>
       <c r="I811" s="4"/>
-      <c r="J811" s="4"/>
+      <c r="J811" s="7"/>
       <c r="K811" s="4"/>
       <c r="L811" s="4"/>
       <c r="M811" s="4"/>
@@ -24950,7 +25115,7 @@
       <c r="G812" s="4"/>
       <c r="H812" s="4"/>
       <c r="I812" s="4"/>
-      <c r="J812" s="4"/>
+      <c r="J812" s="7"/>
       <c r="K812" s="4"/>
       <c r="L812" s="4"/>
       <c r="M812" s="4"/>
@@ -24980,7 +25145,7 @@
       <c r="G813" s="4"/>
       <c r="H813" s="4"/>
       <c r="I813" s="4"/>
-      <c r="J813" s="4"/>
+      <c r="J813" s="7"/>
       <c r="K813" s="4"/>
       <c r="L813" s="4"/>
       <c r="M813" s="4"/>
@@ -25010,7 +25175,7 @@
       <c r="G814" s="4"/>
       <c r="H814" s="4"/>
       <c r="I814" s="4"/>
-      <c r="J814" s="4"/>
+      <c r="J814" s="7"/>
       <c r="K814" s="4"/>
       <c r="L814" s="4"/>
       <c r="M814" s="4"/>
@@ -25040,7 +25205,7 @@
       <c r="G815" s="4"/>
       <c r="H815" s="4"/>
       <c r="I815" s="4"/>
-      <c r="J815" s="4"/>
+      <c r="J815" s="7"/>
       <c r="K815" s="4"/>
       <c r="L815" s="4"/>
       <c r="M815" s="4"/>
@@ -25070,7 +25235,7 @@
       <c r="G816" s="4"/>
       <c r="H816" s="4"/>
       <c r="I816" s="4"/>
-      <c r="J816" s="4"/>
+      <c r="J816" s="7"/>
       <c r="K816" s="4"/>
       <c r="L816" s="4"/>
       <c r="M816" s="4"/>
@@ -25100,7 +25265,7 @@
       <c r="G817" s="4"/>
       <c r="H817" s="4"/>
       <c r="I817" s="4"/>
-      <c r="J817" s="4"/>
+      <c r="J817" s="7"/>
       <c r="K817" s="4"/>
       <c r="L817" s="4"/>
       <c r="M817" s="4"/>
@@ -25130,7 +25295,7 @@
       <c r="G818" s="4"/>
       <c r="H818" s="4"/>
       <c r="I818" s="4"/>
-      <c r="J818" s="4"/>
+      <c r="J818" s="7"/>
       <c r="K818" s="4"/>
       <c r="L818" s="4"/>
       <c r="M818" s="4"/>
@@ -25160,7 +25325,7 @@
       <c r="G819" s="4"/>
       <c r="H819" s="4"/>
       <c r="I819" s="4"/>
-      <c r="J819" s="4"/>
+      <c r="J819" s="7"/>
       <c r="K819" s="4"/>
       <c r="L819" s="4"/>
       <c r="M819" s="4"/>
@@ -25190,7 +25355,7 @@
       <c r="G820" s="4"/>
       <c r="H820" s="4"/>
       <c r="I820" s="4"/>
-      <c r="J820" s="4"/>
+      <c r="J820" s="7"/>
       <c r="K820" s="4"/>
       <c r="L820" s="4"/>
       <c r="M820" s="4"/>
@@ -25220,7 +25385,7 @@
       <c r="G821" s="4"/>
       <c r="H821" s="4"/>
       <c r="I821" s="4"/>
-      <c r="J821" s="4"/>
+      <c r="J821" s="7"/>
       <c r="K821" s="4"/>
       <c r="L821" s="4"/>
       <c r="M821" s="4"/>
@@ -25250,7 +25415,7 @@
       <c r="G822" s="4"/>
       <c r="H822" s="4"/>
       <c r="I822" s="4"/>
-      <c r="J822" s="4"/>
+      <c r="J822" s="7"/>
       <c r="K822" s="4"/>
       <c r="L822" s="4"/>
       <c r="M822" s="4"/>
@@ -25280,7 +25445,7 @@
       <c r="G823" s="4"/>
       <c r="H823" s="4"/>
       <c r="I823" s="4"/>
-      <c r="J823" s="4"/>
+      <c r="J823" s="7"/>
       <c r="K823" s="4"/>
       <c r="L823" s="4"/>
       <c r="M823" s="4"/>
@@ -25310,7 +25475,7 @@
       <c r="G824" s="4"/>
       <c r="H824" s="4"/>
       <c r="I824" s="4"/>
-      <c r="J824" s="4"/>
+      <c r="J824" s="7"/>
       <c r="K824" s="4"/>
       <c r="L824" s="4"/>
       <c r="M824" s="4"/>
@@ -25340,7 +25505,7 @@
       <c r="G825" s="4"/>
       <c r="H825" s="4"/>
       <c r="I825" s="4"/>
-      <c r="J825" s="4"/>
+      <c r="J825" s="7"/>
       <c r="K825" s="4"/>
       <c r="L825" s="4"/>
       <c r="M825" s="4"/>
@@ -25370,7 +25535,7 @@
       <c r="G826" s="4"/>
       <c r="H826" s="4"/>
       <c r="I826" s="4"/>
-      <c r="J826" s="4"/>
+      <c r="J826" s="7"/>
       <c r="K826" s="4"/>
       <c r="L826" s="4"/>
       <c r="M826" s="4"/>
@@ -25400,7 +25565,7 @@
       <c r="G827" s="4"/>
       <c r="H827" s="4"/>
       <c r="I827" s="4"/>
-      <c r="J827" s="4"/>
+      <c r="J827" s="7"/>
       <c r="K827" s="4"/>
       <c r="L827" s="4"/>
       <c r="M827" s="4"/>
@@ -25430,7 +25595,7 @@
       <c r="G828" s="4"/>
       <c r="H828" s="4"/>
       <c r="I828" s="4"/>
-      <c r="J828" s="4"/>
+      <c r="J828" s="7"/>
       <c r="K828" s="4"/>
       <c r="L828" s="4"/>
       <c r="M828" s="4"/>
@@ -25460,7 +25625,7 @@
       <c r="G829" s="4"/>
       <c r="H829" s="4"/>
       <c r="I829" s="4"/>
-      <c r="J829" s="4"/>
+      <c r="J829" s="7"/>
       <c r="K829" s="4"/>
       <c r="L829" s="4"/>
       <c r="M829" s="4"/>
@@ -25490,7 +25655,7 @@
       <c r="G830" s="4"/>
       <c r="H830" s="4"/>
       <c r="I830" s="4"/>
-      <c r="J830" s="4"/>
+      <c r="J830" s="7"/>
       <c r="K830" s="4"/>
       <c r="L830" s="4"/>
       <c r="M830" s="4"/>
@@ -25520,7 +25685,7 @@
       <c r="G831" s="4"/>
       <c r="H831" s="4"/>
       <c r="I831" s="4"/>
-      <c r="J831" s="4"/>
+      <c r="J831" s="7"/>
       <c r="K831" s="4"/>
       <c r="L831" s="4"/>
       <c r="M831" s="4"/>
@@ -25550,7 +25715,7 @@
       <c r="G832" s="4"/>
       <c r="H832" s="4"/>
       <c r="I832" s="4"/>
-      <c r="J832" s="4"/>
+      <c r="J832" s="7"/>
       <c r="K832" s="4"/>
       <c r="L832" s="4"/>
       <c r="M832" s="4"/>
@@ -25580,7 +25745,7 @@
       <c r="G833" s="4"/>
       <c r="H833" s="4"/>
       <c r="I833" s="4"/>
-      <c r="J833" s="4"/>
+      <c r="J833" s="7"/>
       <c r="K833" s="4"/>
       <c r="L833" s="4"/>
       <c r="M833" s="4"/>
@@ -25610,7 +25775,7 @@
       <c r="G834" s="4"/>
       <c r="H834" s="4"/>
       <c r="I834" s="4"/>
-      <c r="J834" s="4"/>
+      <c r="J834" s="7"/>
       <c r="K834" s="4"/>
       <c r="L834" s="4"/>
       <c r="M834" s="4"/>
@@ -25640,7 +25805,7 @@
       <c r="G835" s="4"/>
       <c r="H835" s="4"/>
       <c r="I835" s="4"/>
-      <c r="J835" s="4"/>
+      <c r="J835" s="7"/>
       <c r="K835" s="4"/>
       <c r="L835" s="4"/>
       <c r="M835" s="4"/>
@@ -25670,7 +25835,7 @@
       <c r="G836" s="4"/>
       <c r="H836" s="4"/>
       <c r="I836" s="4"/>
-      <c r="J836" s="4"/>
+      <c r="J836" s="7"/>
       <c r="K836" s="4"/>
       <c r="L836" s="4"/>
       <c r="M836" s="4"/>
@@ -25700,7 +25865,7 @@
       <c r="G837" s="4"/>
       <c r="H837" s="4"/>
       <c r="I837" s="4"/>
-      <c r="J837" s="4"/>
+      <c r="J837" s="7"/>
       <c r="K837" s="4"/>
       <c r="L837" s="4"/>
       <c r="M837" s="4"/>
@@ -25730,7 +25895,7 @@
       <c r="G838" s="4"/>
       <c r="H838" s="4"/>
       <c r="I838" s="4"/>
-      <c r="J838" s="4"/>
+      <c r="J838" s="7"/>
       <c r="K838" s="4"/>
       <c r="L838" s="4"/>
       <c r="M838" s="4"/>
@@ -25760,7 +25925,7 @@
       <c r="G839" s="4"/>
       <c r="H839" s="4"/>
       <c r="I839" s="4"/>
-      <c r="J839" s="4"/>
+      <c r="J839" s="7"/>
       <c r="K839" s="4"/>
       <c r="L839" s="4"/>
       <c r="M839" s="4"/>
@@ -25790,7 +25955,7 @@
       <c r="G840" s="4"/>
       <c r="H840" s="4"/>
       <c r="I840" s="4"/>
-      <c r="J840" s="4"/>
+      <c r="J840" s="7"/>
       <c r="K840" s="4"/>
       <c r="L840" s="4"/>
       <c r="M840" s="4"/>
@@ -25820,7 +25985,7 @@
       <c r="G841" s="4"/>
       <c r="H841" s="4"/>
       <c r="I841" s="4"/>
-      <c r="J841" s="4"/>
+      <c r="J841" s="7"/>
       <c r="K841" s="4"/>
       <c r="L841" s="4"/>
       <c r="M841" s="4"/>
@@ -25850,7 +26015,7 @@
       <c r="G842" s="4"/>
       <c r="H842" s="4"/>
       <c r="I842" s="4"/>
-      <c r="J842" s="4"/>
+      <c r="J842" s="7"/>
       <c r="K842" s="4"/>
       <c r="L842" s="4"/>
       <c r="M842" s="4"/>
@@ -25880,7 +26045,7 @@
       <c r="G843" s="4"/>
       <c r="H843" s="4"/>
       <c r="I843" s="4"/>
-      <c r="J843" s="4"/>
+      <c r="J843" s="7"/>
       <c r="K843" s="4"/>
       <c r="L843" s="4"/>
       <c r="M843" s="4"/>
@@ -25910,7 +26075,7 @@
       <c r="G844" s="4"/>
       <c r="H844" s="4"/>
       <c r="I844" s="4"/>
-      <c r="J844" s="4"/>
+      <c r="J844" s="7"/>
       <c r="K844" s="4"/>
       <c r="L844" s="4"/>
       <c r="M844" s="4"/>
@@ -25940,7 +26105,7 @@
       <c r="G845" s="4"/>
       <c r="H845" s="4"/>
       <c r="I845" s="4"/>
-      <c r="J845" s="4"/>
+      <c r="J845" s="7"/>
       <c r="K845" s="4"/>
       <c r="L845" s="4"/>
       <c r="M845" s="4"/>
@@ -25970,7 +26135,7 @@
       <c r="G846" s="4"/>
       <c r="H846" s="4"/>
       <c r="I846" s="4"/>
-      <c r="J846" s="4"/>
+      <c r="J846" s="7"/>
       <c r="K846" s="4"/>
       <c r="L846" s="4"/>
       <c r="M846" s="4"/>
@@ -26000,7 +26165,7 @@
       <c r="G847" s="4"/>
       <c r="H847" s="4"/>
       <c r="I847" s="4"/>
-      <c r="J847" s="4"/>
+      <c r="J847" s="7"/>
       <c r="K847" s="4"/>
       <c r="L847" s="4"/>
       <c r="M847" s="4"/>
@@ -26030,7 +26195,7 @@
       <c r="G848" s="4"/>
       <c r="H848" s="4"/>
       <c r="I848" s="4"/>
-      <c r="J848" s="4"/>
+      <c r="J848" s="7"/>
       <c r="K848" s="4"/>
       <c r="L848" s="4"/>
       <c r="M848" s="4"/>
@@ -26060,7 +26225,7 @@
       <c r="G849" s="4"/>
       <c r="H849" s="4"/>
       <c r="I849" s="4"/>
-      <c r="J849" s="4"/>
+      <c r="J849" s="7"/>
       <c r="K849" s="4"/>
       <c r="L849" s="4"/>
       <c r="M849" s="4"/>
@@ -26090,7 +26255,7 @@
       <c r="G850" s="4"/>
       <c r="H850" s="4"/>
       <c r="I850" s="4"/>
-      <c r="J850" s="4"/>
+      <c r="J850" s="7"/>
       <c r="K850" s="4"/>
       <c r="L850" s="4"/>
       <c r="M850" s="4"/>
@@ -26120,7 +26285,7 @@
       <c r="G851" s="4"/>
       <c r="H851" s="4"/>
       <c r="I851" s="4"/>
-      <c r="J851" s="4"/>
+      <c r="J851" s="7"/>
       <c r="K851" s="4"/>
       <c r="L851" s="4"/>
       <c r="M851" s="4"/>
@@ -26150,7 +26315,7 @@
       <c r="G852" s="4"/>
       <c r="H852" s="4"/>
       <c r="I852" s="4"/>
-      <c r="J852" s="4"/>
+      <c r="J852" s="7"/>
       <c r="K852" s="4"/>
       <c r="L852" s="4"/>
       <c r="M852" s="4"/>
@@ -26180,7 +26345,7 @@
       <c r="G853" s="4"/>
       <c r="H853" s="4"/>
       <c r="I853" s="4"/>
-      <c r="J853" s="4"/>
+      <c r="J853" s="7"/>
       <c r="K853" s="4"/>
       <c r="L853" s="4"/>
       <c r="M853" s="4"/>
@@ -26210,7 +26375,7 @@
       <c r="G854" s="4"/>
       <c r="H854" s="4"/>
       <c r="I854" s="4"/>
-      <c r="J854" s="4"/>
+      <c r="J854" s="7"/>
       <c r="K854" s="4"/>
       <c r="L854" s="4"/>
       <c r="M854" s="4"/>
@@ -26240,7 +26405,7 @@
       <c r="G855" s="4"/>
       <c r="H855" s="4"/>
       <c r="I855" s="4"/>
-      <c r="J855" s="4"/>
+      <c r="J855" s="7"/>
       <c r="K855" s="4"/>
       <c r="L855" s="4"/>
       <c r="M855" s="4"/>
@@ -26270,7 +26435,7 @@
       <c r="G856" s="4"/>
       <c r="H856" s="4"/>
       <c r="I856" s="4"/>
-      <c r="J856" s="4"/>
+      <c r="J856" s="7"/>
       <c r="K856" s="4"/>
       <c r="L856" s="4"/>
       <c r="M856" s="4"/>
@@ -26300,7 +26465,7 @@
       <c r="G857" s="4"/>
       <c r="H857" s="4"/>
       <c r="I857" s="4"/>
-      <c r="J857" s="4"/>
+      <c r="J857" s="7"/>
       <c r="K857" s="4"/>
       <c r="L857" s="4"/>
       <c r="M857" s="4"/>
@@ -26330,7 +26495,7 @@
       <c r="G858" s="4"/>
       <c r="H858" s="4"/>
       <c r="I858" s="4"/>
-      <c r="J858" s="4"/>
+      <c r="J858" s="7"/>
       <c r="K858" s="4"/>
       <c r="L858" s="4"/>
       <c r="M858" s="4"/>
@@ -26360,7 +26525,7 @@
       <c r="G859" s="4"/>
       <c r="H859" s="4"/>
       <c r="I859" s="4"/>
-      <c r="J859" s="4"/>
+      <c r="J859" s="7"/>
       <c r="K859" s="4"/>
       <c r="L859" s="4"/>
       <c r="M859" s="4"/>
@@ -26390,7 +26555,7 @@
       <c r="G860" s="4"/>
       <c r="H860" s="4"/>
       <c r="I860" s="4"/>
-      <c r="J860" s="4"/>
+      <c r="J860" s="7"/>
       <c r="K860" s="4"/>
       <c r="L860" s="4"/>
       <c r="M860" s="4"/>
@@ -26420,7 +26585,7 @@
       <c r="G861" s="4"/>
       <c r="H861" s="4"/>
       <c r="I861" s="4"/>
-      <c r="J861" s="4"/>
+      <c r="J861" s="7"/>
       <c r="K861" s="4"/>
       <c r="L861" s="4"/>
       <c r="M861" s="4"/>
@@ -26450,7 +26615,7 @@
       <c r="G862" s="4"/>
       <c r="H862" s="4"/>
       <c r="I862" s="4"/>
-      <c r="J862" s="4"/>
+      <c r="J862" s="7"/>
       <c r="K862" s="4"/>
       <c r="L862" s="4"/>
       <c r="M862" s="4"/>
@@ -26480,7 +26645,7 @@
       <c r="G863" s="4"/>
       <c r="H863" s="4"/>
       <c r="I863" s="4"/>
-      <c r="J863" s="4"/>
+      <c r="J863" s="7"/>
       <c r="K863" s="4"/>
       <c r="L863" s="4"/>
       <c r="M863" s="4"/>
@@ -26510,7 +26675,7 @@
       <c r="G864" s="4"/>
       <c r="H864" s="4"/>
       <c r="I864" s="4"/>
-      <c r="J864" s="4"/>
+      <c r="J864" s="7"/>
       <c r="K864" s="4"/>
       <c r="L864" s="4"/>
       <c r="M864" s="4"/>
@@ -26540,7 +26705,7 @@
       <c r="G865" s="4"/>
       <c r="H865" s="4"/>
       <c r="I865" s="4"/>
-      <c r="J865" s="4"/>
+      <c r="J865" s="7"/>
       <c r="K865" s="4"/>
       <c r="L865" s="4"/>
       <c r="M865" s="4"/>
@@ -26570,7 +26735,7 @@
       <c r="G866" s="4"/>
       <c r="H866" s="4"/>
       <c r="I866" s="4"/>
-      <c r="J866" s="4"/>
+      <c r="J866" s="7"/>
       <c r="K866" s="4"/>
       <c r="L866" s="4"/>
       <c r="M866" s="4"/>
@@ -26600,7 +26765,7 @@
       <c r="G867" s="4"/>
       <c r="H867" s="4"/>
       <c r="I867" s="4"/>
-      <c r="J867" s="4"/>
+      <c r="J867" s="7"/>
       <c r="K867" s="4"/>
       <c r="L867" s="4"/>
       <c r="M867" s="4"/>
@@ -26630,7 +26795,7 @@
       <c r="G868" s="4"/>
       <c r="H868" s="4"/>
       <c r="I868" s="4"/>
-      <c r="J868" s="4"/>
+      <c r="J868" s="7"/>
       <c r="K868" s="4"/>
       <c r="L868" s="4"/>
       <c r="M868" s="4"/>
@@ -26660,7 +26825,7 @@
       <c r="G869" s="4"/>
       <c r="H869" s="4"/>
       <c r="I869" s="4"/>
-      <c r="J869" s="4"/>
+      <c r="J869" s="7"/>
       <c r="K869" s="4"/>
       <c r="L869" s="4"/>
       <c r="M869" s="4"/>
@@ -26690,7 +26855,7 @@
       <c r="G870" s="4"/>
       <c r="H870" s="4"/>
       <c r="I870" s="4"/>
-      <c r="J870" s="4"/>
+      <c r="J870" s="7"/>
       <c r="K870" s="4"/>
       <c r="L870" s="4"/>
       <c r="M870" s="4"/>
@@ -26720,7 +26885,7 @@
       <c r="G871" s="4"/>
       <c r="H871" s="4"/>
       <c r="I871" s="4"/>
-      <c r="J871" s="4"/>
+      <c r="J871" s="7"/>
       <c r="K871" s="4"/>
       <c r="L871" s="4"/>
       <c r="M871" s="4"/>
@@ -26750,7 +26915,7 @@
       <c r="G872" s="4"/>
       <c r="H872" s="4"/>
       <c r="I872" s="4"/>
-      <c r="J872" s="4"/>
+      <c r="J872" s="7"/>
       <c r="K872" s="4"/>
       <c r="L872" s="4"/>
       <c r="M872" s="4"/>
@@ -26780,7 +26945,7 @@
       <c r="G873" s="4"/>
       <c r="H873" s="4"/>
       <c r="I873" s="4"/>
-      <c r="J873" s="4"/>
+      <c r="J873" s="7"/>
       <c r="K873" s="4"/>
       <c r="L873" s="4"/>
       <c r="M873" s="4"/>
@@ -26810,7 +26975,7 @@
       <c r="G874" s="4"/>
       <c r="H874" s="4"/>
       <c r="I874" s="4"/>
-      <c r="J874" s="4"/>
+      <c r="J874" s="7"/>
       <c r="K874" s="4"/>
       <c r="L874" s="4"/>
       <c r="M874" s="4"/>
@@ -26840,7 +27005,7 @@
       <c r="G875" s="4"/>
       <c r="H875" s="4"/>
       <c r="I875" s="4"/>
-      <c r="J875" s="4"/>
+      <c r="J875" s="7"/>
       <c r="K875" s="4"/>
       <c r="L875" s="4"/>
       <c r="M875" s="4"/>
@@ -26870,7 +27035,7 @@
       <c r="G876" s="4"/>
       <c r="H876" s="4"/>
       <c r="I876" s="4"/>
-      <c r="J876" s="4"/>
+      <c r="J876" s="7"/>
       <c r="K876" s="4"/>
       <c r="L876" s="4"/>
       <c r="M876" s="4"/>
@@ -26900,7 +27065,7 @@
       <c r="G877" s="4"/>
       <c r="H877" s="4"/>
       <c r="I877" s="4"/>
-      <c r="J877" s="4"/>
+      <c r="J877" s="7"/>
       <c r="K877" s="4"/>
       <c r="L877" s="4"/>
       <c r="M877" s="4"/>
@@ -26930,7 +27095,7 @@
       <c r="G878" s="4"/>
       <c r="H878" s="4"/>
       <c r="I878" s="4"/>
-      <c r="J878" s="4"/>
+      <c r="J878" s="7"/>
       <c r="K878" s="4"/>
       <c r="L878" s="4"/>
       <c r="M878" s="4"/>
@@ -26960,7 +27125,7 @@
       <c r="G879" s="4"/>
       <c r="H879" s="4"/>
       <c r="I879" s="4"/>
-      <c r="J879" s="4"/>
+      <c r="J879" s="7"/>
       <c r="K879" s="4"/>
       <c r="L879" s="4"/>
       <c r="M879" s="4"/>
@@ -26990,7 +27155,7 @@
       <c r="G880" s="4"/>
       <c r="H880" s="4"/>
       <c r="I880" s="4"/>
-      <c r="J880" s="4"/>
+      <c r="J880" s="7"/>
       <c r="K880" s="4"/>
       <c r="L880" s="4"/>
       <c r="M880" s="4"/>
@@ -27020,7 +27185,7 @@
       <c r="G881" s="4"/>
       <c r="H881" s="4"/>
       <c r="I881" s="4"/>
-      <c r="J881" s="4"/>
+      <c r="J881" s="7"/>
       <c r="K881" s="4"/>
       <c r="L881" s="4"/>
       <c r="M881" s="4"/>
@@ -27050,7 +27215,7 @@
       <c r="G882" s="4"/>
       <c r="H882" s="4"/>
       <c r="I882" s="4"/>
-      <c r="J882" s="4"/>
+      <c r="J882" s="7"/>
       <c r="K882" s="4"/>
       <c r="L882" s="4"/>
       <c r="M882" s="4"/>
@@ -27080,7 +27245,7 @@
       <c r="G883" s="4"/>
       <c r="H883" s="4"/>
       <c r="I883" s="4"/>
-      <c r="J883" s="4"/>
+      <c r="J883" s="7"/>
       <c r="K883" s="4"/>
       <c r="L883" s="4"/>
       <c r="M883" s="4"/>
@@ -27110,7 +27275,7 @@
       <c r="G884" s="4"/>
       <c r="H884" s="4"/>
       <c r="I884" s="4"/>
-      <c r="J884" s="4"/>
+      <c r="J884" s="7"/>
       <c r="K884" s="4"/>
       <c r="L884" s="4"/>
       <c r="M884" s="4"/>
@@ -27140,7 +27305,7 @@
       <c r="G885" s="4"/>
       <c r="H885" s="4"/>
       <c r="I885" s="4"/>
-      <c r="J885" s="4"/>
+      <c r="J885" s="7"/>
       <c r="K885" s="4"/>
       <c r="L885" s="4"/>
       <c r="M885" s="4"/>
@@ -27170,7 +27335,7 @@
       <c r="G886" s="4"/>
       <c r="H886" s="4"/>
       <c r="I886" s="4"/>
-      <c r="J886" s="4"/>
+      <c r="J886" s="7"/>
       <c r="K886" s="4"/>
       <c r="L886" s="4"/>
       <c r="M886" s="4"/>
@@ -27200,7 +27365,7 @@
       <c r="G887" s="4"/>
       <c r="H887" s="4"/>
       <c r="I887" s="4"/>
-      <c r="J887" s="4"/>
+      <c r="J887" s="7"/>
       <c r="K887" s="4"/>
       <c r="L887" s="4"/>
       <c r="M887" s="4"/>
@@ -27230,7 +27395,7 @@
       <c r="G888" s="4"/>
       <c r="H888" s="4"/>
       <c r="I888" s="4"/>
-      <c r="J888" s="4"/>
+      <c r="J888" s="7"/>
       <c r="K888" s="4"/>
       <c r="L888" s="4"/>
       <c r="M888" s="4"/>
@@ -27260,7 +27425,7 @@
       <c r="G889" s="4"/>
       <c r="H889" s="4"/>
       <c r="I889" s="4"/>
-      <c r="J889" s="4"/>
+      <c r="J889" s="7"/>
       <c r="K889" s="4"/>
       <c r="L889" s="4"/>
       <c r="M889" s="4"/>
@@ -27290,7 +27455,7 @@
       <c r="G890" s="4"/>
       <c r="H890" s="4"/>
       <c r="I890" s="4"/>
-      <c r="J890" s="4"/>
+      <c r="J890" s="7"/>
       <c r="K890" s="4"/>
       <c r="L890" s="4"/>
       <c r="M890" s="4"/>
@@ -27320,7 +27485,7 @@
       <c r="G891" s="4"/>
       <c r="H891" s="4"/>
       <c r="I891" s="4"/>
-      <c r="J891" s="4"/>
+      <c r="J891" s="7"/>
       <c r="K891" s="4"/>
       <c r="L891" s="4"/>
       <c r="M891" s="4"/>
@@ -27350,7 +27515,7 @@
       <c r="G892" s="4"/>
       <c r="H892" s="4"/>
       <c r="I892" s="4"/>
-      <c r="J892" s="4"/>
+      <c r="J892" s="7"/>
       <c r="K892" s="4"/>
       <c r="L892" s="4"/>
       <c r="M892" s="4"/>
@@ -27380,7 +27545,7 @@
       <c r="G893" s="4"/>
       <c r="H893" s="4"/>
       <c r="I893" s="4"/>
-      <c r="J893" s="4"/>
+      <c r="J893" s="7"/>
       <c r="K893" s="4"/>
       <c r="L893" s="4"/>
       <c r="M893" s="4"/>
@@ -27410,7 +27575,7 @@
       <c r="G894" s="4"/>
       <c r="H894" s="4"/>
       <c r="I894" s="4"/>
-      <c r="J894" s="4"/>
+      <c r="J894" s="7"/>
       <c r="K894" s="4"/>
       <c r="L894" s="4"/>
       <c r="M894" s="4"/>
@@ -27440,7 +27605,7 @@
       <c r="G895" s="4"/>
       <c r="H895" s="4"/>
       <c r="I895" s="4"/>
-      <c r="J895" s="4"/>
+      <c r="J895" s="7"/>
       <c r="K895" s="4"/>
       <c r="L895" s="4"/>
       <c r="M895" s="4"/>
@@ -27470,7 +27635,7 @@
       <c r="G896" s="4"/>
       <c r="H896" s="4"/>
       <c r="I896" s="4"/>
-      <c r="J896" s="4"/>
+      <c r="J896" s="7"/>
       <c r="K896" s="4"/>
       <c r="L896" s="4"/>
       <c r="M896" s="4"/>
@@ -27500,7 +27665,7 @@
       <c r="G897" s="4"/>
       <c r="H897" s="4"/>
       <c r="I897" s="4"/>
-      <c r="J897" s="4"/>
+      <c r="J897" s="7"/>
       <c r="K897" s="4"/>
       <c r="L897" s="4"/>
       <c r="M897" s="4"/>
@@ -27530,7 +27695,7 @@
       <c r="G898" s="4"/>
       <c r="H898" s="4"/>
       <c r="I898" s="4"/>
-      <c r="J898" s="4"/>
+      <c r="J898" s="7"/>
       <c r="K898" s="4"/>
       <c r="L898" s="4"/>
       <c r="M898" s="4"/>
@@ -27560,7 +27725,7 @@
       <c r="G899" s="4"/>
       <c r="H899" s="4"/>
       <c r="I899" s="4"/>
-      <c r="J899" s="4"/>
+      <c r="J899" s="7"/>
       <c r="K899" s="4"/>
       <c r="L899" s="4"/>
       <c r="M899" s="4"/>
@@ -27590,7 +27755,7 @@
       <c r="G900" s="4"/>
       <c r="H900" s="4"/>
       <c r="I900" s="4"/>
-      <c r="J900" s="4"/>
+      <c r="J900" s="7"/>
       <c r="K900" s="4"/>
       <c r="L900" s="4"/>
       <c r="M900" s="4"/>
@@ -27620,7 +27785,7 @@
       <c r="G901" s="4"/>
       <c r="H901" s="4"/>
       <c r="I901" s="4"/>
-      <c r="J901" s="4"/>
+      <c r="J901" s="7"/>
       <c r="K901" s="4"/>
       <c r="L901" s="4"/>
       <c r="M901" s="4"/>
@@ -27650,7 +27815,7 @@
       <c r="G902" s="4"/>
       <c r="H902" s="4"/>
       <c r="I902" s="4"/>
-      <c r="J902" s="4"/>
+      <c r="J902" s="7"/>
       <c r="K902" s="4"/>
       <c r="L902" s="4"/>
       <c r="M902" s="4"/>
@@ -27680,7 +27845,7 @@
       <c r="G903" s="4"/>
       <c r="H903" s="4"/>
       <c r="I903" s="4"/>
-      <c r="J903" s="4"/>
+      <c r="J903" s="7"/>
       <c r="K903" s="4"/>
       <c r="L903" s="4"/>
       <c r="M903" s="4"/>
@@ -27710,7 +27875,7 @@
       <c r="G904" s="4"/>
       <c r="H904" s="4"/>
       <c r="I904" s="4"/>
-      <c r="J904" s="4"/>
+      <c r="J904" s="7"/>
       <c r="K904" s="4"/>
       <c r="L904" s="4"/>
       <c r="M904" s="4"/>
@@ -27740,7 +27905,7 @@
       <c r="G905" s="4"/>
       <c r="H905" s="4"/>
       <c r="I905" s="4"/>
-      <c r="J905" s="4"/>
+      <c r="J905" s="7"/>
       <c r="K905" s="4"/>
       <c r="L905" s="4"/>
       <c r="M905" s="4"/>
@@ -27770,7 +27935,7 @@
       <c r="G906" s="4"/>
       <c r="H906" s="4"/>
       <c r="I906" s="4"/>
-      <c r="J906" s="4"/>
+      <c r="J906" s="7"/>
       <c r="K906" s="4"/>
       <c r="L906" s="4"/>
       <c r="M906" s="4"/>
@@ -27800,7 +27965,7 @@
       <c r="G907" s="4"/>
       <c r="H907" s="4"/>
       <c r="I907" s="4"/>
-      <c r="J907" s="4"/>
+      <c r="J907" s="7"/>
       <c r="K907" s="4"/>
       <c r="L907" s="4"/>
       <c r="M907" s="4"/>
@@ -27830,7 +27995,7 @@
       <c r="G908" s="4"/>
       <c r="H908" s="4"/>
       <c r="I908" s="4"/>
-      <c r="J908" s="4"/>
+      <c r="J908" s="7"/>
       <c r="K908" s="4"/>
       <c r="L908" s="4"/>
       <c r="M908" s="4"/>
@@ -27860,7 +28025,7 @@
       <c r="G909" s="4"/>
       <c r="H909" s="4"/>
       <c r="I909" s="4"/>
-      <c r="J909" s="4"/>
+      <c r="J909" s="7"/>
       <c r="K909" s="4"/>
       <c r="L909" s="4"/>
       <c r="M909" s="4"/>
@@ -27890,7 +28055,7 @@
       <c r="G910" s="4"/>
       <c r="H910" s="4"/>
       <c r="I910" s="4"/>
-      <c r="J910" s="4"/>
+      <c r="J910" s="7"/>
       <c r="K910" s="4"/>
       <c r="L910" s="4"/>
       <c r="M910" s="4"/>
@@ -27920,7 +28085,7 @@
       <c r="G911" s="4"/>
       <c r="H911" s="4"/>
       <c r="I911" s="4"/>
-      <c r="J911" s="4"/>
+      <c r="J911" s="7"/>
       <c r="K911" s="4"/>
       <c r="L911" s="4"/>
       <c r="M911" s="4"/>
@@ -27950,7 +28115,7 @@
       <c r="G912" s="4"/>
       <c r="H912" s="4"/>
       <c r="I912" s="4"/>
-      <c r="J912" s="4"/>
+      <c r="J912" s="7"/>
       <c r="K912" s="4"/>
       <c r="L912" s="4"/>
       <c r="M912" s="4"/>
@@ -27980,7 +28145,7 @@
       <c r="G913" s="4"/>
       <c r="H913" s="4"/>
       <c r="I913" s="4"/>
-      <c r="J913" s="4"/>
+      <c r="J913" s="7"/>
       <c r="K913" s="4"/>
       <c r="L913" s="4"/>
       <c r="M913" s="4"/>
@@ -28010,7 +28175,7 @@
       <c r="G914" s="4"/>
       <c r="H914" s="4"/>
       <c r="I914" s="4"/>
-      <c r="J914" s="4"/>
+      <c r="J914" s="7"/>
       <c r="K914" s="4"/>
       <c r="L914" s="4"/>
       <c r="M914" s="4"/>
@@ -28040,7 +28205,7 @@
       <c r="G915" s="4"/>
       <c r="H915" s="4"/>
       <c r="I915" s="4"/>
-      <c r="J915" s="4"/>
+      <c r="J915" s="7"/>
       <c r="K915" s="4"/>
       <c r="L915" s="4"/>
       <c r="M915" s="4"/>
@@ -28070,7 +28235,7 @@
       <c r="G916" s="4"/>
       <c r="H916" s="4"/>
       <c r="I916" s="4"/>
-      <c r="J916" s="4"/>
+      <c r="J916" s="7"/>
       <c r="K916" s="4"/>
       <c r="L916" s="4"/>
       <c r="M916" s="4"/>
@@ -28100,7 +28265,7 @@
       <c r="G917" s="4"/>
       <c r="H917" s="4"/>
       <c r="I917" s="4"/>
-      <c r="J917" s="4"/>
+      <c r="J917" s="7"/>
       <c r="K917" s="4"/>
       <c r="L917" s="4"/>
       <c r="M917" s="4"/>
@@ -28130,7 +28295,7 @@
       <c r="G918" s="4"/>
       <c r="H918" s="4"/>
       <c r="I918" s="4"/>
-      <c r="J918" s="4"/>
+      <c r="J918" s="7"/>
       <c r="K918" s="4"/>
       <c r="L918" s="4"/>
       <c r="M918" s="4"/>
@@ -28160,7 +28325,7 @@
       <c r="G919" s="4"/>
       <c r="H919" s="4"/>
       <c r="I919" s="4"/>
-      <c r="J919" s="4"/>
+      <c r="J919" s="7"/>
       <c r="K919" s="4"/>
       <c r="L919" s="4"/>
       <c r="M919" s="4"/>
@@ -28190,7 +28355,7 @@
       <c r="G920" s="4"/>
       <c r="H920" s="4"/>
       <c r="I920" s="4"/>
-      <c r="J920" s="4"/>
+      <c r="J920" s="7"/>
       <c r="K920" s="4"/>
       <c r="L920" s="4"/>
       <c r="M920" s="4"/>
@@ -28220,7 +28385,7 @@
       <c r="G921" s="4"/>
       <c r="H921" s="4"/>
       <c r="I921" s="4"/>
-      <c r="J921" s="4"/>
+      <c r="J921" s="7"/>
       <c r="K921" s="4"/>
       <c r="L921" s="4"/>
       <c r="M921" s="4"/>
@@ -28250,7 +28415,7 @@
       <c r="G922" s="4"/>
       <c r="H922" s="4"/>
       <c r="I922" s="4"/>
-      <c r="J922" s="4"/>
+      <c r="J922" s="7"/>
       <c r="K922" s="4"/>
       <c r="L922" s="4"/>
       <c r="M922" s="4"/>
@@ -28280,7 +28445,7 @@
       <c r="G923" s="4"/>
       <c r="H923" s="4"/>
       <c r="I923" s="4"/>
-      <c r="J923" s="4"/>
+      <c r="J923" s="7"/>
       <c r="K923" s="4"/>
       <c r="L923" s="4"/>
       <c r="M923" s="4"/>
@@ -28310,7 +28475,7 @@
       <c r="G924" s="4"/>
       <c r="H924" s="4"/>
       <c r="I924" s="4"/>
-      <c r="J924" s="4"/>
+      <c r="J924" s="7"/>
       <c r="K924" s="4"/>
       <c r="L924" s="4"/>
       <c r="M924" s="4"/>
@@ -28340,7 +28505,7 @@
       <c r="G925" s="4"/>
       <c r="H925" s="4"/>
       <c r="I925" s="4"/>
-      <c r="J925" s="4"/>
+      <c r="J925" s="7"/>
       <c r="K925" s="4"/>
       <c r="L925" s="4"/>
       <c r="M925" s="4"/>
@@ -28370,7 +28535,7 @@
       <c r="G926" s="4"/>
       <c r="H926" s="4"/>
       <c r="I926" s="4"/>
-      <c r="J926" s="4"/>
+      <c r="J926" s="7"/>
       <c r="K926" s="4"/>
       <c r="L926" s="4"/>
       <c r="M926" s="4"/>
@@ -28400,7 +28565,7 @@
       <c r="G927" s="4"/>
       <c r="H927" s="4"/>
       <c r="I927" s="4"/>
-      <c r="J927" s="4"/>
+      <c r="J927" s="7"/>
       <c r="K927" s="4"/>
       <c r="L927" s="4"/>
       <c r="M927" s="4"/>
@@ -28430,7 +28595,7 @@
       <c r="G928" s="4"/>
       <c r="H928" s="4"/>
       <c r="I928" s="4"/>
-      <c r="J928" s="4"/>
+      <c r="J928" s="7"/>
       <c r="K928" s="4"/>
       <c r="L928" s="4"/>
       <c r="M928" s="4"/>
@@ -28460,7 +28625,7 @@
       <c r="G929" s="4"/>
       <c r="H929" s="4"/>
       <c r="I929" s="4"/>
-      <c r="J929" s="4"/>
+      <c r="J929" s="7"/>
       <c r="K929" s="4"/>
       <c r="L929" s="4"/>
       <c r="M929" s="4"/>
@@ -28490,7 +28655,7 @@
       <c r="G930" s="4"/>
       <c r="H930" s="4"/>
       <c r="I930" s="4"/>
-      <c r="J930" s="4"/>
+      <c r="J930" s="7"/>
       <c r="K930" s="4"/>
       <c r="L930" s="4"/>
       <c r="M930" s="4"/>
@@ -28520,7 +28685,7 @@
       <c r="G931" s="4"/>
       <c r="H931" s="4"/>
       <c r="I931" s="4"/>
-      <c r="J931" s="4"/>
+      <c r="J931" s="7"/>
       <c r="K931" s="4"/>
       <c r="L931" s="4"/>
       <c r="M931" s="4"/>
@@ -28550,7 +28715,7 @@
       <c r="G932" s="4"/>
       <c r="H932" s="4"/>
       <c r="I932" s="4"/>
-      <c r="J932" s="4"/>
+      <c r="J932" s="7"/>
       <c r="K932" s="4"/>
       <c r="L932" s="4"/>
       <c r="M932" s="4"/>
@@ -28580,7 +28745,7 @@
       <c r="G933" s="4"/>
       <c r="H933" s="4"/>
       <c r="I933" s="4"/>
-      <c r="J933" s="4"/>
+      <c r="J933" s="7"/>
       <c r="K933" s="4"/>
       <c r="L933" s="4"/>
       <c r="M933" s="4"/>
@@ -28610,7 +28775,7 @@
       <c r="G934" s="4"/>
       <c r="H934" s="4"/>
       <c r="I934" s="4"/>
-      <c r="J934" s="4"/>
+      <c r="J934" s="7"/>
       <c r="K934" s="4"/>
       <c r="L934" s="4"/>
       <c r="M934" s="4"/>
@@ -28640,7 +28805,7 @@
       <c r="G935" s="4"/>
       <c r="H935" s="4"/>
       <c r="I935" s="4"/>
-      <c r="J935" s="4"/>
+      <c r="J935" s="7"/>
       <c r="K935" s="4"/>
       <c r="L935" s="4"/>
       <c r="M935" s="4"/>
@@ -28670,7 +28835,7 @@
       <c r="G936" s="4"/>
       <c r="H936" s="4"/>
       <c r="I936" s="4"/>
-      <c r="J936" s="4"/>
+      <c r="J936" s="7"/>
       <c r="K936" s="4"/>
       <c r="L936" s="4"/>
       <c r="M936" s="4"/>
@@ -28700,7 +28865,7 @@
       <c r="G937" s="4"/>
       <c r="H937" s="4"/>
       <c r="I937" s="4"/>
-      <c r="J937" s="4"/>
+      <c r="J937" s="7"/>
       <c r="K937" s="4"/>
       <c r="L937" s="4"/>
       <c r="M937" s="4"/>
@@ -28730,7 +28895,7 @@
       <c r="G938" s="4"/>
       <c r="H938" s="4"/>
       <c r="I938" s="4"/>
-      <c r="J938" s="4"/>
+      <c r="J938" s="7"/>
       <c r="K938" s="4"/>
       <c r="L938" s="4"/>
       <c r="M938" s="4"/>
@@ -28760,7 +28925,7 @@
       <c r="G939" s="4"/>
       <c r="H939" s="4"/>
       <c r="I939" s="4"/>
-      <c r="J939" s="4"/>
+      <c r="J939" s="7"/>
       <c r="K939" s="4"/>
       <c r="L939" s="4"/>
       <c r="M939" s="4"/>
@@ -28790,7 +28955,7 @@
       <c r="G940" s="4"/>
       <c r="H940" s="4"/>
       <c r="I940" s="4"/>
-      <c r="J940" s="4"/>
+      <c r="J940" s="7"/>
       <c r="K940" s="4"/>
       <c r="L940" s="4"/>
       <c r="M940" s="4"/>
@@ -28820,7 +28985,7 @@
       <c r="G941" s="4"/>
       <c r="H941" s="4"/>
       <c r="I941" s="4"/>
-      <c r="J941" s="4"/>
+      <c r="J941" s="7"/>
       <c r="K941" s="4"/>
       <c r="L941" s="4"/>
       <c r="M941" s="4"/>
@@ -28850,7 +29015,7 @@
       <c r="G942" s="4"/>
       <c r="H942" s="4"/>
       <c r="I942" s="4"/>
-      <c r="J942" s="4"/>
+      <c r="J942" s="7"/>
       <c r="K942" s="4"/>
       <c r="L942" s="4"/>
       <c r="M942" s="4"/>
@@ -28880,7 +29045,7 @@
       <c r="G943" s="4"/>
       <c r="H943" s="4"/>
       <c r="I943" s="4"/>
-      <c r="J943" s="4"/>
+      <c r="J943" s="7"/>
       <c r="K943" s="4"/>
       <c r="L943" s="4"/>
       <c r="M943" s="4"/>
@@ -28910,7 +29075,7 @@
       <c r="G944" s="4"/>
       <c r="H944" s="4"/>
       <c r="I944" s="4"/>
-      <c r="J944" s="4"/>
+      <c r="J944" s="7"/>
       <c r="K944" s="4"/>
       <c r="L944" s="4"/>
       <c r="M944" s="4"/>
@@ -28940,7 +29105,7 @@
       <c r="G945" s="4"/>
       <c r="H945" s="4"/>
       <c r="I945" s="4"/>
-      <c r="J945" s="4"/>
+      <c r="J945" s="7"/>
       <c r="K945" s="4"/>
       <c r="L945" s="4"/>
       <c r="M945" s="4"/>
@@ -28970,7 +29135,7 @@
       <c r="G946" s="4"/>
       <c r="H946" s="4"/>
       <c r="I946" s="4"/>
-      <c r="J946" s="4"/>
+      <c r="J946" s="7"/>
       <c r="K946" s="4"/>
       <c r="L946" s="4"/>
       <c r="M946" s="4"/>
@@ -29000,7 +29165,7 @@
       <c r="G947" s="4"/>
       <c r="H947" s="4"/>
       <c r="I947" s="4"/>
-      <c r="J947" s="4"/>
+      <c r="J947" s="7"/>
       <c r="K947" s="4"/>
       <c r="L947" s="4"/>
       <c r="M947" s="4"/>
@@ -29030,7 +29195,7 @@
       <c r="G948" s="4"/>
       <c r="H948" s="4"/>
       <c r="I948" s="4"/>
-      <c r="J948" s="4"/>
+      <c r="J948" s="7"/>
       <c r="K948" s="4"/>
       <c r="L948" s="4"/>
       <c r="M948" s="4"/>
@@ -29060,7 +29225,7 @@
       <c r="G949" s="4"/>
       <c r="H949" s="4"/>
       <c r="I949" s="4"/>
-      <c r="J949" s="4"/>
+      <c r="J949" s="7"/>
       <c r="K949" s="4"/>
       <c r="L949" s="4"/>
       <c r="M949" s="4"/>
@@ -29090,7 +29255,7 @@
       <c r="G950" s="4"/>
       <c r="H950" s="4"/>
       <c r="I950" s="4"/>
-      <c r="J950" s="4"/>
+      <c r="J950" s="7"/>
       <c r="K950" s="4"/>
       <c r="L950" s="4"/>
       <c r="M950" s="4"/>
@@ -29120,7 +29285,7 @@
       <c r="G951" s="4"/>
       <c r="H951" s="4"/>
       <c r="I951" s="4"/>
-      <c r="J951" s="4"/>
+      <c r="J951" s="7"/>
       <c r="K951" s="4"/>
       <c r="L951" s="4"/>
       <c r="M951" s="4"/>
@@ -29150,7 +29315,7 @@
       <c r="G952" s="4"/>
       <c r="H952" s="4"/>
       <c r="I952" s="4"/>
-      <c r="J952" s="4"/>
+      <c r="J952" s="7"/>
       <c r="K952" s="4"/>
       <c r="L952" s="4"/>
       <c r="M952" s="4"/>
@@ -29180,7 +29345,7 @@
       <c r="G953" s="4"/>
       <c r="H953" s="4"/>
       <c r="I953" s="4"/>
-      <c r="J953" s="4"/>
+      <c r="J953" s="7"/>
       <c r="K953" s="4"/>
       <c r="L953" s="4"/>
       <c r="M953" s="4"/>
@@ -29210,7 +29375,7 @@
       <c r="G954" s="4"/>
       <c r="H954" s="4"/>
       <c r="I954" s="4"/>
-      <c r="J954" s="4"/>
+      <c r="J954" s="7"/>
       <c r="K954" s="4"/>
       <c r="L954" s="4"/>
       <c r="M954" s="4"/>
@@ -29240,7 +29405,7 @@
       <c r="G955" s="4"/>
       <c r="H955" s="4"/>
       <c r="I955" s="4"/>
-      <c r="J955" s="4"/>
+      <c r="J955" s="7"/>
       <c r="K955" s="4"/>
       <c r="L955" s="4"/>
       <c r="M955" s="4"/>
@@ -29270,7 +29435,7 @@
       <c r="G956" s="4"/>
       <c r="H956" s="4"/>
       <c r="I956" s="4"/>
-      <c r="J956" s="4"/>
+      <c r="J956" s="7"/>
       <c r="K956" s="4"/>
       <c r="L956" s="4"/>
       <c r="M956" s="4"/>
@@ -29300,7 +29465,7 @@
       <c r="G957" s="4"/>
       <c r="H957" s="4"/>
       <c r="I957" s="4"/>
-      <c r="J957" s="4"/>
+      <c r="J957" s="7"/>
       <c r="K957" s="4"/>
       <c r="L957" s="4"/>
       <c r="M957" s="4"/>
@@ -29330,7 +29495,7 @@
       <c r="G958" s="4"/>
       <c r="H958" s="4"/>
       <c r="I958" s="4"/>
-      <c r="J958" s="4"/>
+      <c r="J958" s="7"/>
       <c r="K958" s="4"/>
       <c r="L958" s="4"/>
       <c r="M958" s="4"/>
@@ -29360,7 +29525,7 @@
       <c r="G959" s="4"/>
       <c r="H959" s="4"/>
       <c r="I959" s="4"/>
-      <c r="J959" s="4"/>
+      <c r="J959" s="7"/>
       <c r="K959" s="4"/>
       <c r="L959" s="4"/>
       <c r="M959" s="4"/>
@@ -29390,7 +29555,7 @@
       <c r="G960" s="4"/>
       <c r="H960" s="4"/>
       <c r="I960" s="4"/>
-      <c r="J960" s="4"/>
+      <c r="J960" s="7"/>
       <c r="K960" s="4"/>
       <c r="L960" s="4"/>
       <c r="M960" s="4"/>
@@ -29420,7 +29585,7 @@
       <c r="G961" s="4"/>
       <c r="H961" s="4"/>
       <c r="I961" s="4"/>
-      <c r="J961" s="4"/>
+      <c r="J961" s="7"/>
       <c r="K961" s="4"/>
       <c r="L961" s="4"/>
       <c r="M961" s="4"/>
@@ -29450,7 +29615,7 @@
       <c r="G962" s="4"/>
       <c r="H962" s="4"/>
       <c r="I962" s="4"/>
-      <c r="J962" s="4"/>
+      <c r="J962" s="7"/>
       <c r="K962" s="4"/>
       <c r="L962" s="4"/>
       <c r="M962" s="4"/>
@@ -29480,7 +29645,7 @@
       <c r="G963" s="4"/>
       <c r="H963" s="4"/>
       <c r="I963" s="4"/>
-      <c r="J963" s="4"/>
+      <c r="J963" s="7"/>
       <c r="K963" s="4"/>
       <c r="L963" s="4"/>
       <c r="M963" s="4"/>
@@ -29510,7 +29675,7 @@
       <c r="G964" s="4"/>
       <c r="H964" s="4"/>
       <c r="I964" s="4"/>
-      <c r="J964" s="4"/>
+      <c r="J964" s="7"/>
       <c r="K964" s="4"/>
       <c r="L964" s="4"/>
       <c r="M964" s="4"/>
@@ -29540,7 +29705,7 @@
       <c r="G965" s="4"/>
       <c r="H965" s="4"/>
       <c r="I965" s="4"/>
-      <c r="J965" s="4"/>
+      <c r="J965" s="7"/>
       <c r="K965" s="4"/>
       <c r="L965" s="4"/>
       <c r="M965" s="4"/>
@@ -29570,7 +29735,7 @@
       <c r="G966" s="4"/>
       <c r="H966" s="4"/>
       <c r="I966" s="4"/>
-      <c r="J966" s="4"/>
+      <c r="J966" s="7"/>
       <c r="K966" s="4"/>
       <c r="L966" s="4"/>
       <c r="M966" s="4"/>
@@ -29600,7 +29765,7 @@
       <c r="G967" s="4"/>
       <c r="H967" s="4"/>
       <c r="I967" s="4"/>
-      <c r="J967" s="4"/>
+      <c r="J967" s="7"/>
       <c r="K967" s="4"/>
       <c r="L967" s="4"/>
       <c r="M967" s="4"/>
@@ -29630,7 +29795,7 @@
       <c r="G968" s="4"/>
       <c r="H968" s="4"/>
       <c r="I968" s="4"/>
-      <c r="J968" s="4"/>
+      <c r="J968" s="7"/>
       <c r="K968" s="4"/>
       <c r="L968" s="4"/>
       <c r="M968" s="4"/>
@@ -29660,7 +29825,7 @@
       <c r="G969" s="4"/>
       <c r="H969" s="4"/>
       <c r="I969" s="4"/>
-      <c r="J969" s="4"/>
+      <c r="J969" s="7"/>
       <c r="K969" s="4"/>
       <c r="L969" s="4"/>
       <c r="M969" s="4"/>
@@ -29690,7 +29855,7 @@
       <c r="G970" s="4"/>
       <c r="H970" s="4"/>
       <c r="I970" s="4"/>
-      <c r="J970" s="4"/>
+      <c r="J970" s="7"/>
       <c r="K970" s="4"/>
       <c r="L970" s="4"/>
       <c r="M970" s="4"/>
@@ -29720,7 +29885,7 @@
       <c r="G971" s="4"/>
       <c r="H971" s="4"/>
       <c r="I971" s="4"/>
-      <c r="J971" s="4"/>
+      <c r="J971" s="7"/>
       <c r="K971" s="4"/>
       <c r="L971" s="4"/>
       <c r="M971" s="4"/>
@@ -29750,7 +29915,7 @@
       <c r="G972" s="4"/>
       <c r="H972" s="4"/>
       <c r="I972" s="4"/>
-      <c r="J972" s="4"/>
+      <c r="J972" s="7"/>
       <c r="K972" s="4"/>
       <c r="L972" s="4"/>
       <c r="M972" s="4"/>
@@ -29780,7 +29945,7 @@
       <c r="G973" s="4"/>
       <c r="H973" s="4"/>
       <c r="I973" s="4"/>
-      <c r="J973" s="4"/>
+      <c r="J973" s="7"/>
       <c r="K973" s="4"/>
       <c r="L973" s="4"/>
       <c r="M973" s="4"/>
@@ -29810,7 +29975,7 @@
       <c r="G974" s="4"/>
       <c r="H974" s="4"/>
       <c r="I974" s="4"/>
-      <c r="J974" s="4"/>
+      <c r="J974" s="7"/>
       <c r="K974" s="4"/>
       <c r="L974" s="4"/>
       <c r="M974" s="4"/>
@@ -29840,7 +30005,7 @@
       <c r="G975" s="4"/>
       <c r="H975" s="4"/>
       <c r="I975" s="4"/>
-      <c r="J975" s="4"/>
+      <c r="J975" s="7"/>
       <c r="K975" s="4"/>
       <c r="L975" s="4"/>
       <c r="M975" s="4"/>
@@ -29870,7 +30035,7 @@
       <c r="G976" s="4"/>
       <c r="H976" s="4"/>
       <c r="I976" s="4"/>
-      <c r="J976" s="4"/>
+      <c r="J976" s="7"/>
       <c r="K976" s="4"/>
       <c r="L976" s="4"/>
       <c r="M976" s="4"/>
@@ -29900,7 +30065,7 @@
       <c r="G977" s="4"/>
       <c r="H977" s="4"/>
       <c r="I977" s="4"/>
-      <c r="J977" s="4"/>
+      <c r="J977" s="7"/>
       <c r="K977" s="4"/>
       <c r="L977" s="4"/>
       <c r="M977" s="4"/>
@@ -29930,7 +30095,7 @@
       <c r="G978" s="4"/>
       <c r="H978" s="4"/>
       <c r="I978" s="4"/>
-      <c r="J978" s="4"/>
+      <c r="J978" s="7"/>
       <c r="K978" s="4"/>
       <c r="L978" s="4"/>
       <c r="M978" s="4"/>
@@ -29960,7 +30125,7 @@
       <c r="G979" s="4"/>
       <c r="H979" s="4"/>
       <c r="I979" s="4"/>
-      <c r="J979" s="4"/>
+      <c r="J979" s="7"/>
       <c r="K979" s="4"/>
       <c r="L979" s="4"/>
       <c r="M979" s="4"/>
@@ -29990,7 +30155,7 @@
       <c r="G980" s="4"/>
       <c r="H980" s="4"/>
       <c r="I980" s="4"/>
-      <c r="J980" s="4"/>
+      <c r="J980" s="7"/>
       <c r="K980" s="4"/>
       <c r="L980" s="4"/>
       <c r="M980" s="4"/>
@@ -30020,7 +30185,7 @@
       <c r="G981" s="4"/>
       <c r="H981" s="4"/>
       <c r="I981" s="4"/>
-      <c r="J981" s="4"/>
+      <c r="J981" s="7"/>
       <c r="K981" s="4"/>
       <c r="L981" s="4"/>
       <c r="M981" s="4"/>
@@ -30050,7 +30215,7 @@
       <c r="G982" s="4"/>
       <c r="H982" s="4"/>
       <c r="I982" s="4"/>
-      <c r="J982" s="4"/>
+      <c r="J982" s="7"/>
       <c r="K982" s="4"/>
       <c r="L982" s="4"/>
       <c r="M982" s="4"/>
@@ -30080,7 +30245,7 @@
       <c r="G983" s="4"/>
       <c r="H983" s="4"/>
       <c r="I983" s="4"/>
-      <c r="J983" s="4"/>
+      <c r="J983" s="7"/>
       <c r="K983" s="4"/>
       <c r="L983" s="4"/>
       <c r="M983" s="4"/>
@@ -30110,7 +30275,7 @@
       <c r="G984" s="4"/>
       <c r="H984" s="4"/>
       <c r="I984" s="4"/>
-      <c r="J984" s="4"/>
+      <c r="J984" s="7"/>
       <c r="K984" s="4"/>
       <c r="L984" s="4"/>
       <c r="M984" s="4"/>
@@ -30140,7 +30305,7 @@
       <c r="G985" s="4"/>
       <c r="H985" s="4"/>
       <c r="I985" s="4"/>
-      <c r="J985" s="4"/>
+      <c r="J985" s="7"/>
       <c r="K985" s="4"/>
       <c r="L985" s="4"/>
       <c r="M985" s="4"/>
@@ -30170,7 +30335,7 @@
       <c r="G986" s="4"/>
       <c r="H986" s="4"/>
       <c r="I986" s="4"/>
-      <c r="J986" s="4"/>
+      <c r="J986" s="7"/>
       <c r="K986" s="4"/>
       <c r="L986" s="4"/>
       <c r="M986" s="4"/>
@@ -30200,7 +30365,7 @@
       <c r="G987" s="4"/>
       <c r="H987" s="4"/>
       <c r="I987" s="4"/>
-      <c r="J987" s="4"/>
+      <c r="J987" s="7"/>
       <c r="K987" s="4"/>
       <c r="L987" s="4"/>
       <c r="M987" s="4"/>
@@ -30230,7 +30395,7 @@
       <c r="G988" s="4"/>
       <c r="H988" s="4"/>
       <c r="I988" s="4"/>
-      <c r="J988" s="4"/>
+      <c r="J988" s="7"/>
       <c r="K988" s="4"/>
       <c r="L988" s="4"/>
       <c r="M988" s="4"/>
@@ -30260,7 +30425,7 @@
       <c r="G989" s="4"/>
       <c r="H989" s="4"/>
       <c r="I989" s="4"/>
-      <c r="J989" s="4"/>
+      <c r="J989" s="7"/>
       <c r="K989" s="4"/>
       <c r="L989" s="4"/>
       <c r="M989" s="4"/>
@@ -30290,7 +30455,7 @@
       <c r="G990" s="4"/>
       <c r="H990" s="4"/>
       <c r="I990" s="4"/>
-      <c r="J990" s="4"/>
+      <c r="J990" s="7"/>
       <c r="K990" s="4"/>
       <c r="L990" s="4"/>
       <c r="M990" s="4"/>
@@ -30320,7 +30485,7 @@
       <c r="G991" s="4"/>
       <c r="H991" s="4"/>
       <c r="I991" s="4"/>
-      <c r="J991" s="4"/>
+      <c r="J991" s="7"/>
       <c r="K991" s="4"/>
       <c r="L991" s="4"/>
       <c r="M991" s="4"/>
@@ -30350,7 +30515,7 @@
       <c r="G992" s="4"/>
       <c r="H992" s="4"/>
       <c r="I992" s="4"/>
-      <c r="J992" s="4"/>
+      <c r="J992" s="7"/>
       <c r="K992" s="4"/>
       <c r="L992" s="4"/>
       <c r="M992" s="4"/>
@@ -30380,7 +30545,7 @@
       <c r="G993" s="4"/>
       <c r="H993" s="4"/>
       <c r="I993" s="4"/>
-      <c r="J993" s="4"/>
+      <c r="J993" s="7"/>
       <c r="K993" s="4"/>
       <c r="L993" s="4"/>
       <c r="M993" s="4"/>
@@ -30410,7 +30575,7 @@
       <c r="G994" s="4"/>
       <c r="H994" s="4"/>
       <c r="I994" s="4"/>
-      <c r="J994" s="4"/>
+      <c r="J994" s="7"/>
       <c r="K994" s="4"/>
       <c r="L994" s="4"/>
       <c r="M994" s="4"/>
@@ -30440,7 +30605,7 @@
       <c r="G995" s="4"/>
       <c r="H995" s="4"/>
       <c r="I995" s="4"/>
-      <c r="J995" s="4"/>
+      <c r="J995" s="7"/>
       <c r="K995" s="4"/>
       <c r="L995" s="4"/>
       <c r="M995" s="4"/>
@@ -30470,7 +30635,7 @@
       <c r="G996" s="4"/>
       <c r="H996" s="4"/>
       <c r="I996" s="4"/>
-      <c r="J996" s="4"/>
+      <c r="J996" s="7"/>
       <c r="K996" s="4"/>
       <c r="L996" s="4"/>
       <c r="M996" s="4"/>
@@ -30500,7 +30665,7 @@
       <c r="G997" s="4"/>
       <c r="H997" s="4"/>
       <c r="I997" s="4"/>
-      <c r="J997" s="4"/>
+      <c r="J997" s="7"/>
       <c r="K997" s="4"/>
       <c r="L997" s="4"/>
       <c r="M997" s="4"/>
@@ -30530,7 +30695,7 @@
       <c r="G998" s="4"/>
       <c r="H998" s="4"/>
       <c r="I998" s="4"/>
-      <c r="J998" s="4"/>
+      <c r="J998" s="7"/>
       <c r="K998" s="4"/>
       <c r="L998" s="4"/>
       <c r="M998" s="4"/>
@@ -30560,7 +30725,7 @@
       <c r="G999" s="4"/>
       <c r="H999" s="4"/>
       <c r="I999" s="4"/>
-      <c r="J999" s="4"/>
+      <c r="J999" s="7"/>
       <c r="K999" s="4"/>
       <c r="L999" s="4"/>
       <c r="M999" s="4"/>
@@ -30590,7 +30755,7 @@
       <c r="G1000" s="4"/>
       <c r="H1000" s="4"/>
       <c r="I1000" s="4"/>
-      <c r="J1000" s="4"/>
+      <c r="J1000" s="7"/>
       <c r="K1000" s="4"/>
       <c r="L1000" s="4"/>
       <c r="M1000" s="4"/>

--- a/results/metrics.xlsx
+++ b/results/metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahmadabdullah/Desktop/GHaLIB/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B7F4A3-FF33-784C-8F95-F12A83F010D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDEDD9FB-3FFC-F84C-90E1-56C2C47C91D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="25">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -92,6 +92,9 @@
   </si>
   <si>
     <t>MultiLing BERT</t>
+  </si>
+  <si>
+    <t>Finetuned RoBERTa</t>
   </si>
 </sst>
 </file>
@@ -417,7 +420,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="12.6640625" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="19.5" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
     <col min="9" max="9" width="16.6640625" customWidth="1"/>
     <col min="10" max="10" width="22.6640625" style="8" customWidth="1"/>
@@ -493,17 +496,13 @@
         <v>7</v>
       </c>
       <c r="G2" s="7">
-        <v>0.85</v>
+        <v>0.81</v>
       </c>
       <c r="H2" s="7">
-        <v>0.85</v>
+        <v>0.81</v>
       </c>
-      <c r="I2" s="7">
-        <v>0.85</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>17</v>
-      </c>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
@@ -1406,15 +1405,29 @@
       <c r="AB21" s="4"/>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
+      <c r="A22" s="7">
+        <v>20</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G22" s="7">
+        <v>0.74</v>
+      </c>
+      <c r="H22" s="7">
+        <v>0.67</v>
+      </c>
+      <c r="I22" s="7"/>
       <c r="J22" s="7"/>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1436,16 +1449,34 @@
       <c r="AB22" s="4"/>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="7"/>
+      <c r="A23" s="7">
+        <v>20</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G23" s="7">
+        <v>0.85</v>
+      </c>
+      <c r="H23" s="7">
+        <v>0.85</v>
+      </c>
+      <c r="I23" s="7">
+        <v>0.85</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>17</v>
+      </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>

--- a/results/metrics.xlsx
+++ b/results/metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahmadabdullah/Desktop/GHaLIB/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1457F9C-BBD8-8844-8E68-0540ECC887E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC4F0AD-34A0-9E49-A22B-6301A3F37A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="26">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -1433,8 +1433,12 @@
       <c r="H22" s="6">
         <v>0.7</v>
       </c>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
+      <c r="I22" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>

--- a/results/metrics.xlsx
+++ b/results/metrics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahmadabdullah/Desktop/GHaLIB/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC4F0AD-34A0-9E49-A22B-6301A3F37A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ACA6404-F944-C840-9E44-094303475B03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -642,13 +642,13 @@
         <v>6</v>
       </c>
       <c r="G5" s="6">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="H5" s="6">
-        <v>0.53</v>
+        <v>0.66</v>
       </c>
       <c r="I5" s="6">
-        <v>0.53</v>
+        <v>0.66</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>17</v>
@@ -1471,8 +1471,8 @@
       <c r="D23" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E23" s="8" t="s">
-        <v>9</v>
+      <c r="E23" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>7</v>

--- a/results/metrics.xlsx
+++ b/results/metrics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahmadabdullah/Desktop/GHaLIB/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ACA6404-F944-C840-9E44-094303475B03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{950AFC0A-2462-2D41-B98A-9C40486E7AA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="29">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -70,12 +70,6 @@
     <t>RoBERTa + ROS</t>
   </si>
   <si>
-    <t>Test Score</t>
-  </si>
-  <si>
-    <t>Currently best on LB</t>
-  </si>
-  <si>
     <t>DistilBERT</t>
   </si>
   <si>
@@ -88,9 +82,6 @@
     <t>RoBERTa Urdu</t>
   </si>
   <si>
-    <t>Remarks</t>
-  </si>
-  <si>
     <t>MultiLing BERT</t>
   </si>
   <si>
@@ -99,12 +90,30 @@
   <si>
     <t>-</t>
   </si>
+  <si>
+    <t>German</t>
+  </si>
+  <si>
+    <t>Spanish</t>
+  </si>
+  <si>
+    <t>Multi</t>
+  </si>
+  <si>
+    <t>XLM RoBERTa</t>
+  </si>
+  <si>
+    <t>XLM RoBERTa + EuroBERT</t>
+  </si>
+  <si>
+    <t>XLM RoBERTa + UrduBERT</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -135,8 +144,20 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -161,6 +182,18 @@
         <bgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFD9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -174,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -198,6 +231,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -423,7 +477,7 @@
   <cols>
     <col min="1" max="1" width="12.6640625" style="7"/>
     <col min="2" max="2" width="12.6640625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="19.5" style="7" customWidth="1"/>
+    <col min="3" max="3" width="46.1640625" style="7" customWidth="1"/>
     <col min="4" max="4" width="15" style="7" customWidth="1"/>
     <col min="5" max="8" width="12.6640625" style="7"/>
     <col min="9" max="9" width="16.6640625" style="7" customWidth="1"/>
@@ -456,12 +510,8 @@
       <c r="H1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
       <c r="K1" s="3"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
@@ -506,8 +556,8 @@
       <c r="H2" s="6">
         <v>0.81</v>
       </c>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
@@ -552,7 +602,8 @@
       <c r="H3" s="6">
         <v>0.56000000000000005</v>
       </c>
-      <c r="J3" s="6"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="14"/>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
@@ -580,7 +631,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>12</v>
@@ -597,12 +648,8 @@
       <c r="H4" s="6">
         <v>0.93</v>
       </c>
-      <c r="I4" s="6">
-        <v>0.95</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>17</v>
-      </c>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
@@ -630,7 +677,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>12</v>
@@ -647,12 +694,8 @@
       <c r="H5" s="6">
         <v>0.66</v>
       </c>
-      <c r="I5" s="6">
-        <v>0.66</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>17</v>
-      </c>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
@@ -697,8 +740,8 @@
       <c r="H6" s="6">
         <v>0.52</v>
       </c>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
@@ -743,8 +786,8 @@
       <c r="H7" s="6">
         <v>0.24</v>
       </c>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
@@ -772,7 +815,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>12</v>
@@ -789,8 +832,8 @@
       <c r="H8" s="6">
         <v>0.54</v>
       </c>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
@@ -818,7 +861,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>12</v>
@@ -835,8 +878,8 @@
       <c r="H9" s="6">
         <v>0.78</v>
       </c>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
@@ -864,7 +907,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>12</v>
@@ -881,8 +924,8 @@
       <c r="H10" s="6">
         <v>0.73</v>
       </c>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
@@ -910,7 +953,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>12</v>
@@ -927,8 +970,8 @@
       <c r="H11" s="6">
         <v>0.44</v>
       </c>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
@@ -956,7 +999,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>12</v>
@@ -973,8 +1016,8 @@
       <c r="H12" s="6">
         <v>0.93</v>
       </c>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
@@ -1002,7 +1045,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>12</v>
@@ -1019,8 +1062,8 @@
       <c r="H13" s="6">
         <v>0.51</v>
       </c>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
       <c r="K13" s="6"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
@@ -1065,8 +1108,8 @@
       <c r="H14" s="6">
         <v>0.85</v>
       </c>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
       <c r="K14" s="6"/>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
@@ -1111,8 +1154,8 @@
       <c r="H15" s="6">
         <v>0.56000000000000005</v>
       </c>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
       <c r="K15" s="6"/>
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
@@ -1140,7 +1183,7 @@
         <v>11</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>12</v>
@@ -1157,8 +1200,8 @@
       <c r="H16" s="6">
         <v>0.93</v>
       </c>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
@@ -1186,7 +1229,7 @@
         <v>11</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>12</v>
@@ -1203,8 +1246,8 @@
       <c r="H17" s="6">
         <v>0.53</v>
       </c>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
       <c r="K17" s="6"/>
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
@@ -1232,7 +1275,7 @@
         <v>11</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>12</v>
@@ -1249,8 +1292,8 @@
       <c r="H18" s="6">
         <v>0.76</v>
       </c>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
       <c r="K18" s="6"/>
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
@@ -1278,7 +1321,7 @@
         <v>11</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>12</v>
@@ -1295,8 +1338,8 @@
       <c r="H19" s="6">
         <v>0.49</v>
       </c>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
       <c r="K19" s="6"/>
       <c r="L19" s="6"/>
       <c r="M19" s="6"/>
@@ -1324,7 +1367,7 @@
         <v>11</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>12</v>
@@ -1341,8 +1384,8 @@
       <c r="H20" s="6">
         <v>0.93</v>
       </c>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
       <c r="K20" s="6"/>
       <c r="L20" s="6"/>
       <c r="M20" s="6"/>
@@ -1370,7 +1413,7 @@
         <v>11</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>12</v>
@@ -1387,8 +1430,8 @@
       <c r="H21" s="6">
         <v>0.5</v>
       </c>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
@@ -1416,10 +1459,10 @@
         <v>11</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>9</v>
@@ -1433,12 +1476,8 @@
       <c r="H22" s="6">
         <v>0.7</v>
       </c>
-      <c r="I22" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>17</v>
-      </c>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
@@ -1466,10 +1505,10 @@
         <v>11</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>10</v>
@@ -1480,15 +1519,11 @@
       <c r="G23" s="6">
         <v>0.85</v>
       </c>
-      <c r="H23" s="6">
+      <c r="H23" s="12">
         <v>0.85</v>
       </c>
-      <c r="I23" s="6">
-        <v>0.85</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>17</v>
-      </c>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
       <c r="K23" s="6"/>
       <c r="L23" s="6"/>
       <c r="M23" s="6"/>
@@ -1512,15 +1547,29 @@
       <c r="A24" s="6">
         <v>23</v>
       </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
+      <c r="B24" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H24" s="10">
+        <v>0.86299999999999999</v>
+      </c>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
       <c r="K24" s="6"/>
       <c r="L24" s="6"/>
       <c r="M24" s="6"/>
@@ -1544,15 +1593,29 @@
       <c r="A25" s="6">
         <v>24</v>
       </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
+      <c r="B25" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H25" s="10">
+        <v>0.872</v>
+      </c>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
       <c r="K25" s="6"/>
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
@@ -1576,15 +1639,29 @@
       <c r="A26" s="6">
         <v>25</v>
       </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
+      <c r="B26" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H26" s="10">
+        <v>0.84499999999999997</v>
+      </c>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
       <c r="K26" s="6"/>
       <c r="L26" s="6"/>
       <c r="M26" s="6"/>
@@ -1608,15 +1685,29 @@
       <c r="A27" s="6">
         <v>26</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
+      <c r="B27" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H27" s="10">
+        <v>0.94499999999999995</v>
+      </c>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
       <c r="K27" s="6"/>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
@@ -1640,15 +1731,29 @@
       <c r="A28" s="6">
         <v>27</v>
       </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
+      <c r="B28" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H28" s="10">
+        <v>0.71199999999999997</v>
+      </c>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
       <c r="K28" s="6"/>
       <c r="L28" s="6"/>
       <c r="M28" s="6"/>
@@ -1672,15 +1777,29 @@
       <c r="A29" s="6">
         <v>28</v>
       </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
+      <c r="B29" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H29" s="10">
+        <v>0.70130000000000003</v>
+      </c>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
       <c r="K29" s="6"/>
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
@@ -1704,15 +1823,29 @@
       <c r="A30" s="6">
         <v>29</v>
       </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
+      <c r="B30" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H30" s="10">
+        <v>0.68600000000000005</v>
+      </c>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
       <c r="K30" s="6"/>
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
@@ -1736,15 +1869,29 @@
       <c r="A31" s="6">
         <v>30</v>
       </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
+      <c r="B31" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H31" s="10">
+        <v>0.65</v>
+      </c>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
       <c r="K31" s="6"/>
       <c r="L31" s="6"/>
       <c r="M31" s="6"/>
